--- a/rampup.xlsx
+++ b/rampup.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\projects\efeed\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18252" windowHeight="7896"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18255" windowHeight="7890"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -13,7 +18,7 @@
     <sheet name="ellipse" sheetId="7" r:id="rId4"/>
     <sheet name="Лист2" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,12 +45,6 @@
     <t>The given parameters are:</t>
   </si>
   <si>
-    <t>v0 - base speed,</t>
-  </si>
-  <si>
-    <t>v - slew speed,</t>
-  </si>
-  <si>
     <t>a - acceleration,</t>
   </si>
   <si>
@@ -56,9 +55,6 @@
   </si>
   <si>
     <t>S - acceleration/deceleration distance</t>
-  </si>
-  <si>
-    <t>p1 - delay period for the initial step</t>
   </si>
   <si>
     <t>pS - delay period for the slew speed steps</t>
@@ -901,12 +897,21 @@
   <si>
     <t>(2*x+1)b²=2xb²+b²</t>
   </si>
+  <si>
+    <t>v - target velocity, slew speed</t>
+  </si>
+  <si>
+    <t>v0 - initial velocity, base speed,</t>
+  </si>
+  <si>
+    <t>p1 - delay period for the initial step:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -915,6 +920,7 @@
     <numFmt numFmtId="168" formatCode="0.00000000"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* &quot;-&quot;?\ _₽_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="181" formatCode="0.0000000000000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1141,7 +1147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1211,6 +1217,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1279,6 +1286,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1365,107 +1392,98 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>460</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>660</c:v>
-                </c:pt>
                 <c:pt idx="3" formatCode="0">
+                  <c:v>208.76826722338205</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0">
+                  <c:v>243.70430544272949</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0">
+                  <c:v>292.39766081871346</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0">
+                  <c:v>344.82758620689657</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0">
+                  <c:v>394.21813403416559</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0">
+                  <c:v>439.88269794721407</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>482.3151125401929</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0">
+                  <c:v>520.83333333333337</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0">
+                  <c:v>557.62081784386612</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0">
+                  <c:v>591.71597633136093</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0">
+                  <c:v>655.02183406113534</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="0">
+                  <c:v>684.93150684931504</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="0">
+                  <c:v>714.28571428571433</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="0">
+                  <c:v>740.74074074074076</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0">
+                  <c:v>767.26342710997437</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="0">
+                  <c:v>793.65079365079362</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="0">
+                  <c:v>817.43869209809259</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0">
+                  <c:v>842.69662921348311</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="0">
+                  <c:v>864.55331412103749</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="0">
+                  <c:v>887.5739644970414</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0">
                   <c:v>909.09090909090912</c:v>
                 </c:pt>
-                <c:pt idx="4" formatCode="0">
+                <c:pt idx="25" formatCode="0">
+                  <c:v>931.67701863354034</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="0">
+                  <c:v>952.38095238095241</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0">
+                  <c:v>974.02597402597405</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="0">
+                  <c:v>993.37748344370857</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="0">
+                  <c:v>1013.5135135135135</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0">
+                  <c:v>1034.4827586206898</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="0">
+                  <c:v>1052.6315789473683</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="0">
                   <c:v>1071.4285714285713</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="0">
-                  <c:v>1250</c:v>
-                </c:pt>
-                <c:pt idx="6" formatCode="0">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="0">
-                  <c:v>1666.6666666666667</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="0">
-                  <c:v>1875</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="10" formatCode="0">
-                  <c:v>2142.8571428571427</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="0">
-                  <c:v>2307.6923076923076</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="0">
-                  <c:v>2307.6923076923076</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="0">
-                  <c:v>2500</c:v>
-                </c:pt>
-                <c:pt idx="14" formatCode="0">
-                  <c:v>2727.2727272727275</c:v>
-                </c:pt>
-                <c:pt idx="15" formatCode="0">
-                  <c:v>2727.2727272727275</c:v>
-                </c:pt>
-                <c:pt idx="16" formatCode="0">
-                  <c:v>2727.2727272727275</c:v>
-                </c:pt>
-                <c:pt idx="17" formatCode="0">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="18" formatCode="0">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="19" formatCode="0">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="20" formatCode="0">
-                  <c:v>3333.3333333333335</c:v>
-                </c:pt>
-                <c:pt idx="21" formatCode="0">
-                  <c:v>3333.3333333333335</c:v>
-                </c:pt>
-                <c:pt idx="22" formatCode="0">
-                  <c:v>3333.3333333333335</c:v>
-                </c:pt>
-                <c:pt idx="23" formatCode="0">
-                  <c:v>3333.3333333333335</c:v>
-                </c:pt>
-                <c:pt idx="24" formatCode="0">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="25" formatCode="0">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="26" formatCode="0">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="0">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="28" formatCode="0">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="29" formatCode="0">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="0">
-                  <c:v>4285.7142857142853</c:v>
-                </c:pt>
-                <c:pt idx="31" formatCode="0">
-                  <c:v>4285.7142857142853</c:v>
-                </c:pt>
-                <c:pt idx="32" formatCode="0">
-                  <c:v>4285.7142857142853</c:v>
-                </c:pt>
                 <c:pt idx="33" formatCode="0">
-                  <c:v>4285.7142857142853</c:v>
+                  <c:v>1090.909090909091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1503,109 +1521,100 @@
             <c:numRef>
               <c:f>Лист1!$M$2:$M$35</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* "-"?\ _₽_-;_-@_-</c:formatCode>
+                <c:formatCode>_-* #\ ##0.0\ _₽_-;\-* #\ ##0.0\ _₽_-;_-* "-"?\ _₽_-;_-@_-</c:formatCode>
                 <c:ptCount val="34"/>
-                <c:pt idx="0">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>460</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>600</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>895.82364335844579</c:v>
+                  <c:v>208.80613017821099</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1071.8241083510134</c:v>
+                  <c:v>243.67209828576023</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1274.2350098532629</c:v>
+                  <c:v>292.40006101302259</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1470.6529344628423</c:v>
+                  <c:v>344.74772451762777</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1652.1368949298385</c:v>
+                  <c:v>394.35874060546962</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1819.1099575609635</c:v>
+                  <c:v>440.03143692479534</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1973.7091502469334</c:v>
+                  <c:v>482.11394386876282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2117.9756015258135</c:v>
+                  <c:v>521.17052431883496</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2253.5695366079408</c:v>
+                  <c:v>557.69985514203893</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2381.7996403943566</c:v>
+                  <c:v>592.10117694056908</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2503.6985683714856</c:v>
+                  <c:v>624.68871380354847</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2620.0899482814275</c:v>
+                  <c:v>655.71108433692723</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2731.6394881111296</c:v>
+                  <c:v>685.36736237531932</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2838.892515239565</c:v>
+                  <c:v>713.81911534285325</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2942.3014191760326</c:v>
+                  <c:v>741.19921562036393</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3042.2458583344142</c:v>
+                  <c:v>767.61829107819574</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3139.0478134584259</c:v>
+                  <c:v>793.16949026335078</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3232.9829499617563</c:v>
+                  <c:v>817.93204621478105</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3324.2893084355046</c:v>
+                  <c:v>841.97397731643673</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3413.1740369527561</c:v>
+                  <c:v>865.35416119711988</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3499.8186696031266</c:v>
+                  <c:v>888.12394733828319</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3584.3833119984306</c:v>
+                  <c:v>910.32842588654194</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3667.0099949405731</c:v>
+                  <c:v>932.00743701080285</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3747.8253877183624</c:v>
+                  <c:v>953.19638210035691</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3826.9430130853784</c:v>
+                  <c:v>973.9268819036414</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3904.4650705281497</c:v>
+                  <c:v>994.22731518675721</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3980.4839487110507</c:v>
+                  <c:v>1014.1232631977515</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4055.0834891022514</c:v>
+                  <c:v>1033.6378791828179</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4128.3400487729195</c:v>
+                  <c:v>1052.7921977520673</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4200.3233998556252</c:v>
+                  <c:v>1071.6053955807872</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4271.0974951928465</c:v>
+                  <c:v>1090.095012441446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1620,11 +1629,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="205023104"/>
-        <c:axId val="205033472"/>
+        <c:axId val="-1409098560"/>
+        <c:axId val="-1409092576"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="205023104"/>
+        <c:axId val="-1409098560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1680,12 +1689,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205033472"/>
+        <c:crossAx val="-1409092576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="205033472"/>
+        <c:axId val="-1409092576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1742,7 +1751,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205023104"/>
+        <c:crossAx val="-1409098560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1841,6 +1850,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1953,80 +1982,71 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>65.217391304347828</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>45.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.488734331156856</c:v>
+                  <c:v>1436.7394278317272</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.969581310163637</c:v>
+                  <c:v>777.68464442267782</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17.895976530533058</c:v>
+                  <c:v>673.16496774998018</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.985485733969318</c:v>
+                  <c:v>605.37709486456424</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14.623864683136356</c:v>
+                  <c:v>556.07499228878555</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13.581390701044569</c:v>
+                  <c:v>517.86406477110768</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.746342636032498</c:v>
+                  <c:v>487.00130106892351</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.056046390730806</c:v>
+                  <c:v>461.33413913067466</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.471937957406334</c:v>
+                  <c:v>439.51516797636657</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>10.9686817805724</c:v>
+                  <c:v>420.64789692555138</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10.528793839556215</c:v>
+                  <c:v>404.10758665094988</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>10.139735605393065</c:v>
+                  <c:v>389.44270718017805</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.7922325416319662</c:v>
+                  <c:v>376.31713596099593</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.4792472705557635</c:v>
+                  <c:v>364.47447024508324</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.1953244492807684</c:v>
+                  <c:v>353.71505109645437</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.9361573201419233</c:v>
+                  <c:v>343.88064571056657</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.6982919809590182</c:v>
+                  <c:v>334.84392860567385</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.4789202355411284</c:v>
+                  <c:v>326.5010721302105</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.2757311412822663</c:v>
+                  <c:v>318.76641046340961</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.0868024725439884</c:v>
+                  <c:v>311.56852150994916</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.9105199522712821</c:v>
+                  <c:v>304.84730003176361</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.745516194040392</c:v>
+                  <c:v>298.55173745662682</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2138,80 +2158,71 @@
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>65.217391304347828</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.488734331156856</c:v>
+                  <c:v>1436.7394278317272</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>27.989667116328057</c:v>
+                  <c:v>1231.1627064013815</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23.543537705383493</c:v>
+                  <c:v>1025.9915779793182</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.39910253261592</c:v>
+                  <c:v>870.20153771793866</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.158301586306511</c:v>
+                  <c:v>760.72866938210097</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16.491581432616403</c:v>
+                  <c:v>681.76947105547879</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15.199807933325262</c:v>
+                  <c:v>622.25953805157644</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.164469117768713</c:v>
+                  <c:v>575.62733501112177</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.312214028751834</c:v>
+                  <c:v>537.92375456793673</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12.595517897984431</c:v>
+                  <c:v>506.67016328209712</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11.982273097481261</c:v>
+                  <c:v>480.23918692781717</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11.449988585192518</c:v>
+                  <c:v>457.51857360070113</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.982415553212096</c:v>
+                  <c:v>437.72145635921703</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.567501178348909</c:v>
+                  <c:v>420.27453951819086</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10.196100169914358</c:v>
+                  <c:v>404.74948391426454</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.8611359492242254</c:v>
+                  <c:v>390.81924373977637</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9.5570382430548868</c:v>
+                  <c:v>378.22937427962967</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9.2793560820835381</c:v>
+                  <c:v>366.77863569270511</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9.0244853009254982</c:v>
+                  <c:v>356.30554872511436</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.7894726946838215</c:v>
+                  <c:v>346.67886681793249</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8.5718726688779991</c:v>
+                  <c:v>337.79068890001577</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.3696405737571222</c:v>
+                  <c:v>329.55139207900584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2323,80 +2334,71 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>33</c:v>
+                  <c:v>1437</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28</c:v>
+                  <c:v>1231</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24</c:v>
+                  <c:v>1026</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20</c:v>
+                  <c:v>870</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18</c:v>
+                  <c:v>761</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16</c:v>
+                  <c:v>682</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>15</c:v>
+                  <c:v>622</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14</c:v>
+                  <c:v>576</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13</c:v>
+                  <c:v>538</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>507</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11</c:v>
+                  <c:v>458</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11</c:v>
+                  <c:v>438</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10</c:v>
+                  <c:v>405</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>10</c:v>
+                  <c:v>391</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>10</c:v>
+                  <c:v>378</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>9</c:v>
+                  <c:v>367</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>9</c:v>
+                  <c:v>356</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9</c:v>
+                  <c:v>347</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>9</c:v>
+                  <c:v>338</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8</c:v>
+                  <c:v>330</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2411,11 +2413,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="205538432"/>
-        <c:axId val="205539968"/>
+        <c:axId val="-1409087136"/>
+        <c:axId val="-1409085504"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="205538432"/>
+        <c:axId val="-1409087136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2472,12 +2474,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205539968"/>
+        <c:crossAx val="-1409085504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="205539968"/>
+        <c:axId val="-1409085504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2534,7 +2536,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205538432"/>
+        <c:crossAx val="-1409087136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2790,11 +2792,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="205556352"/>
-        <c:axId val="205574528"/>
+        <c:axId val="-1409090400"/>
+        <c:axId val="-1409084960"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="205556352"/>
+        <c:axId val="-1409090400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2850,12 +2852,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205574528"/>
+        <c:crossAx val="-1409084960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="205574528"/>
+        <c:axId val="-1409084960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2912,7 +2914,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205556352"/>
+        <c:crossAx val="-1409090400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3051,148 +3053,139 @@
             <c:numRef>
               <c:f>Лист1!$M$2:$M$48</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* "-"?\ _₽_-;_-@_-</c:formatCode>
+                <c:formatCode>_-* #\ ##0.0\ _₽_-;\-* #\ ##0.0\ _₽_-;_-* "-"?\ _₽_-;_-@_-</c:formatCode>
                 <c:ptCount val="47"/>
-                <c:pt idx="0">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>460</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>600</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>895.82364335844579</c:v>
+                  <c:v>208.80613017821099</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1071.8241083510134</c:v>
+                  <c:v>243.67209828576023</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1274.2350098532629</c:v>
+                  <c:v>292.40006101302259</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1470.6529344628423</c:v>
+                  <c:v>344.74772451762777</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1652.1368949298385</c:v>
+                  <c:v>394.35874060546962</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1819.1099575609635</c:v>
+                  <c:v>440.03143692479534</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1973.7091502469334</c:v>
+                  <c:v>482.11394386876282</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2117.9756015258135</c:v>
+                  <c:v>521.17052431883496</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2253.5695366079408</c:v>
+                  <c:v>557.69985514203893</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2381.7996403943566</c:v>
+                  <c:v>592.10117694056908</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2503.6985683714856</c:v>
+                  <c:v>624.68871380354847</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2620.0899482814275</c:v>
+                  <c:v>655.71108433692723</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2731.6394881111296</c:v>
+                  <c:v>685.36736237531932</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2838.892515239565</c:v>
+                  <c:v>713.81911534285325</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2942.3014191760326</c:v>
+                  <c:v>741.19921562036393</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3042.2458583344142</c:v>
+                  <c:v>767.61829107819574</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3139.0478134584259</c:v>
+                  <c:v>793.16949026335078</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3232.9829499617563</c:v>
+                  <c:v>817.93204621478105</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3324.2893084355046</c:v>
+                  <c:v>841.97397731643673</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3413.1740369527561</c:v>
+                  <c:v>865.35416119711988</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3499.8186696031266</c:v>
+                  <c:v>888.12394733828319</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3584.3833119984306</c:v>
+                  <c:v>910.32842588654194</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3667.0099949405731</c:v>
+                  <c:v>932.00743701080285</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>3747.8253877183624</c:v>
+                  <c:v>953.19638210035691</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3826.9430130853784</c:v>
+                  <c:v>973.9268819036414</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3904.4650705281497</c:v>
+                  <c:v>994.22731518675721</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3980.4839487110507</c:v>
+                  <c:v>1014.1232631977515</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4055.0834891022514</c:v>
+                  <c:v>1033.6378791828179</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4128.3400487729195</c:v>
+                  <c:v>1052.7921977520673</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4200.3233998556252</c:v>
+                  <c:v>1071.6053955807872</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4271.0974951928465</c:v>
+                  <c:v>1090.095012441446</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4340.7211236271087</c:v>
+                  <c:v>1108.277139670437</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4409.2484736975857</c:v>
+                  <c:v>1126.1665817243077</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4476.7296208649477</c:v>
+                  <c:v>1143.7769953601046</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4543.2109505323206</c:v>
+                  <c:v>1161.1210101016891</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4608.7355268779165</c:v>
+                  <c:v>1178.2103329685826</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>4673.3434157250049</c:v>
+                  <c:v>1195.0558399019194</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4737.0719682430508</c:v>
+                  <c:v>1211.6676558904758</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>4799.9560711212298</c:v>
+                  <c:v>1228.0552254538218</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>4862.028367922223</c:v>
+                  <c:v>1244.2273748606688</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>4923.3194555641685</c:v>
+                  <c:v>1260.1923672341861</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>4983.8580592564149</c:v>
+                  <c:v>1275.9579515114885</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5043.6711887027705</c:v>
+                  <c:v>1291.5314060731457</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>5102.7842779625489</c:v>
+                  <c:v>1306.9195777338398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3207,11 +3200,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="205602176"/>
-        <c:axId val="205617024"/>
+        <c:axId val="-1409089856"/>
+        <c:axId val="-1409089312"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="205602176"/>
+        <c:axId val="-1409089856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3267,12 +3260,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205617024"/>
+        <c:crossAx val="-1409089312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="205617024"/>
+        <c:axId val="-1409089312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3292,7 +3285,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* &quot;-&quot;?\ _₽_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_-* #\ ##0.0\ _₽_-;\-* #\ ##0.0\ _₽_-;_-* &quot;-&quot;?\ _₽_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3329,7 +3322,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="205602176"/>
+        <c:crossAx val="-1409089856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5696,16 +5689,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>594180</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>175078</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>26529</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>434851</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>303894</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>15421</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>342380</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>25043</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6260,7 +6253,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6269,54 +6262,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R345"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" customWidth="1"/>
-    <col min="3" max="4" width="12.21875" customWidth="1"/>
-    <col min="8" max="8" width="7.88671875" customWidth="1"/>
-    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" customWidth="1"/>
-    <col min="11" max="11" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -6324,1657 +6321,1764 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="15">
-        <f t="shared" ref="F2:F3" si="0">$B$12/J2</f>
-        <v>75</v>
-      </c>
-      <c r="G2" s="21">
-        <f>$B$12/J2</f>
-        <v>75</v>
-      </c>
-      <c r="H2" s="12">
-        <f>ROUND(G2,0)</f>
-        <v>75</v>
-      </c>
-      <c r="J2" s="14">
-        <v>400</v>
-      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="12"/>
+      <c r="J2" s="14"/>
       <c r="K2" s="4"/>
       <c r="L2" t="str">
-        <f t="shared" ref="L2:L48" si="1">CONCATENATE("0x",DEC2HEX(G2*POWER(2,24),8),",")</f>
-        <v>0x4B000000,</v>
-      </c>
-      <c r="M2" s="19">
-        <f t="shared" ref="M2:M48" si="2">$B$12/G2</f>
-        <v>400</v>
+        <f t="shared" ref="L2:L48" si="0">CONCATENATE("0x",DEC2HEX(G2*POWER(2,24),8),",")</f>
+        <v>0x00000000,</v>
+      </c>
+      <c r="M2" s="19"/>
+      <c r="N2">
+        <f>10/0.00625</f>
+        <v>1600</v>
       </c>
       <c r="O2" s="17"/>
     </row>
-    <row r="3" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B3" s="7">
         <v>72000000</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3">
-        <f t="shared" ref="D3:D5" si="3">G2-G3</f>
-        <v>9.7826086956521721</v>
+        <f t="shared" ref="D3:D5" si="1">G2-G3</f>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="15"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="13"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K5" si="2">J3-J2</f>
+        <v>0</v>
+      </c>
+      <c r="L3" t="str">
         <f t="shared" si="0"/>
-        <v>65.217391304347828</v>
-      </c>
-      <c r="G3" s="21">
-        <f>$B$12/J3</f>
-        <v>65.217391304347828</v>
-      </c>
-      <c r="H3" s="13">
-        <f>ROUND(G3,0)</f>
-        <v>65</v>
-      </c>
-      <c r="J3" s="14">
-        <v>460</v>
-      </c>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:K5" si="4">J3-J2</f>
-        <v>60</v>
-      </c>
-      <c r="L3" t="str">
-        <f t="shared" si="1"/>
-        <v>0x4137A6F4,</v>
-      </c>
-      <c r="M3" s="19">
-        <f t="shared" si="2"/>
-        <v>460</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <v>0x00000000,</v>
+      </c>
+      <c r="M3" s="19"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="D4" s="3">
-        <f t="shared" si="3"/>
-        <v>15.217391304347828</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="15">
-        <f>$B$12/J4</f>
-        <v>45.454545454545453</v>
-      </c>
-      <c r="G4" s="21">
-        <v>50</v>
-      </c>
-      <c r="H4" s="13">
-        <f>ROUND(G4,0)</f>
-        <v>50</v>
-      </c>
-      <c r="J4" s="14">
-        <v>660</v>
-      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="13"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="4">
-        <f t="shared" si="4"/>
-        <v>200</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>0x00000000,</v>
+      </c>
+      <c r="M4" s="19"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>0x32000000,</v>
-      </c>
-      <c r="M4" s="19">
-        <f t="shared" si="2"/>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="D5" s="3">
-        <f t="shared" si="3"/>
-        <v>16.511265668843144</v>
+        <v>-1436.7394278317272</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" s="15">
         <f>B17</f>
-        <v>33.488734331156856</v>
+        <v>1436.7394278317272</v>
       </c>
       <c r="G5" s="21">
         <f>B17</f>
-        <v>33.488734331156856</v>
+        <v>1436.7394278317272</v>
       </c>
       <c r="H5" s="8">
         <f>ROUND(G5,0)</f>
-        <v>33</v>
+        <v>1437</v>
       </c>
       <c r="J5" s="4">
-        <f t="shared" ref="J5:J35" si="5">$B$12/H5</f>
-        <v>909.09090909090912</v>
+        <f t="shared" ref="J4:J35" si="3">$B$12/H5</f>
+        <v>208.76826722338205</v>
       </c>
       <c r="K5" s="4">
-        <f t="shared" si="4"/>
-        <v>249.09090909090912</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" si="1"/>
-        <v>0x217D1DB1,</v>
+        <f t="shared" si="2"/>
+        <v>208.76826722338205</v>
+      </c>
+      <c r="L5" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M5" s="19">
-        <f t="shared" si="2"/>
-        <v>895.82364335844579</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" ref="M2:M48" si="4">$B$12/G5</f>
+        <v>208.80613017821099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="D6" s="3">
         <f>G5-G6</f>
-        <v>5.4990672148287985</v>
+        <v>205.57672143034574</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" s="15">
-        <f t="shared" ref="F6:F35" si="6">F5*(1+-1*$B$22*F5*F5)</f>
-        <v>20.969581310163637</v>
+        <f t="shared" ref="F6:F35" si="5">F5*(1+-1*$B$22*F5*F5)</f>
+        <v>777.68464442267782</v>
       </c>
       <c r="G6" s="21">
-        <f t="shared" ref="G6:G48" si="7">G5*(1+I6+1.5*I6*I6)</f>
-        <v>27.989667116328057</v>
+        <f t="shared" ref="G6:G48" si="6">G5*(1+I6+1.5*I6*I6)</f>
+        <v>1231.1627064013815</v>
       </c>
       <c r="H6" s="8">
-        <f t="shared" ref="H6:H35" si="8">ROUND(G6,0)</f>
-        <v>28</v>
+        <f t="shared" ref="H6:H35" si="7">ROUND(G6,0)</f>
+        <v>1231</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" ref="I6:I48" si="9">-1*$B$22*G5*G5</f>
-        <v>-0.37383177570093457</v>
+        <f t="shared" ref="I6:I48" si="8">-1*$B$22*G5*G5</f>
+        <v>-0.45871559633027531</v>
       </c>
       <c r="J6" s="4">
-        <f t="shared" si="5"/>
-        <v>1071.4285714285713</v>
+        <f t="shared" si="3"/>
+        <v>243.70430544272949</v>
       </c>
       <c r="K6" s="4">
         <f>J6-J5</f>
-        <v>162.33766233766221</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="1"/>
-        <v>0x1BFD5AD2,</v>
+        <v>34.936038219347438</v>
+      </c>
+      <c r="L6" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M6" s="19">
-        <f t="shared" si="2"/>
-        <v>1071.8241083510134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>243.67209828576023</v>
+      </c>
+      <c r="N6">
+        <f t="shared" ref="N6:N44" si="9">I6*65536</f>
+        <v>-30062.385321100923</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5">
         <f>((((72000000)/((B6)/(1/B12)))+0.5)-1)</f>
-        <v>2399.5</v>
+        <v>239.5</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" ref="D7:D37" si="10">G6-G7</f>
-        <v>4.4461294109445646</v>
+        <v>205.17112842206325</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" s="15">
+        <f t="shared" si="5"/>
+        <v>673.16496774998018</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="6"/>
-        <v>17.895976530533058</v>
-      </c>
-      <c r="G7" s="21">
+        <v>1025.9915779793182</v>
+      </c>
+      <c r="H7" s="8">
         <f t="shared" si="7"/>
-        <v>23.543537705383493</v>
-      </c>
-      <c r="H7" s="8">
+        <v>1026</v>
+      </c>
+      <c r="I7" s="2">
         <f t="shared" si="8"/>
-        <v>24</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.26114048842761872</v>
+        <v>-0.33683591325190537</v>
       </c>
       <c r="J7" s="4">
-        <f t="shared" si="5"/>
-        <v>1250</v>
+        <f t="shared" si="3"/>
+        <v>292.39766081871346</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" ref="K7:K35" si="11">J7-J6</f>
-        <v>178.57142857142867</v>
-      </c>
-      <c r="L7" t="str">
-        <f t="shared" si="1"/>
-        <v>0x178B2549,</v>
+        <v>48.69335537598397</v>
+      </c>
+      <c r="L7" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M7" s="19">
-        <f t="shared" si="2"/>
-        <v>1274.2350098532629</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>292.40006101302259</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="9"/>
+        <v>-22074.87841087687</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" si="10"/>
-        <v>3.1444351727675723</v>
+        <v>155.79004026137954</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" s="15">
+        <f t="shared" si="5"/>
+        <v>605.37709486456424</v>
+      </c>
+      <c r="G8" s="21">
         <f t="shared" si="6"/>
-        <v>15.985485733969318</v>
-      </c>
-      <c r="G8" s="21">
+        <v>870.20153771793866</v>
+      </c>
+      <c r="H8" s="8">
         <f t="shared" si="7"/>
-        <v>20.39910253261592</v>
-      </c>
-      <c r="H8" s="8">
+        <v>870</v>
+      </c>
+      <c r="I8" s="2">
         <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="I8" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.18476605589493808</v>
+        <v>-0.23392415957433141</v>
       </c>
       <c r="J8" s="4">
-        <f t="shared" si="5"/>
-        <v>1500</v>
+        <f t="shared" si="3"/>
+        <v>344.82758620689657</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="11"/>
-        <v>250</v>
-      </c>
-      <c r="L8" t="str">
-        <f t="shared" si="1"/>
-        <v>0x14662B95,</v>
+        <v>52.429925388183108</v>
+      </c>
+      <c r="L8" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M8" s="19">
-        <f t="shared" si="2"/>
-        <v>1470.6529344628423</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>344.74772451762777</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="9"/>
+        <v>-15330.453721863383</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>146</v>
       </c>
       <c r="B9">
         <f>B1+50</f>
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" si="10"/>
-        <v>2.2408009463094096</v>
+        <v>109.47286833583769</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" s="15">
+        <f t="shared" si="5"/>
+        <v>556.07499228878555</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="6"/>
-        <v>14.623864683136356</v>
-      </c>
-      <c r="G9" s="21">
+        <v>760.72866938210097</v>
+      </c>
+      <c r="H9" s="8">
         <f t="shared" si="7"/>
-        <v>18.158301586306511</v>
-      </c>
-      <c r="H9" s="8">
+        <v>761</v>
+      </c>
+      <c r="I9" s="2">
         <f t="shared" si="8"/>
-        <v>18</v>
-      </c>
-      <c r="I9" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.13870779471205907</v>
+        <v>-0.16827793694370333</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" si="5"/>
-        <v>1666.6666666666667</v>
+        <f t="shared" si="3"/>
+        <v>394.21813403416559</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="11"/>
-        <v>166.66666666666674</v>
-      </c>
-      <c r="L9" t="str">
-        <f t="shared" si="1"/>
-        <v>0x12288673,</v>
+        <v>49.390547827269017</v>
+      </c>
+      <c r="L9" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M9" s="19">
-        <f t="shared" si="2"/>
-        <v>1652.1368949298385</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>394.35874060546962</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="9"/>
+        <v>-11028.262875542541</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="B10">
         <f>B2</f>
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" si="10"/>
-        <v>1.6667201536901075</v>
+        <v>78.959198326622186</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" s="15">
+        <f t="shared" si="5"/>
+        <v>517.86406477110768</v>
+      </c>
+      <c r="G10" s="21">
         <f t="shared" si="6"/>
-        <v>13.581390701044569</v>
-      </c>
-      <c r="G10" s="21">
+        <v>681.76947105547879</v>
+      </c>
+      <c r="H10" s="8">
         <f t="shared" si="7"/>
-        <v>16.491581432616403</v>
-      </c>
-      <c r="H10" s="8">
+        <v>682</v>
+      </c>
+      <c r="I10" s="2">
         <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
-      <c r="I10" s="2">
-        <f t="shared" si="9"/>
-        <v>-0.10990797216642051</v>
+        <v>-0.12860180187108042</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="5"/>
-        <v>1875</v>
+        <f t="shared" si="3"/>
+        <v>439.88269794721407</v>
       </c>
       <c r="K10" s="4">
         <f t="shared" si="11"/>
-        <v>208.33333333333326</v>
-      </c>
-      <c r="L10" t="str">
-        <f t="shared" si="1"/>
-        <v>0x107DD847,</v>
+        <v>45.664563913048482</v>
+      </c>
+      <c r="L10" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M10" s="19">
-        <f t="shared" si="2"/>
-        <v>1819.1099575609635</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>440.03143692479534</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="9"/>
+        <v>-8428.0476874231263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="7">
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" si="10"/>
-        <v>1.2917734992911409</v>
+        <v>59.509933003902347</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" s="15">
+        <f t="shared" si="5"/>
+        <v>487.00130106892351</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="6"/>
-        <v>12.746342636032498</v>
-      </c>
-      <c r="G11" s="21">
+        <v>622.25953805157644</v>
+      </c>
+      <c r="H11" s="8">
         <f t="shared" si="7"/>
-        <v>15.199807933325262</v>
-      </c>
-      <c r="H11" s="8">
+        <v>622</v>
+      </c>
+      <c r="I11" s="2">
         <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="I11" s="2">
-        <f t="shared" si="9"/>
-        <v>-9.0657419382872695E-2</v>
+        <v>-0.1032910248140594</v>
       </c>
       <c r="J11" s="4">
-        <f t="shared" si="5"/>
-        <v>2000</v>
+        <f t="shared" si="3"/>
+        <v>482.3151125401929</v>
       </c>
       <c r="K11" s="4">
         <f t="shared" si="11"/>
-        <v>125</v>
-      </c>
-      <c r="L11" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0F33269C,</v>
+        <v>42.43241459297883</v>
+      </c>
+      <c r="L11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M11" s="19">
-        <f t="shared" si="2"/>
-        <v>1973.7091502469334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>482.11394386876282</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="9"/>
+        <v>-6769.2806022141967</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" s="6">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" si="10"/>
-        <v>1.0353388155565497</v>
+        <v>46.632203040454669</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" s="15">
+        <f t="shared" si="5"/>
+        <v>461.33413913067466</v>
+      </c>
+      <c r="G12" s="21">
         <f t="shared" si="6"/>
-        <v>12.056046390730806</v>
-      </c>
-      <c r="G12" s="21">
+        <v>575.62733501112177</v>
+      </c>
+      <c r="H12" s="8">
         <f t="shared" si="7"/>
-        <v>14.164469117768713</v>
-      </c>
-      <c r="H12" s="8">
+        <v>576</v>
+      </c>
+      <c r="I12" s="2">
         <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="I12" s="2">
-        <f t="shared" si="9"/>
-        <v>-7.7011387069992526E-2</v>
+        <v>-8.60459850435914E-2</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="5"/>
-        <v>2142.8571428571427</v>
+        <f t="shared" si="3"/>
+        <v>520.83333333333337</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="11"/>
-        <v>142.85714285714266</v>
-      </c>
-      <c r="L12" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0E2A1AA5,</v>
+        <v>38.518220793140472</v>
+      </c>
+      <c r="L12" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M12" s="19">
-        <f t="shared" si="2"/>
-        <v>2117.9756015258135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>521.17052431883496</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="9"/>
+        <v>-5639.109675816806</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" si="10"/>
-        <v>0.85225508901687874</v>
+        <v>37.703580443185047</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13" s="15">
+        <f t="shared" si="5"/>
+        <v>439.51516797636657</v>
+      </c>
+      <c r="G13" s="21">
         <f t="shared" si="6"/>
-        <v>11.471937957406334</v>
-      </c>
-      <c r="G13" s="21">
+        <v>537.92375456793673</v>
+      </c>
+      <c r="H13" s="8">
         <f t="shared" si="7"/>
-        <v>13.312214028751834</v>
-      </c>
-      <c r="H13" s="8">
+        <v>538</v>
+      </c>
+      <c r="I13" s="2">
         <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="I13" s="2">
-        <f t="shared" si="9"/>
-        <v>-6.6877395129407852E-2</v>
+        <v>-7.363262862489027E-2</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" si="5"/>
-        <v>2307.6923076923076</v>
+        <f t="shared" si="3"/>
+        <v>557.62081784386612</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="11"/>
-        <v>164.83516483516496</v>
-      </c>
-      <c r="L13" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0D4FED42,</v>
+        <v>36.787484510532749</v>
+      </c>
+      <c r="L13" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M13" s="19">
-        <f t="shared" si="2"/>
-        <v>2253.5695366079408</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>557.69985514203893</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="9"/>
+        <v>-4825.5879495608087</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" si="10"/>
-        <v>0.71669613076740291</v>
+        <v>31.253591285839605</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14" s="15">
+        <f t="shared" si="5"/>
+        <v>420.64789692555138</v>
+      </c>
+      <c r="G14" s="21">
         <f t="shared" si="6"/>
-        <v>10.9686817805724</v>
-      </c>
-      <c r="G14" s="21">
+        <v>506.67016328209712</v>
+      </c>
+      <c r="H14" s="8">
         <f t="shared" si="7"/>
-        <v>12.595517897984431</v>
-      </c>
-      <c r="H14" s="8">
+        <v>507</v>
+      </c>
+      <c r="I14" s="2">
         <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="I14" s="2">
-        <f t="shared" si="9"/>
-        <v>-5.907168078243237E-2</v>
+        <v>-6.4302659050770178E-2</v>
       </c>
       <c r="J14" s="4">
-        <f t="shared" si="5"/>
-        <v>2307.6923076923076</v>
+        <f t="shared" si="3"/>
+        <v>591.71597633136093</v>
       </c>
       <c r="K14" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L14" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0C9873DC,</v>
+        <v>34.095158487494814</v>
+      </c>
+      <c r="L14" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M14" s="19">
-        <f t="shared" si="2"/>
-        <v>2381.7996403943566</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>592.10117694056908</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="9"/>
+        <v>-4214.1390635512744</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4">
         <f>(B10*B10-B9*B9)/(2*B11)</f>
-        <v>59.662500000000001</v>
+        <v>99.91</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="10"/>
-        <v>0.61324480050316943</v>
+        <v>26.430976354279949</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15" s="15">
+        <f t="shared" si="5"/>
+        <v>404.10758665094988</v>
+      </c>
+      <c r="G15" s="21">
         <f t="shared" si="6"/>
-        <v>10.528793839556215</v>
-      </c>
-      <c r="G15" s="21">
+        <v>480.23918692781717</v>
+      </c>
+      <c r="H15" s="8">
         <f t="shared" si="7"/>
-        <v>11.982273097481261</v>
-      </c>
-      <c r="H15" s="8">
+        <v>480</v>
+      </c>
+      <c r="I15" s="2">
         <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="I15" s="2">
-        <f t="shared" si="9"/>
-        <v>-5.2882357039482041E-2</v>
+        <v>-5.7047700968957102E-2</v>
       </c>
       <c r="J15" s="4">
-        <f t="shared" si="5"/>
-        <v>2500</v>
+        <f t="shared" si="3"/>
+        <v>625</v>
       </c>
       <c r="K15" s="4">
         <f t="shared" si="11"/>
-        <v>192.30769230769238</v>
-      </c>
-      <c r="L15" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0BFB763F,</v>
+        <v>33.284023668639065</v>
+      </c>
+      <c r="L15" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M15" s="19">
-        <f t="shared" si="2"/>
-        <v>2503.6985683714856</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>624.68871380354847</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="9"/>
+        <v>-3738.6781307015726</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="D16" s="3">
         <f t="shared" si="10"/>
-        <v>0.53228451228874363</v>
+        <v>22.720613327116041</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16" s="15">
+        <f t="shared" si="5"/>
+        <v>389.44270718017805</v>
+      </c>
+      <c r="G16" s="21">
         <f t="shared" si="6"/>
-        <v>10.139735605393065</v>
-      </c>
-      <c r="G16" s="21">
+        <v>457.51857360070113</v>
+      </c>
+      <c r="H16" s="8">
         <f t="shared" si="7"/>
-        <v>11.449988585192518</v>
-      </c>
-      <c r="H16" s="8">
+        <v>458</v>
+      </c>
+      <c r="I16" s="2">
         <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
-      <c r="I16" s="2">
-        <f t="shared" si="9"/>
-        <v>-4.7858289527541058E-2</v>
+        <v>-5.1251039258020201E-2</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="5"/>
-        <v>2727.2727272727275</v>
+        <f t="shared" si="3"/>
+        <v>655.02183406113534</v>
       </c>
       <c r="K16" s="4">
         <f t="shared" si="11"/>
-        <v>227.27272727272748</v>
-      </c>
-      <c r="L16" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0B733273,</v>
+        <v>30.021834061135337</v>
+      </c>
+      <c r="L16" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M16" s="19">
-        <f t="shared" si="2"/>
-        <v>2620.0899482814275</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>655.71108433692723</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="9"/>
+        <v>-3358.7881088136119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B17" s="3">
         <f>B12/SQRT(B9*B9+2*B11)</f>
-        <v>33.488734331156856</v>
+        <v>1436.7394278317272</v>
       </c>
       <c r="D17" s="3">
         <f t="shared" si="10"/>
-        <v>0.46757303198042166</v>
+        <v>19.797117241484102</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17" s="15">
+        <f t="shared" si="5"/>
+        <v>376.31713596099593</v>
+      </c>
+      <c r="G17" s="21">
         <f t="shared" si="6"/>
-        <v>9.7922325416319662</v>
-      </c>
-      <c r="G17" s="21">
+        <v>437.72145635921703</v>
+      </c>
+      <c r="H17" s="8">
         <f t="shared" si="7"/>
-        <v>10.982415553212096</v>
-      </c>
-      <c r="H17" s="8">
+        <v>438</v>
+      </c>
+      <c r="I17" s="2">
         <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
-      <c r="I17" s="2">
-        <f t="shared" si="9"/>
-        <v>-4.3700746200346315E-2</v>
+        <v>-4.6516276708804483E-2</v>
       </c>
       <c r="J17" s="4">
-        <f t="shared" si="5"/>
-        <v>2727.2727272727275</v>
+        <f t="shared" si="3"/>
+        <v>684.93150684931504</v>
       </c>
       <c r="K17" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L17" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0AFB7F95,</v>
+        <v>29.909672788179705</v>
+      </c>
+      <c r="L17" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M17" s="19">
-        <f t="shared" si="2"/>
-        <v>2731.6394881111296</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>685.36736237531932</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="9"/>
+        <v>-3048.4907103882106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D18" s="3">
         <f t="shared" si="10"/>
-        <v>0.41491437486318716</v>
+        <v>17.446916841026166</v>
       </c>
       <c r="E18">
         <v>17</v>
       </c>
       <c r="F18" s="15">
+        <f t="shared" si="5"/>
+        <v>364.47447024508324</v>
+      </c>
+      <c r="G18" s="21">
         <f t="shared" si="6"/>
-        <v>9.4792472705557635</v>
-      </c>
-      <c r="G18" s="21">
+        <v>420.27453951819086</v>
+      </c>
+      <c r="H18" s="8">
         <f t="shared" si="7"/>
-        <v>10.567501178348909</v>
-      </c>
-      <c r="H18" s="8">
+        <v>420</v>
+      </c>
+      <c r="I18" s="2">
         <f t="shared" si="8"/>
-        <v>11</v>
-      </c>
-      <c r="I18" s="2">
-        <f t="shared" si="9"/>
-        <v>-4.0204483794478316E-2</v>
+        <v>-4.257779407938532E-2</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" si="5"/>
-        <v>2727.2727272727275</v>
+        <f t="shared" si="3"/>
+        <v>714.28571428571433</v>
       </c>
       <c r="K18" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L18" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0A9147C1,</v>
+        <v>29.354207436399292</v>
+      </c>
+      <c r="L18" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M18" s="19">
-        <f t="shared" si="2"/>
-        <v>2838.892515239565</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>713.81911534285325</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="9"/>
+        <v>-2790.3783127865963</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="3">
         <f t="shared" si="10"/>
-        <v>0.37140100843455137</v>
+        <v>15.525055603926319</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19" s="15">
+        <f t="shared" si="5"/>
+        <v>353.71505109645437</v>
+      </c>
+      <c r="G19" s="21">
         <f t="shared" si="6"/>
-        <v>9.1953244492807684</v>
-      </c>
-      <c r="G19" s="21">
+        <v>404.74948391426454</v>
+      </c>
+      <c r="H19" s="8">
         <f t="shared" si="7"/>
-        <v>10.196100169914358</v>
-      </c>
-      <c r="H19" s="8">
+        <v>405</v>
+      </c>
+      <c r="I19" s="2">
         <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="I19" s="2">
-        <f t="shared" si="9"/>
-        <v>-3.7224027051468524E-2</v>
+        <v>-3.9251264126050532E-2</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" si="5"/>
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>740.74074074074076</v>
       </c>
       <c r="K19" s="4">
         <f t="shared" si="11"/>
-        <v>272.72727272727252</v>
-      </c>
-      <c r="L19" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0A32339E,</v>
+        <v>26.455026455026427</v>
+      </c>
+      <c r="L19" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M19" s="19">
-        <f t="shared" si="2"/>
-        <v>2942.3014191760326</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>741.19921562036393</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="9"/>
+        <v>-2572.3708457648477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20" s="3">
         <f>B12/B10</f>
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="D20" s="3">
         <f t="shared" si="10"/>
-        <v>0.33496422069013221</v>
+        <v>13.930240174488176</v>
       </c>
       <c r="E20">
         <v>19</v>
       </c>
       <c r="F20" s="15">
+        <f t="shared" si="5"/>
+        <v>343.88064571056657</v>
+      </c>
+      <c r="G20" s="21">
         <f t="shared" si="6"/>
-        <v>8.9361573201419233</v>
-      </c>
-      <c r="G20" s="21">
+        <v>390.81924373977637</v>
+      </c>
+      <c r="H20" s="8">
         <f t="shared" si="7"/>
-        <v>9.8611359492242254</v>
-      </c>
-      <c r="H20" s="8">
+        <v>391</v>
+      </c>
+      <c r="I20" s="2">
         <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="I20" s="2">
-        <f t="shared" si="9"/>
-        <v>-3.4653486224975862E-2</v>
+        <v>-3.6404921050858553E-2</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" si="5"/>
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>767.26342710997437</v>
       </c>
       <c r="K20" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L20" t="str">
-        <f t="shared" si="1"/>
-        <v>0x09DC7367,</v>
+        <v>26.522686369233611</v>
+      </c>
+      <c r="L20" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M20" s="19">
-        <f t="shared" si="2"/>
-        <v>3042.2458583344142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>767.61829107819574</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="9"/>
+        <v>-2385.8329059890661</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D21" s="3">
         <f t="shared" si="10"/>
-        <v>0.30409770616933862</v>
+        <v>12.589869460146701</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21" s="15">
+        <f t="shared" si="5"/>
+        <v>334.84392860567385</v>
+      </c>
+      <c r="G21" s="21">
         <f t="shared" si="6"/>
-        <v>8.6982919809590182</v>
-      </c>
-      <c r="G21" s="21">
+        <v>378.22937427962967</v>
+      </c>
+      <c r="H21" s="8">
         <f t="shared" si="7"/>
-        <v>9.5570382430548868</v>
-      </c>
-      <c r="H21" s="8">
+        <v>378</v>
+      </c>
+      <c r="I21" s="2">
         <f t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="I21" s="2">
-        <f t="shared" si="9"/>
-        <v>-3.241400073636079E-2</v>
+        <v>-3.3942151394962386E-2</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="5"/>
-        <v>3000</v>
+        <f t="shared" si="3"/>
+        <v>793.65079365079362</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L21" t="str">
-        <f t="shared" si="1"/>
-        <v>0x098E9A0E,</v>
+        <v>26.387366540819244</v>
+      </c>
+      <c r="L21" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M21" s="19">
-        <f t="shared" si="2"/>
-        <v>3139.0478134584259</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>793.16949026335078</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="9"/>
+        <v>-2224.4328338202549</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22">
+        <v>23</v>
+      </c>
+      <c r="B22" s="39">
         <f>B11/(B12*B12)</f>
-        <v>3.3333333333333332E-4</v>
+        <v>2.2222222222222222E-7</v>
       </c>
       <c r="D22" s="3">
         <f t="shared" si="10"/>
-        <v>0.27768216097134868</v>
+        <v>11.450738586924558</v>
       </c>
       <c r="E22">
         <v>21</v>
       </c>
       <c r="F22" s="15">
+        <f t="shared" si="5"/>
+        <v>326.5010721302105</v>
+      </c>
+      <c r="G22" s="21">
         <f t="shared" si="6"/>
-        <v>8.4789202355411284</v>
-      </c>
-      <c r="G22" s="21">
+        <v>366.77863569270511</v>
+      </c>
+      <c r="H22" s="8">
         <f t="shared" si="7"/>
-        <v>9.2793560820835381</v>
-      </c>
-      <c r="H22" s="8">
+        <v>367</v>
+      </c>
+      <c r="I22" s="2">
         <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="I22" s="2">
-        <f t="shared" si="9"/>
-        <v>-3.0445659993071212E-2</v>
+        <v>-3.1790546570657816E-2</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" si="5"/>
-        <v>3333.3333333333335</v>
+        <f t="shared" si="3"/>
+        <v>817.43869209809259</v>
       </c>
       <c r="K22" s="4">
         <f t="shared" si="11"/>
-        <v>333.33333333333348</v>
-      </c>
-      <c r="L22" t="str">
-        <f t="shared" si="1"/>
-        <v>0x094783E1,</v>
+        <v>23.787898447298971</v>
+      </c>
+      <c r="L22" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M22" s="19">
-        <f t="shared" si="2"/>
-        <v>3232.9829499617563</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>817.93204621478105</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="9"/>
+        <v>-2083.4252600546306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D23" s="3">
         <f t="shared" si="10"/>
-        <v>0.25487078115803996</v>
+        <v>10.473086967590746</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="F23" s="15">
+        <f t="shared" si="5"/>
+        <v>318.76641046340961</v>
+      </c>
+      <c r="G23" s="21">
         <f t="shared" si="6"/>
-        <v>8.2757311412822663</v>
-      </c>
-      <c r="G23" s="21">
+        <v>356.30554872511436</v>
+      </c>
+      <c r="H23" s="8">
         <f t="shared" si="7"/>
-        <v>9.0244853009254982</v>
-      </c>
-      <c r="H23" s="8">
+        <v>356</v>
+      </c>
+      <c r="I23" s="2">
         <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="I23" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.870214976603358E-2</v>
+        <v>-2.9894792800133799E-2</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="5"/>
-        <v>3333.3333333333335</v>
+        <f t="shared" si="3"/>
+        <v>842.69662921348311</v>
       </c>
       <c r="K23" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L23" t="str">
-        <f t="shared" si="1"/>
-        <v>0x090644AB,</v>
+        <v>25.257937115390519</v>
+      </c>
+      <c r="L23" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M23" s="19">
-        <f t="shared" si="2"/>
-        <v>3324.2893084355046</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>841.97397731643673</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="9"/>
+        <v>-1959.1851409495687</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" si="10"/>
-        <v>0.23501260624167664</v>
+        <v>9.6266819071818759</v>
       </c>
       <c r="E24">
         <v>23</v>
       </c>
       <c r="F24" s="15">
+        <f t="shared" si="5"/>
+        <v>311.56852150994916</v>
+      </c>
+      <c r="G24" s="21">
         <f t="shared" si="6"/>
-        <v>8.0868024725439884</v>
-      </c>
-      <c r="G24" s="21">
+        <v>346.67886681793249</v>
+      </c>
+      <c r="H24" s="8">
         <f t="shared" si="7"/>
-        <v>8.7894726946838215</v>
-      </c>
-      <c r="H24" s="8">
+        <v>347</v>
+      </c>
+      <c r="I24" s="2">
         <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="I24" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.7147111648873457E-2</v>
+        <v>-2.8211920900512191E-2</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="5"/>
-        <v>3333.3333333333335</v>
+        <f t="shared" si="3"/>
+        <v>864.55331412103749</v>
       </c>
       <c r="K24" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L24" t="str">
-        <f t="shared" si="1"/>
-        <v>0x08CA1AE1,</v>
+        <v>21.856684907554381</v>
+      </c>
+      <c r="L24" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M24" s="19">
-        <f t="shared" si="2"/>
-        <v>3413.1740369527561</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>865.35416119711988</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="9"/>
+        <v>-1848.8964481359669</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3">
         <f t="shared" si="10"/>
-        <v>0.21760002580582238</v>
+        <v>8.8881779179167211</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25" s="15">
+        <f t="shared" si="5"/>
+        <v>304.84730003176361</v>
+      </c>
+      <c r="G25" s="21">
         <f t="shared" si="6"/>
-        <v>7.9105199522712821</v>
-      </c>
-      <c r="G25" s="21">
+        <v>337.79068890001577</v>
+      </c>
+      <c r="H25" s="8">
         <f t="shared" si="7"/>
-        <v>8.5718726688779991</v>
-      </c>
-      <c r="H25" s="8">
+        <v>338</v>
+      </c>
+      <c r="I25" s="2">
         <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="I25" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.5751610083530826E-2</v>
+        <v>-2.6708052599592396E-2</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="5"/>
-        <v>3333.3333333333335</v>
+        <f t="shared" si="3"/>
+        <v>887.5739644970414</v>
       </c>
       <c r="K25" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L25" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0892663F,</v>
+        <v>23.020650376003914</v>
+      </c>
+      <c r="L25" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M25" s="19">
-        <f t="shared" si="2"/>
-        <v>3499.8186696031266</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>888.12394733828319</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="9"/>
+        <v>-1750.3389351668873</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D26" s="3">
         <f t="shared" si="10"/>
-        <v>0.20223209512087692</v>
+        <v>8.2392968210099298</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26" s="15">
+        <f t="shared" si="5"/>
+        <v>298.55173745662682</v>
+      </c>
+      <c r="G26" s="21">
         <f t="shared" si="6"/>
-        <v>7.745516194040392</v>
-      </c>
-      <c r="G26" s="21">
+        <v>329.55139207900584</v>
+      </c>
+      <c r="H26" s="8">
         <f t="shared" si="7"/>
-        <v>8.3696405737571222</v>
-      </c>
-      <c r="H26" s="8">
+        <v>330</v>
+      </c>
+      <c r="I26" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="I26" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.4492333683819211E-2</v>
+        <v>-2.5356122112788277E-2</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="5"/>
-        <v>3750</v>
+        <f t="shared" si="3"/>
+        <v>909.09090909090912</v>
       </c>
       <c r="K26" s="4">
         <f t="shared" si="11"/>
-        <v>416.66666666666652</v>
-      </c>
-      <c r="L26" t="str">
-        <f t="shared" si="1"/>
-        <v>0x085EA0C3,</v>
+        <v>21.51694459386772</v>
+      </c>
+      <c r="L26" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M26" s="19">
-        <f t="shared" si="2"/>
-        <v>3584.3833119984306</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>910.32842588654194</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="9"/>
+        <v>-1661.7388187836925</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="10"/>
-        <v>0.18858842462433145</v>
+        <v>7.6655485902668943</v>
       </c>
       <c r="E27">
         <v>26</v>
       </c>
       <c r="F27" s="15">
+        <f t="shared" si="5"/>
+        <v>292.63821439139014</v>
+      </c>
+      <c r="G27" s="21">
         <f t="shared" si="6"/>
-        <v>7.5906238885225576</v>
-      </c>
-      <c r="G27" s="21">
+        <v>321.88584348873894</v>
+      </c>
+      <c r="H27" s="8">
         <f t="shared" si="7"/>
-        <v>8.1810521491327908</v>
-      </c>
-      <c r="H27" s="8">
+        <v>322</v>
+      </c>
+      <c r="I27" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="I27" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.3350294444627148E-2</v>
+        <v>-2.4134248893602363E-2</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" si="5"/>
-        <v>3750</v>
+        <f t="shared" si="3"/>
+        <v>931.67701863354034</v>
       </c>
       <c r="K27" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L27" t="str">
-        <f t="shared" si="1"/>
-        <v>0x082E596F,</v>
+        <v>22.58610954263122</v>
+      </c>
+      <c r="L27" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M27" s="19">
-        <f t="shared" si="2"/>
-        <v>3667.0099949405731</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>932.00743701080285</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="9"/>
+        <v>-1581.6621354911244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D28" s="3">
         <f t="shared" si="10"/>
-        <v>0.17641028446371898</v>
+        <v>7.1553161456183716</v>
       </c>
       <c r="E28">
         <v>27</v>
       </c>
       <c r="F28" s="15">
+        <f t="shared" si="5"/>
+        <v>287.06917101232699</v>
+      </c>
+      <c r="G28" s="21">
         <f t="shared" si="6"/>
-        <v>7.4448394515357723</v>
-      </c>
-      <c r="G28" s="21">
+        <v>314.73052734312057</v>
+      </c>
+      <c r="H28" s="8">
         <f t="shared" si="7"/>
-        <v>8.0046418646690718</v>
-      </c>
-      <c r="H28" s="8">
+        <v>315</v>
+      </c>
+      <c r="I28" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="I28" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.230987142227675E-2</v>
+        <v>-2.3024554719657097E-2</v>
       </c>
       <c r="J28" s="4">
-        <f t="shared" si="5"/>
-        <v>3750</v>
+        <f t="shared" si="3"/>
+        <v>952.38095238095241</v>
       </c>
       <c r="K28" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L28" t="str">
-        <f t="shared" si="1"/>
-        <v>0x08013035,</v>
+        <v>20.703933747412066</v>
+      </c>
+      <c r="L28" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M28" s="19">
-        <f t="shared" si="2"/>
-        <v>3747.8253877183624</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="14.55" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>953.19638210035691</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="9"/>
+        <v>-1508.9372181074475</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D29" s="3">
         <f t="shared" si="10"/>
-        <v>0.16548672245198404</v>
+        <v>6.6991899047096126</v>
       </c>
       <c r="E29">
         <v>28</v>
       </c>
       <c r="F29" s="15">
+        <f t="shared" si="5"/>
+        <v>281.81205995427376</v>
+      </c>
+      <c r="G29" s="21">
         <f t="shared" si="6"/>
-        <v>7.3072944681864946</v>
-      </c>
-      <c r="G29" s="21">
+        <v>308.03133743841096</v>
+      </c>
+      <c r="H29" s="8">
         <f t="shared" si="7"/>
-        <v>7.8391551422170878</v>
-      </c>
-      <c r="H29" s="8">
+        <v>308</v>
+      </c>
+      <c r="I29" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="I29" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.135809712720425E-2</v>
+        <v>-2.2012289964817505E-2</v>
       </c>
       <c r="J29" s="4">
-        <f t="shared" si="5"/>
-        <v>3750</v>
+        <f t="shared" si="3"/>
+        <v>974.02597402597405</v>
       </c>
       <c r="K29" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L29" t="str">
-        <f t="shared" si="1"/>
-        <v>0x07D6D2DF,</v>
+        <v>21.645021645021643</v>
+      </c>
+      <c r="L29" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M29" s="19">
-        <f t="shared" si="2"/>
-        <v>3826.9430130853784</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>973.9268819036414</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="9"/>
+        <v>-1442.59743513428</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D30" s="3">
         <f t="shared" si="10"/>
-        <v>0.15564422379518028</v>
+        <v>6.2894767818793866</v>
       </c>
       <c r="E30">
         <v>29</v>
       </c>
       <c r="F30" s="15">
+        <f t="shared" si="5"/>
+        <v>276.83851314477852</v>
+      </c>
+      <c r="G30" s="21">
         <f t="shared" si="6"/>
-        <v>7.1772330240864832</v>
-      </c>
-      <c r="G30" s="21">
+        <v>301.74186065653157</v>
+      </c>
+      <c r="H30" s="8">
         <f t="shared" si="7"/>
-        <v>7.6835109184219075</v>
-      </c>
-      <c r="H30" s="8">
+        <v>302</v>
+      </c>
+      <c r="I30" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="I30" s="2">
-        <f t="shared" si="9"/>
-        <v>-2.0484117781249533E-2</v>
+        <v>-2.1085178854243599E-2</v>
       </c>
       <c r="J30" s="4">
-        <f t="shared" si="5"/>
-        <v>3750</v>
+        <f t="shared" si="3"/>
+        <v>993.37748344370857</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L30" t="str">
-        <f t="shared" si="1"/>
-        <v>0x07AEFA92,</v>
+        <v>19.351509417734519</v>
+      </c>
+      <c r="L30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M30" s="19">
-        <f t="shared" si="2"/>
-        <v>3904.4650705281497</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>994.22731518675721</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="9"/>
+        <v>-1381.8382813917085</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D31" s="3">
         <f t="shared" si="10"/>
-        <v>0.14673891116019799</v>
+        <v>5.9198330126387759</v>
       </c>
       <c r="E31">
         <v>30</v>
       </c>
       <c r="F31" s="15">
+        <f t="shared" si="5"/>
+        <v>272.12367259103019</v>
+      </c>
+      <c r="G31" s="21">
         <f t="shared" si="6"/>
-        <v>7.0539935360380976</v>
-      </c>
-      <c r="G31" s="21">
+        <v>295.8220276438928</v>
+      </c>
+      <c r="H31" s="8">
         <f t="shared" si="7"/>
-        <v>7.5367720072617095</v>
-      </c>
-      <c r="H31" s="8">
+        <v>296</v>
+      </c>
+      <c r="I31" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="I31" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.9678780011169555E-2</v>
+        <v>-2.0232922327214603E-2</v>
       </c>
       <c r="J31" s="4">
-        <f t="shared" si="5"/>
-        <v>3750</v>
+        <f t="shared" si="3"/>
+        <v>1013.5135135135135</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L31" t="str">
-        <f t="shared" si="1"/>
-        <v>0x078969E3,</v>
+        <v>20.136030069804974</v>
+      </c>
+      <c r="L31" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M31" s="19">
-        <f t="shared" si="2"/>
-        <v>3980.4839487110507</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>1014.1232631977515</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="9"/>
+        <v>-1325.9847976363362</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="10"/>
-        <v>0.13865059234562516</v>
+        <v>5.5849861790651403</v>
       </c>
       <c r="E32">
         <v>31</v>
       </c>
       <c r="F32" s="15">
+        <f t="shared" si="5"/>
+        <v>267.64564817737192</v>
+      </c>
+      <c r="G32" s="21">
         <f t="shared" si="6"/>
-        <v>6.9369940598562074</v>
-      </c>
-      <c r="G32" s="21">
+        <v>290.23704146482766</v>
+      </c>
+      <c r="H32" s="8">
         <f t="shared" si="7"/>
-        <v>7.3981214149160843</v>
-      </c>
-      <c r="H32" s="8">
+        <v>290</v>
+      </c>
+      <c r="I32" s="2">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="I32" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.8934310763147898E-2</v>
+        <v>-1.9446816008743126E-2</v>
       </c>
       <c r="J32" s="4">
-        <f t="shared" si="5"/>
-        <v>4285.7142857142853</v>
+        <f t="shared" si="3"/>
+        <v>1034.4827586206898</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="11"/>
-        <v>535.71428571428532</v>
-      </c>
-      <c r="L32" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0765EB48,</v>
+        <v>20.969245107176221</v>
+      </c>
+      <c r="L32" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M32" s="19">
-        <f t="shared" si="2"/>
-        <v>4055.0834891022514</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>1033.6378791828179</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="9"/>
+        <v>-1274.4665339489895</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D33" s="3">
         <f t="shared" si="10"/>
-        <v>0.1312781690654905</v>
+        <v>5.2805223715411671</v>
       </c>
       <c r="E33">
         <v>32</v>
       </c>
       <c r="F33" s="15">
+        <f t="shared" si="5"/>
+        <v>263.38507484092469</v>
+      </c>
+      <c r="G33" s="21">
         <f t="shared" si="6"/>
-        <v>6.8257203127230452</v>
-      </c>
-      <c r="G33" s="21">
+        <v>284.95651909328649</v>
+      </c>
+      <c r="H33" s="8">
         <f t="shared" si="7"/>
-        <v>7.2668432458505938</v>
-      </c>
-      <c r="H33" s="8">
+        <v>285</v>
+      </c>
+      <c r="I33" s="2">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="I33" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.8244066823279989E-2</v>
+        <v>-1.8719453386279131E-2</v>
       </c>
       <c r="J33" s="4">
-        <f t="shared" si="5"/>
-        <v>4285.7142857142853</v>
+        <f t="shared" si="3"/>
+        <v>1052.6315789473683</v>
       </c>
       <c r="K33" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L33" t="str">
-        <f t="shared" si="1"/>
-        <v>0x07444FD6,</v>
+        <v>18.14882032667856</v>
+      </c>
+      <c r="L33" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M33" s="19">
-        <f t="shared" si="2"/>
-        <v>4128.3400487729195</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>1052.7921977520673</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="9"/>
+        <v>-1226.7980971231891</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D34" s="3">
         <f t="shared" si="10"/>
-        <v>0.12453606040121379</v>
+        <v>5.0027215133420668</v>
       </c>
       <c r="E34">
         <v>33</v>
       </c>
       <c r="F34" s="15">
+        <f t="shared" si="5"/>
+        <v>259.32474822378839</v>
+      </c>
+      <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>6.7197158346899313</v>
-      </c>
-      <c r="G34" s="3">
+        <v>279.95379757994442</v>
+      </c>
+      <c r="H34" s="8">
         <f t="shared" si="7"/>
-        <v>7.14230718544938</v>
-      </c>
-      <c r="H34" s="8">
+        <v>280</v>
+      </c>
+      <c r="I34" s="2">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="I34" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.7602336919921465E-2</v>
+        <v>-1.8044492838613899E-2</v>
       </c>
       <c r="J34" s="4">
-        <f t="shared" si="5"/>
-        <v>4285.7142857142853</v>
+        <f t="shared" si="3"/>
+        <v>1071.4285714285713</v>
       </c>
       <c r="K34" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L34" t="str">
-        <f t="shared" si="1"/>
-        <v>0x07246E3E,</v>
+        <v>18.796992481203006</v>
+      </c>
+      <c r="L34" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M34" s="19">
-        <f t="shared" si="2"/>
-        <v>4200.3233998556252</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>1071.6053955807872</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="9"/>
+        <v>-1182.5638826714005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="10"/>
-        <v>0.11835139100422065</v>
+        <v>4.7484287120500994</v>
       </c>
       <c r="E35">
         <v>34</v>
       </c>
       <c r="F35" s="15">
+        <f t="shared" si="5"/>
+        <v>255.44932282721885</v>
+      </c>
+      <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>6.6185738505980378</v>
-      </c>
-      <c r="G35" s="3">
+        <v>275.20536886789432</v>
+      </c>
+      <c r="H35" s="9">
         <f t="shared" si="7"/>
-        <v>7.0239557944451594</v>
-      </c>
-      <c r="H35" s="9">
+        <v>275</v>
+      </c>
+      <c r="I35" s="2">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="I35" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.700418397710728E-2</v>
+        <v>-1.7416473062096108E-2</v>
       </c>
       <c r="J35" s="4">
-        <f t="shared" si="5"/>
-        <v>4285.7142857142853</v>
+        <f t="shared" si="3"/>
+        <v>1090.909090909091</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L35" t="str">
-        <f t="shared" si="1"/>
-        <v>0x070621F7,</v>
+        <v>19.480519480519661</v>
+      </c>
+      <c r="L35" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
       </c>
       <c r="M35" s="19">
-        <f t="shared" si="2"/>
-        <v>4271.0974951928465</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>1090.095012441446</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="9"/>
+        <v>-1141.4059785975305</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="10"/>
-        <v>0.11266176159285202</v>
+        <v>4.5149528504624641</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="7"/>
-        <v>6.9112940328523074</v>
+        <f t="shared" si="6"/>
+        <v>270.69041601743186</v>
       </c>
       <c r="H36" s="12">
         <f>ROUND(G36,0)</f>
-        <v>7</v>
+        <v>271</v>
       </c>
       <c r="I36" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.6830665567491951E-2</v>
+      </c>
+      <c r="L36" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M36" s="19">
+        <f t="shared" si="4"/>
+        <v>1108.277139670437</v>
+      </c>
+      <c r="N36">
         <f t="shared" si="9"/>
-        <v>-1.6445318334106576E-2</v>
-      </c>
-      <c r="L36" t="str">
-        <f t="shared" si="1"/>
-        <v>0x06E94A90,</v>
-      </c>
-      <c r="M36" s="19">
-        <f t="shared" si="2"/>
-        <v>4340.7211236271087</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1103.0144986311525</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D37" s="3">
         <f t="shared" si="10"/>
-        <v>0.10741346704648169</v>
+        <v>4.299985979398798</v>
       </c>
       <c r="G37" s="3">
-        <f t="shared" si="7"/>
-        <v>6.8038805658058257</v>
+        <f t="shared" si="6"/>
+        <v>266.39043003803306</v>
       </c>
       <c r="H37" s="13">
         <f>ROUND(G37,0)</f>
-        <v>7</v>
+        <v>266</v>
       </c>
       <c r="I37" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.6282955849708961E-2</v>
+      </c>
+      <c r="L37" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M37" s="19">
+        <f t="shared" si="4"/>
+        <v>1126.1665817243077</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="9"/>
-        <v>-1.5921995069513303E-2</v>
-      </c>
-      <c r="L37" t="str">
-        <f t="shared" si="1"/>
-        <v>0x06CDCB1D,</v>
-      </c>
-      <c r="M37" s="19">
-        <f t="shared" si="2"/>
-        <v>4409.2484736975857</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1067.1197945665265</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
-        <f t="shared" si="7"/>
-        <v>6.701320504186203</v>
+        <f t="shared" si="6"/>
+        <v>262.28889129348903</v>
       </c>
       <c r="H38" s="13">
         <f>ROUND(G38,0)</f>
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="I38" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.5769746936855154E-2</v>
+      </c>
+      <c r="L38" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M38" s="19">
+        <f t="shared" si="4"/>
+        <v>1143.7769953601046</v>
+      </c>
+      <c r="N38">
         <f t="shared" si="9"/>
-        <v>-1.5430930251250067E-2</v>
-      </c>
-      <c r="L38" t="str">
-        <f t="shared" si="1"/>
-        <v>0x06B389BD,</v>
-      </c>
-      <c r="M38" s="19">
-        <f t="shared" si="2"/>
-        <v>4476.7296208649477</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1033.4861352537393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
-        <f t="shared" si="7"/>
-        <v>6.6032593085920759</v>
+        <f t="shared" si="6"/>
+        <v>258.37100301348136</v>
       </c>
       <c r="H39" s="8">
         <f>ROUND(G39,0)</f>
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="I39" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.528788055465949E-2</v>
+      </c>
+      <c r="L39" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M39" s="19">
+        <f t="shared" si="4"/>
+        <v>1161.1210101016891</v>
+      </c>
+      <c r="N39">
         <f t="shared" si="9"/>
-        <v>-1.4969232166608809E-2</v>
-      </c>
-      <c r="L39" t="str">
-        <f t="shared" si="1"/>
-        <v>0x069A6F33,</v>
-      </c>
-      <c r="M39" s="19">
-        <f t="shared" si="2"/>
-        <v>4543.2109505323206</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1001.9065400301644</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
-        <f t="shared" si="7"/>
-        <v>6.509377642748535</v>
+        <f t="shared" si="6"/>
+        <v>254.62346713946161</v>
       </c>
       <c r="H40" s="8">
         <f t="shared" ref="H40:H53" si="12">ROUND(G40,0)</f>
-        <v>7</v>
+        <v>255</v>
       </c>
       <c r="I40" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.4834572266264976E-2</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="0"/>
+        <v>0xFE9F9B8A,</v>
+      </c>
+      <c r="M40" s="19">
+        <f t="shared" si="4"/>
+        <v>1178.2103329685826</v>
+      </c>
+      <c r="N40">
         <f t="shared" si="9"/>
-        <v>-1.4534344498835967E-2</v>
-      </c>
-      <c r="L40" t="str">
-        <f t="shared" si="1"/>
-        <v>0x06826692,</v>
-      </c>
-      <c r="M40" s="19">
-        <f t="shared" si="2"/>
-        <v>4608.7355268779165</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-972.19852804194147</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
-        <f t="shared" si="7"/>
-        <v>6.4193870065390675</v>
+        <f t="shared" si="6"/>
+        <v>251.03429478627675</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="I41" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.4407357781804552E-2</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="0"/>
+        <v>0xFB08C78B,</v>
+      </c>
+      <c r="M41" s="19">
+        <f t="shared" si="4"/>
+        <v>1195.0558399019194</v>
+      </c>
+      <c r="N41">
         <f t="shared" si="9"/>
-        <v>-1.4123999098638157E-2</v>
-      </c>
-      <c r="L41" t="str">
-        <f t="shared" si="1"/>
-        <v>0x066B5CF2,</v>
-      </c>
-      <c r="M41" s="19">
-        <f t="shared" si="2"/>
-        <v>4673.3434157250049</v>
+        <v>-944.20059958834315</v>
       </c>
       <c r="Q41">
         <v>1.1000000000000001</v>
@@ -7984,28 +8088,32 @@
         <v>-400.39677700000004</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3">
-        <f t="shared" si="7"/>
-        <v>6.3330260129289959</v>
+        <f t="shared" si="6"/>
+        <v>247.59264517919706</v>
       </c>
       <c r="H42" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="I42" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.400404825752073E-2</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="0"/>
+        <v>0xF797B798,</v>
+      </c>
+      <c r="M42" s="19">
+        <f t="shared" si="4"/>
+        <v>1211.6676558904758</v>
+      </c>
+      <c r="N42">
         <f t="shared" si="9"/>
-        <v>-1.3736176513240869E-2</v>
-      </c>
-      <c r="L42" t="str">
-        <f t="shared" si="1"/>
-        <v>0x06554131,</v>
-      </c>
-      <c r="M42" s="19">
-        <f t="shared" si="2"/>
-        <v>4737.0719682430508</v>
+        <v>-917.76930660487858</v>
       </c>
       <c r="Q42">
         <v>1.2</v>
@@ -8015,28 +8123,32 @@
         <v>-395.19657599999994</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3">
-        <f t="shared" si="7"/>
-        <v>6.250057199584381</v>
+        <f t="shared" si="6"/>
+        <v>244.28868814848005</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>244</v>
       </c>
       <c r="I43" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.3622692877073728E-2</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="0"/>
+        <v>0xF449E777,</v>
+      </c>
+      <c r="M43" s="19">
+        <f t="shared" si="4"/>
+        <v>1228.0552254538218</v>
+      </c>
+      <c r="N43">
         <f t="shared" si="9"/>
-        <v>-1.3369072826811778E-2</v>
-      </c>
-      <c r="L43" t="str">
-        <f t="shared" si="1"/>
-        <v>0x064003BF,</v>
-      </c>
-      <c r="M43" s="19">
-        <f t="shared" si="2"/>
-        <v>4799.9560711212298</v>
+        <v>-892.77680039190386</v>
       </c>
       <c r="Q43">
         <v>1.3</v>
@@ -8046,28 +8158,32 @@
         <v>-384.79639900000006</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3">
-        <f t="shared" si="7"/>
-        <v>6.1702642868002089</v>
+        <f t="shared" si="6"/>
+        <v>241.1134862175771</v>
       </c>
       <c r="H44" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>241</v>
       </c>
       <c r="I44" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.3261547368290076E-2</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="0"/>
+        <v>0xF11D0D6E,</v>
+      </c>
+      <c r="M44" s="19">
+        <f t="shared" si="4"/>
+        <v>1244.2273748606688</v>
+      </c>
+      <c r="N44">
         <f t="shared" si="9"/>
-        <v>-1.302107166602552E-2</v>
-      </c>
-      <c r="L44" t="str">
-        <f t="shared" si="1"/>
-        <v>0x062B9670,</v>
-      </c>
-      <c r="M44" s="19">
-        <f t="shared" si="2"/>
-        <v>4862.028367922223</v>
+        <v>-869.10876832825841</v>
       </c>
       <c r="Q44">
         <v>1.4</v>
@@ -8077,28 +8193,32 @@
         <v>-369.59624800000006</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3">
-        <f t="shared" si="7"/>
-        <v>6.0934498097812888</v>
+        <f t="shared" si="6"/>
+        <v>238.05889307076711</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>238</v>
       </c>
       <c r="I45" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.2690720456320697E-2</v>
+        <f t="shared" si="8"/>
+        <v>-1.2919047385776388E-2</v>
       </c>
       <c r="L45" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0617EC53,</v>
+        <f t="shared" si="0"/>
+        <v>0xEE0F139D,</v>
       </c>
       <c r="M45" s="19">
-        <f t="shared" si="2"/>
-        <v>4923.3194555641685</v>
+        <f t="shared" si="4"/>
+        <v>1260.1923672341861</v>
+      </c>
+      <c r="N45">
+        <f>I45*65536</f>
+        <v>-846.66268947424135</v>
       </c>
       <c r="Q45">
         <v>1.5</v>
@@ -8108,28 +8228,32 @@
         <v>-349.99612500000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3">
-        <f t="shared" si="7"/>
-        <v>6.019433066373475</v>
+        <f t="shared" si="6"/>
+        <v>235.11746577904282</v>
       </c>
       <c r="H46" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>235</v>
       </c>
       <c r="I46" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.2376710194774541E-2</v>
+        <f t="shared" si="8"/>
+        <v>-1.2593785904461984E-2</v>
       </c>
       <c r="L46" t="str">
-        <f t="shared" si="1"/>
-        <v>0x0604F990,</v>
+        <f t="shared" si="0"/>
+        <v>0xEB1E123C,</v>
       </c>
       <c r="M46" s="19">
-        <f t="shared" si="2"/>
-        <v>4983.8580592564149</v>
+        <f t="shared" si="4"/>
+        <v>1275.9579515114885</v>
+      </c>
+      <c r="N46">
+        <f t="shared" ref="N46:N70" si="14">I46*65536</f>
+        <v>-825.34635303482059</v>
       </c>
       <c r="Q46">
         <v>1.6</v>
@@ -8139,28 +8263,32 @@
         <v>-326.3960320000001</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3">
-        <f t="shared" si="7"/>
-        <v>5.9480483317779456</v>
+        <f t="shared" si="6"/>
+        <v>232.28238863516225</v>
       </c>
       <c r="H47" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>232</v>
       </c>
       <c r="I47" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.2077858146850124E-2</v>
+        <f t="shared" si="8"/>
+        <v>-1.2284493936524305E-2</v>
       </c>
       <c r="L47" t="str">
-        <f t="shared" si="1"/>
-        <v>0x05F2B34B,</v>
+        <f t="shared" si="0"/>
+        <v>0xE8484A9F,</v>
       </c>
       <c r="M47" s="19">
-        <f t="shared" si="2"/>
-        <v>5043.6711887027705</v>
+        <f t="shared" si="4"/>
+        <v>1291.5314060731457</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="14"/>
+        <v>-805.07659462405684</v>
       </c>
       <c r="Q47">
         <v>1.7</v>
@@ -8170,28 +8298,32 @@
         <v>-299.19597100000033</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <f t="shared" si="7"/>
-        <v>5.8791433001707194</v>
+        <f t="shared" si="6"/>
+        <v>229.54740682681577</v>
       </c>
       <c r="H48" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>230</v>
       </c>
       <c r="I48" s="2">
-        <f t="shared" si="9"/>
-        <v>-1.1793092985722132E-2</v>
+        <f t="shared" si="8"/>
+        <v>-1.1990024015568122E-2</v>
       </c>
       <c r="L48" t="str">
-        <f t="shared" si="1"/>
-        <v>0x05E10F89,</v>
+        <f t="shared" si="0"/>
+        <v>0xE58C22DA,</v>
       </c>
       <c r="M48" s="19">
-        <f t="shared" si="2"/>
-        <v>5102.7842779625489</v>
+        <f t="shared" si="4"/>
+        <v>1306.9195777338398</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="14"/>
+        <v>-785.77821388427242</v>
       </c>
       <c r="Q48">
         <v>1.8</v>
@@ -8201,28 +8333,32 @@
         <v>-268.79594400000019</v>
       </c>
     </row>
-    <row r="49" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3">
-        <f t="shared" ref="G49:G112" si="14">G48*(1+I49+1.5*I49*I49)</f>
-        <v>5.812577719931209</v>
+        <f t="shared" ref="G49:G112" si="15">G48*(1+I49+1.5*I49*I49)</f>
+        <v>226.90676848129942</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>227</v>
       </c>
       <c r="I49" s="2">
-        <f t="shared" ref="I49:I112" si="15">-1*$B$22*G48*G48</f>
-        <v>-1.1521441981314086E-2</v>
+        <f t="shared" ref="I49:I112" si="16">-1*$B$22*G48*G48</f>
+        <v>-1.1709335995759037E-2</v>
       </c>
       <c r="L49" t="str">
-        <f t="shared" ref="L49:L53" si="16">CONCATENATE("0x",DEC2HEX(G49*POWER(2,24),8),",")</f>
-        <v>0x05D00517,</v>
+        <f t="shared" ref="L49:L53" si="17">CONCATENATE("0x",DEC2HEX(G49*POWER(2,24),8),",")</f>
+        <v>0xE2E821FA,</v>
       </c>
       <c r="M49" s="19">
-        <f t="shared" ref="M49:M53" si="17">$B$12/G49</f>
-        <v>5161.2213110081293</v>
+        <f t="shared" ref="M49:M53" si="18">$B$12/G49</f>
+        <v>1322.1289166820275</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="14"/>
+        <v>-767.38304381806427</v>
       </c>
       <c r="Q49">
         <v>1.9</v>
@@ -8232,28 +8368,32 @@
         <v>-235.59595300000001</v>
       </c>
     </row>
-    <row r="50" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3">
-        <f t="shared" si="14"/>
-        <v>5.7482221946940451</v>
+        <f t="shared" si="15"/>
+        <v>224.35517386157449</v>
       </c>
       <c r="H50" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>224</v>
       </c>
       <c r="I50" s="2">
-        <f t="shared" si="15"/>
-        <v>-1.1262019916746897E-2</v>
+        <f t="shared" si="16"/>
+        <v>-1.1441484796139115E-2</v>
       </c>
       <c r="L50" t="str">
-        <f t="shared" si="16"/>
-        <v>0x05BF8B7D,</v>
+        <f t="shared" si="17"/>
+        <v>0xE05AECAC,</v>
       </c>
       <c r="M50" s="19">
-        <f t="shared" si="17"/>
-        <v>5219.0049347243057</v>
+        <f t="shared" si="18"/>
+        <v>1337.1655078705598</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="14"/>
+        <v>-749.82914759977302</v>
       </c>
       <c r="Q50">
         <v>2</v>
@@ -8263,28 +8403,32 @@
         <v>-199.99600000000009</v>
       </c>
     </row>
-    <row r="51" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3">
-        <f t="shared" si="14"/>
-        <v>5.6859571269380798</v>
+        <f t="shared" si="15"/>
+        <v>221.88773069418372</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>222</v>
       </c>
       <c r="I51" s="2">
-        <f t="shared" si="15"/>
-        <v>-1.1014019466524408E-2</v>
+        <f t="shared" si="16"/>
+        <v>-1.1185609786323847E-2</v>
       </c>
       <c r="L51" t="str">
-        <f t="shared" si="16"/>
-        <v>0x05AF9AE2,</v>
+        <f t="shared" si="17"/>
+        <v>0xDDE34251,</v>
       </c>
       <c r="M51" s="19">
-        <f t="shared" si="17"/>
-        <v>5276.1565608489154</v>
+        <f t="shared" si="18"/>
+        <v>1352.0350992884521</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="14"/>
+        <v>-733.06012295651965</v>
       </c>
       <c r="Q51">
         <v>2.1</v>
@@ -8294,28 +8438,32 @@
         <v>-162.39608700000031</v>
       </c>
     </row>
-    <row r="52" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3">
-        <f t="shared" si="14"/>
-        <v>5.625671784518131</v>
+        <f t="shared" si="15"/>
+        <v>219.49991477352964</v>
       </c>
       <c r="H52" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="I52" s="2">
-        <f t="shared" si="15"/>
-        <v>-1.0776702816459314E-2</v>
+        <f t="shared" si="16"/>
+        <v>-1.0940925562803244E-2</v>
       </c>
       <c r="L52" t="str">
-        <f t="shared" si="16"/>
-        <v>0x05A02C06,</v>
+        <f t="shared" si="17"/>
+        <v>0xDB7FFA6A,</v>
       </c>
       <c r="M52" s="19">
-        <f t="shared" si="17"/>
-        <v>5332.6964581474713</v>
+        <f t="shared" si="18"/>
+        <v>1366.7431274837934</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="14"/>
+        <v>-717.02449768387339</v>
       </c>
       <c r="Q52">
         <v>2.2000000000000002</v>
@@ -8325,28 +8473,32 @@
         <v>-123.19621600000005</v>
       </c>
     </row>
-    <row r="53" spans="5:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="5:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3">
-        <f t="shared" si="14"/>
-        <v>5.567263473587408</v>
+        <f t="shared" si="15"/>
+        <v>217.18753512178537</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>217</v>
       </c>
       <c r="I53" s="2">
-        <f t="shared" si="15"/>
-        <v>-1.0549394342374471E-2</v>
+        <f t="shared" si="16"/>
+        <v>-1.0706713907908172E-2</v>
       </c>
       <c r="L53" t="str">
-        <f t="shared" si="16"/>
-        <v>0x0591382D,</v>
+        <f t="shared" si="17"/>
+        <v>0xD930024D,</v>
       </c>
       <c r="M53" s="19">
-        <f t="shared" si="17"/>
-        <v>5388.6438359398744</v>
+        <f t="shared" si="18"/>
+        <v>1381.2947406570938</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="14"/>
+        <v>-701.67520266866995</v>
       </c>
       <c r="Q53">
         <v>2.2999999999999998</v>
@@ -8356,20 +8508,24 @@
         <v>-82.79638900000009</v>
       </c>
     </row>
-    <row r="54" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3">
-        <f t="shared" si="14"/>
-        <v>5.5106368038766425</v>
+        <f t="shared" si="15"/>
+        <v>214.9467030949196</v>
       </c>
       <c r="H54" s="12">
         <f>ROUND(G54,0)</f>
-        <v>6</v>
+        <v>215</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="15"/>
-        <v>-1.0331474194780177E-2</v>
+        <f t="shared" si="16"/>
+        <v>-1.0482316758283722E-2</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="14"/>
+        <v>-686.96911107088204</v>
       </c>
       <c r="Q54">
         <v>2.4</v>
@@ -8379,20 +8535,24 @@
         <v>-41.59660800000006</v>
       </c>
     </row>
-    <row r="55" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3">
-        <f t="shared" si="14"/>
-        <v>5.4557030343886819</v>
+        <f t="shared" si="15"/>
+        <v>212.77380491747817</v>
       </c>
       <c r="H55" s="13">
         <f>ROUND(G55,0)</f>
-        <v>5</v>
+        <v>213</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="15"/>
-        <v>-1.0122372661413259E-2</v>
+        <f t="shared" si="16"/>
+        <v>-1.0267130038083449E-2</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="14"/>
+        <v>-672.86663417583691</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -8402,20 +8562,24 @@
         <v>3.1249999997271516E-3</v>
       </c>
     </row>
-    <row r="56" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3">
-        <f t="shared" si="14"/>
-        <v>5.4023794893133905</v>
+        <f t="shared" si="15"/>
+        <v>210.66547720545293</v>
       </c>
       <c r="H56" s="13">
         <f>ROUND(G56,0)</f>
-        <v>5</v>
+        <v>211</v>
       </c>
       <c r="I56" s="2">
-        <f t="shared" si="15"/>
-        <v>-9.9215651998126233E-3</v>
+        <f t="shared" si="16"/>
+        <v>-1.0060598235346902E-2</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="14"/>
+        <v>-659.33136595169458</v>
       </c>
       <c r="Q56">
         <v>2.6</v>
@@ -8425,20 +8589,24 @@
         <v>41.602807999999641</v>
       </c>
     </row>
-    <row r="57" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3">
-        <f t="shared" si="14"/>
-        <v>5.3505890354300423</v>
+        <f t="shared" si="15"/>
+        <v>208.61858510062589</v>
       </c>
       <c r="H57" s="8">
         <f>ROUND(G57,0)</f>
-        <v>5</v>
+        <v>209</v>
       </c>
       <c r="I57" s="2">
-        <f t="shared" si="15"/>
-        <v>-9.7285680488513361E-3</v>
+        <f t="shared" si="16"/>
+        <v>-9.8622096191558241E-3</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="14"/>
+        <v>-646.32976960099609</v>
       </c>
       <c r="Q57">
         <v>2.7</v>
@@ -8448,20 +8616,24 @@
         <v>82.802438999999595</v>
       </c>
     </row>
-    <row r="58" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3">
+        <f t="shared" si="15"/>
+        <v>206.63020269348732</v>
+      </c>
+      <c r="H58" s="8">
+        <f t="shared" ref="H58:H111" si="19">ROUND(G58,0)</f>
+        <v>207</v>
+      </c>
+      <c r="I58" s="2">
+        <f t="shared" si="16"/>
+        <v>-9.6714920109749088E-3</v>
+      </c>
+      <c r="N58">
         <f t="shared" si="14"/>
-        <v>5.3002596134936004</v>
-      </c>
-      <c r="H58" s="8">
-        <f t="shared" ref="H58:H111" si="18">ROUND(G58,0)</f>
-        <v>5</v>
-      </c>
-      <c r="I58" s="2">
-        <f t="shared" si="15"/>
-        <v>-9.5429343420213968E-3</v>
+        <v>-633.83090043125162</v>
       </c>
       <c r="Q58">
         <v>2.8</v>
@@ -8471,20 +8643,24 @@
         <v>123.20201599999973</v>
       </c>
     </row>
-    <row r="59" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3">
+        <f t="shared" si="15"/>
+        <v>204.69759545701831</v>
+      </c>
+      <c r="H59" s="8">
+        <f t="shared" si="19"/>
+        <v>205</v>
+      </c>
+      <c r="I59" s="2">
+        <f t="shared" si="16"/>
+        <v>-9.4880090367003671E-3</v>
+      </c>
+      <c r="N59">
         <f t="shared" si="14"/>
-        <v>5.2513238171380126</v>
-      </c>
-      <c r="H59" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I59" s="2">
-        <f t="shared" si="15"/>
-        <v>-9.3642506568104439E-3</v>
+        <v>-621.80616022919526</v>
       </c>
       <c r="Q59">
         <v>2.9</v>
@@ -8494,20 +8670,24 @@
         <v>162.40153699999973</v>
       </c>
     </row>
-    <row r="60" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3">
+        <f t="shared" si="15"/>
+        <v>202.81820445178789</v>
+      </c>
+      <c r="H60" s="8">
+        <f t="shared" si="19"/>
+        <v>203</v>
+      </c>
+      <c r="I60" s="2">
+        <f t="shared" si="16"/>
+        <v>-9.3113567968633598E-3</v>
+      </c>
+      <c r="N60">
         <f t="shared" si="14"/>
-        <v>5.2037185137071038</v>
-      </c>
-      <c r="H60" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I60" s="2">
-        <f t="shared" si="15"/>
-        <v>-9.1921339441469827E-3</v>
+        <v>-610.22907903923715</v>
       </c>
       <c r="Q60">
         <v>3</v>
@@ -8517,20 +8697,24 @@
         <v>200.00099999999975</v>
       </c>
     </row>
-    <row r="61" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3">
+        <f t="shared" si="15"/>
+        <v>200.98963209513937</v>
+      </c>
+      <c r="H61" s="8">
+        <f t="shared" si="19"/>
+        <v>201</v>
+      </c>
+      <c r="I61" s="2">
+        <f t="shared" si="16"/>
+        <v>-9.1411609015660516E-3</v>
+      </c>
+      <c r="N61">
         <f t="shared" si="14"/>
-        <v>5.1573845021685374</v>
-      </c>
-      <c r="H61" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I61" s="2">
-        <f t="shared" si="15"/>
-        <v>-9.0262287899660239E-3</v>
+        <v>-599.07512084503276</v>
       </c>
       <c r="Q61">
         <v>3.1</v>
@@ -8540,20 +8724,24 @@
         <v>235.60040300000037</v>
       </c>
     </row>
-    <row r="62" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3">
+        <f t="shared" si="15"/>
+        <v>199.20962931471041</v>
+      </c>
+      <c r="H62" s="8">
+        <f t="shared" si="19"/>
+        <v>199</v>
+      </c>
+      <c r="I62" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.9770738243865507E-3</v>
+      </c>
+      <c r="N62">
         <f t="shared" si="14"/>
-        <v>5.1122662039007674</v>
-      </c>
-      <c r="H62" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I62" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.8662049677360709E-3</v>
+        <v>-588.32151015499699</v>
       </c>
       <c r="Q62">
         <v>3.2</v>
@@ -8563,20 +8751,24 @@
         <v>268.79974399999992</v>
       </c>
     </row>
-    <row r="63" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3">
+        <f t="shared" si="15"/>
+        <v>197.47608392994803</v>
+      </c>
+      <c r="H63" s="8">
+        <f t="shared" si="19"/>
+        <v>197</v>
+      </c>
+      <c r="I63" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.818772535934296E-3</v>
+      </c>
+      <c r="N63">
         <f t="shared" si="14"/>
-        <v>5.0683113826847572</v>
-      </c>
-      <c r="H63" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I63" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.7117552465153202E-3</v>
+        <v>-577.94707691499002</v>
       </c>
       <c r="Q63">
         <v>3.3</v>
@@ -8586,20 +8778,24 @@
         <v>299.19902099999899</v>
       </c>
     </row>
-    <row r="64" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3">
+        <f t="shared" si="15"/>
+        <v>195.78701012529817</v>
+      </c>
+      <c r="H64" s="8">
+        <f t="shared" si="19"/>
+        <v>196</v>
+      </c>
+      <c r="I64" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.6659563831795287E-3</v>
+      </c>
+      <c r="N64">
         <f t="shared" si="14"/>
-        <v>5.0254708906964884</v>
-      </c>
-      <c r="H64" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I64" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.5625934239506249E-3</v>
+        <v>-567.9321175280536</v>
       </c>
       <c r="Q64">
         <v>3.4</v>
@@ -8609,20 +8805,24 @@
         <v>326.3982319999991</v>
       </c>
     </row>
-    <row r="65" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3">
+        <f t="shared" si="15"/>
+        <v>194.14053889591329</v>
+      </c>
+      <c r="H65" s="8">
+        <f t="shared" si="19"/>
+        <v>194</v>
+      </c>
+      <c r="I65" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.5183451852896899E-3</v>
+      </c>
+      <c r="N65">
         <f t="shared" si="14"/>
-        <v>4.9836984376949882</v>
-      </c>
-      <c r="H65" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I65" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.4184525577459188E-3</v>
+        <v>-558.25827006314512</v>
       </c>
       <c r="Q65">
         <v>3.5</v>
@@ -8632,20 +8832,24 @@
         <v>349.99737499999992</v>
       </c>
     </row>
-    <row r="66" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3">
+        <f t="shared" si="15"/>
+        <v>192.53490936147639</v>
+      </c>
+      <c r="H66" s="8">
+        <f t="shared" si="19"/>
+        <v>193</v>
+      </c>
+      <c r="I66" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.375677520621249E-3</v>
+      </c>
+      <c r="N66">
         <f t="shared" si="14"/>
-        <v>4.9429503809440645</v>
-      </c>
-      <c r="H66" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I66" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.2790833726278223E-3</v>
+        <v>-548.90840199143418</v>
       </c>
       <c r="Q66">
         <v>3.6</v>
@@ -8655,20 +8859,24 @@
         <v>369.59644799999933</v>
       </c>
     </row>
-    <row r="67" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3">
+        <f t="shared" si="15"/>
+        <v>190.9684608564589</v>
+      </c>
+      <c r="H67" s="8">
+        <f t="shared" si="19"/>
+        <v>191</v>
+      </c>
+      <c r="I67" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.2377091828515405E-3</v>
+      </c>
+      <c r="N67">
         <f t="shared" si="14"/>
-        <v>4.9031855337025094</v>
-      </c>
-      <c r="H67" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I67" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.1442528228250245E-3</v>
+        <v>-539.86650900735856</v>
       </c>
       <c r="Q67">
         <v>3.7</v>
@@ -8678,20 +8886,24 @@
         <v>384.79544900000019</v>
       </c>
     </row>
-    <row r="68" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3">
+        <f t="shared" si="15"/>
+        <v>189.4396257161205</v>
+      </c>
+      <c r="H68" s="8">
+        <f t="shared" si="19"/>
+        <v>189</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" si="16"/>
+        <v>-8.104211787085527E-3</v>
+      </c>
+      <c r="N68">
         <f t="shared" si="14"/>
-        <v>4.864364990374221</v>
-      </c>
-      <c r="H68" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I68" s="2">
-        <f t="shared" si="15"/>
-        <v>-8.0137427926365214E-3</v>
+        <v>-531.1176236784371</v>
       </c>
       <c r="Q68">
         <v>3.8</v>
@@ -8701,20 +8913,24 @@
         <v>395.19437600000037</v>
       </c>
     </row>
-    <row r="69" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3">
+        <f t="shared" si="15"/>
+        <v>187.94692268708141</v>
+      </c>
+      <c r="H69" s="8">
+        <f t="shared" si="19"/>
+        <v>188</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="16"/>
+        <v>-7.9749715092141838E-3</v>
+      </c>
+      <c r="N69">
         <f t="shared" si="14"/>
-        <v>4.8264519666325052</v>
-      </c>
-      <c r="H69" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I69" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.8873489198594653E-3</v>
+        <v>-522.64773282786075</v>
       </c>
       <c r="Q69">
         <v>3.9</v>
@@ -8724,20 +8940,24 @@
         <v>400.39322699999911</v>
       </c>
     </row>
-    <row r="70" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3">
+        <f t="shared" si="15"/>
+        <v>186.488950899565</v>
+      </c>
+      <c r="H70" s="8">
+        <f t="shared" si="19"/>
+        <v>186</v>
+      </c>
+      <c r="I70" s="2">
+        <f t="shared" si="16"/>
+        <v>-7.8497879438986125E-3</v>
+      </c>
+      <c r="N70">
         <f t="shared" si="14"/>
-        <v>4.7894116530265443</v>
-      </c>
-      <c r="H70" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="I70" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.7648795287369255E-3</v>
+        <v>-514.44370269133947</v>
       </c>
       <c r="Q70">
         <v>4</v>
@@ -8747,2295 +8967,2295 @@
         <v>399.99199999999973</v>
       </c>
     </row>
-    <row r="71" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3">
-        <f t="shared" si="14"/>
-        <v>4.7532110807469472</v>
+        <f t="shared" si="15"/>
+        <v>185.06438434560565</v>
       </c>
       <c r="H71" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>185</v>
       </c>
       <c r="I71" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.6461546607154846E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.7284730683600802E-3</v>
       </c>
       <c r="Q71">
         <v>4.0999999999999996</v>
       </c>
       <c r="R71" s="16">
-        <f t="shared" ref="R71:R86" si="19" xml:space="preserve"> -66.667*POWER(Q71,3) + 500*POWER(Q71,2) - 833.33*Q71</f>
+        <f t="shared" ref="R71:R86" si="20" xml:space="preserve"> -66.667*POWER(Q71,3) + 500*POWER(Q71,2) - 833.33*Q71</f>
         <v>393.59069300000056</v>
       </c>
     </row>
-    <row r="72" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3">
-        <f t="shared" si="14"/>
-        <v>4.7178189983748489</v>
+        <f t="shared" si="15"/>
+        <v>183.6719668137944</v>
       </c>
       <c r="H72" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>184</v>
       </c>
       <c r="I72" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.5310051927118538E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.6108503007151218E-3</v>
       </c>
       <c r="Q72">
         <v>4.2</v>
       </c>
       <c r="R72" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>380.78930399999945</v>
       </c>
     </row>
-    <row r="73" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3">
-        <f t="shared" si="14"/>
-        <v>4.6832057585682101</v>
+        <f t="shared" si="15"/>
+        <v>182.31050723662219</v>
       </c>
       <c r="H73" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>182</v>
       </c>
       <c r="I73" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.4192720338088864E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.4967536429439091E-3</v>
       </c>
       <c r="Q73">
         <v>4.3</v>
       </c>
       <c r="R73" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>361.18783100000064</v>
       </c>
     </row>
-    <row r="74" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3">
-        <f t="shared" si="14"/>
-        <v>4.6493432137523101</v>
+        <f t="shared" si="15"/>
+        <v>180.9788754112889</v>
       </c>
       <c r="H74" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>181</v>
       </c>
       <c r="I74" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.3108053923621481E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.3860268997498818E-3</v>
       </c>
       <c r="Q74">
         <v>4.4000000000000004</v>
       </c>
       <c r="R74" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>334.38627199999928</v>
       </c>
     </row>
-    <row r="75" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3">
-        <f t="shared" si="14"/>
-        <v>4.616204619981036</v>
+        <f t="shared" si="15"/>
+        <v>179.67599805906545</v>
       </c>
       <c r="H75" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>180</v>
       </c>
       <c r="I75" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.2054641064215521E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.2785229655855177E-3</v>
       </c>
       <c r="Q75">
         <v>4.5</v>
       </c>
       <c r="R75" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>299.9846249999996</v>
       </c>
     </row>
-    <row r="76" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3">
-        <f t="shared" si="14"/>
-        <v>4.5837645482233187</v>
+        <f t="shared" si="15"/>
+        <v>178.40085519200866</v>
       </c>
       <c r="H76" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>178</v>
       </c>
       <c r="I76" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.1031150311780871E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.1741031730047306E-3</v>
       </c>
       <c r="Q76">
         <v>4.5999999999999996</v>
       </c>
       <c r="R76" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>257.58288800000037</v>
       </c>
     </row>
-    <row r="77" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3">
-        <f t="shared" si="14"/>
-        <v>4.5519988024064704</v>
+        <f t="shared" si="15"/>
+        <v>177.1524767590991</v>
       </c>
       <c r="H77" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>177</v>
       </c>
       <c r="I77" s="2">
-        <f t="shared" si="15"/>
-        <v>-7.003632477849641E-3</v>
+        <f t="shared" si="16"/>
+        <v>-7.072636696275566E-3</v>
       </c>
       <c r="Q77">
         <v>4.7</v>
       </c>
       <c r="R77" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>206.78105899999946</v>
       </c>
     </row>
-    <row r="78" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3">
-        <f t="shared" si="14"/>
-        <v>4.5208843436166273</v>
+        <f t="shared" si="15"/>
+        <v>175.92993954675978</v>
       </c>
       <c r="H78" s="8">
-        <f t="shared" si="18"/>
-        <v>5</v>
+        <f t="shared" si="19"/>
+        <v>176</v>
       </c>
       <c r="I78" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.9068976990366467E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.9740000048629219E-3</v>
       </c>
       <c r="Q78">
         <v>4.8</v>
       </c>
       <c r="R78" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>147.1791360000002</v>
       </c>
     </row>
-    <row r="79" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3">
-        <f t="shared" si="14"/>
-        <v>4.490399219917073</v>
+        <f t="shared" si="15"/>
+        <v>174.7323643112675</v>
       </c>
       <c r="H79" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>175</v>
       </c>
       <c r="I79" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.8127984161193136E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.8780763619836777E-3</v>
       </c>
       <c r="Q79">
         <v>4.9000000000000004</v>
       </c>
       <c r="R79" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>78.377116999999544</v>
       </c>
     </row>
-    <row r="80" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3">
-        <f t="shared" si="14"/>
-        <v>4.4605225012990051</v>
+        <f t="shared" si="15"/>
+        <v>173.55891312283134</v>
       </c>
       <c r="H80" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>174</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.7212283847439521E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.7847553639567805E-3</v>
       </c>
       <c r="Q80">
         <v>5</v>
       </c>
       <c r="R80" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-2.5000000000545697E-2</v>
       </c>
     </row>
-    <row r="81" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3">
-        <f t="shared" si="14"/>
-        <v>4.4312342193270373</v>
+        <f t="shared" si="15"/>
+        <v>172.40878690312104</v>
       </c>
       <c r="H81" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>172</v>
       </c>
       <c r="I81" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.6320869948649106E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.6939325165285592E-3</v>
       </c>
       <c r="Q81">
         <v>5.0999999999999996</v>
       </c>
       <c r="R81" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-88.427217000000383</v>
       </c>
     </row>
-    <row r="82" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3">
-        <f t="shared" si="14"/>
-        <v>4.4025153110842545</v>
+        <f t="shared" si="15"/>
+        <v>171.28122313981333</v>
       </c>
       <c r="H82" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>171</v>
       </c>
       <c r="I82" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.5452789021782998E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.6055088447568447E-3</v>
       </c>
       <c r="Q82">
         <v>5.2</v>
       </c>
       <c r="R82" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-187.22953600000073</v>
       </c>
     </row>
-    <row r="83" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3">
-        <f t="shared" si="14"/>
-        <v>4.3743475670595169</v>
+        <f t="shared" si="15"/>
+        <v>170.17549376331323</v>
       </c>
       <c r="H83" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>170</v>
       </c>
       <c r="I83" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.4607136881104296E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.5193905333934508E-3</v>
       </c>
       <c r="Q83">
         <v>5.3</v>
       </c>
       <c r="R83" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-296.8319590000001</v>
       </c>
     </row>
-    <row r="84" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3">
-        <f t="shared" si="14"/>
-        <v>4.346713582653531</v>
+        <f t="shared" si="15"/>
+        <v>169.09090317222555</v>
       </c>
       <c r="H84" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>169</v>
       </c>
       <c r="I84" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.3783055458131715E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.4354885950194353E-3</v>
       </c>
       <c r="Q84">
         <v>5.4</v>
       </c>
       <c r="R84" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-417.6344880000006</v>
       </c>
     </row>
-    <row r="85" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3">
-        <f t="shared" si="14"/>
-        <v>4.3195967130104567</v>
+        <f t="shared" si="15"/>
+        <v>168.02678639541745</v>
       </c>
       <c r="H85" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>168</v>
       </c>
       <c r="I85" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.297972989874898E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.3537185634664354E-3</v>
       </c>
       <c r="Q85">
         <v>5.5</v>
       </c>
       <c r="R85" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-550.03712500000074</v>
       </c>
     </row>
-    <row r="86" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3">
-        <f t="shared" si="14"/>
-        <v>4.2929810309088792</v>
+        <f t="shared" si="15"/>
+        <v>166.98250737964526</v>
       </c>
       <c r="H86" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>167</v>
       </c>
       <c r="I86" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.2196385876835802E-3</v>
+        <f t="shared" si="16"/>
+        <v>-6.2740002103047207E-3</v>
       </c>
       <c r="Q86">
         <v>5.6</v>
       </c>
       <c r="R86" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-694.43987199999992</v>
       </c>
     </row>
-    <row r="87" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3">
-        <f t="shared" si="14"/>
-        <v>4.2668512874702698</v>
+        <f t="shared" si="15"/>
+        <v>165.95745739273343</v>
       </c>
       <c r="H87" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>166</v>
       </c>
       <c r="I87" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.1432287105811544E-3</v>
-      </c>
-    </row>
-    <row r="88" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-6.1962572823985075E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3">
-        <f t="shared" si="14"/>
-        <v>4.2411928754648454</v>
+        <f t="shared" si="15"/>
+        <v>164.95105353320301</v>
       </c>
       <c r="H88" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>165</v>
       </c>
       <c r="I88" s="2">
-        <f t="shared" si="15"/>
-        <v>-6.0686733031288988E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-6.1204172587246515E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3">
-        <f t="shared" si="14"/>
-        <v>4.2159917950143377</v>
+        <f t="shared" si="15"/>
+        <v>163.96273733806481</v>
       </c>
       <c r="H89" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>164</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.9959056689645879E-3</v>
-      </c>
-    </row>
-    <row r="90" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-6.0464111248252454E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3">
-        <f t="shared" si="14"/>
-        <v>4.1912346215088334</v>
+        <f t="shared" si="15"/>
+        <v>162.99197348122726</v>
       </c>
       <c r="H90" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>163</v>
       </c>
       <c r="I90" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.9248622718760724E-3</v>
-      </c>
-    </row>
-    <row r="91" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.974173163420274E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3">
-        <f t="shared" si="14"/>
-        <v>4.1669084755707448</v>
+        <f t="shared" si="15"/>
+        <v>162.03824855563084</v>
       </c>
       <c r="H91" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>162</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.8554825508447643E-3</v>
-      </c>
-    </row>
-    <row r="92" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.9036407598455761E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3">
-        <f t="shared" si="14"/>
-        <v>4.1430009949133293</v>
+        <f t="shared" si="15"/>
+        <v>161.10106993281892</v>
       </c>
       <c r="H92" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>161</v>
       </c>
       <c r="I92" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.7877087479277691E-3</v>
-      </c>
-    </row>
-    <row r="93" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.8347542211058664E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3">
-        <f t="shared" si="14"/>
-        <v>4.1195003079541443</v>
+        <f t="shared" si="15"/>
+        <v>160.17996469419262</v>
       </c>
       <c r="H93" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>160</v>
       </c>
       <c r="I93" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.7214857479509452E-3</v>
-      </c>
-    </row>
-    <row r="94" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.7674566074442241E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3">
-        <f t="shared" si="14"/>
-        <v>4.0963950090555672</v>
+        <f t="shared" si="15"/>
+        <v>159.2744786286859</v>
       </c>
       <c r="H94" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>159</v>
       </c>
       <c r="I94" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.6567609290780968E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.7016935754295095E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3">
-        <f t="shared" si="14"/>
-        <v>4.0736741352751364</v>
+        <f t="shared" si="15"/>
+        <v>158.38417529203704</v>
       </c>
       <c r="H95" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>158</v>
       </c>
       <c r="I95" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.59348402340512E-3</v>
-      </c>
-    </row>
-    <row r="96" spans="5:18" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.6374132316532712E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="5:18" x14ac:dyDescent="0.25">
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3">
-        <f t="shared" si="14"/>
-        <v>4.0513271445181038</v>
+        <f t="shared" si="15"/>
+        <v>157.5086351232332</v>
       </c>
       <c r="H96" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>158</v>
       </c>
       <c r="I96" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.53160698680321E-3</v>
-      </c>
-    </row>
-    <row r="97" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.5745659962086035E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3">
-        <f t="shared" si="14"/>
-        <v>4.0293438949933602</v>
+        <f t="shared" si="15"/>
+        <v>156.64745461406679</v>
       </c>
       <c r="H97" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>157</v>
       </c>
       <c r="I97" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.4710838773030703E-3</v>
-      </c>
-    </row>
-    <row r="98" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.5131044751964026E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3">
-        <f t="shared" si="14"/>
-        <v>4.0077146258818193</v>
+        <f t="shared" si="15"/>
+        <v>155.80024552807154</v>
       </c>
       <c r="H98" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>156</v>
       </c>
       <c r="I98" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.411870741373421E-3</v>
-      </c>
-    </row>
-    <row r="99" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.4529833415702476E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3">
-        <f t="shared" si="14"/>
-        <v>3.9864299391336124</v>
+        <f t="shared" si="15"/>
+        <v>154.96663416540605</v>
       </c>
       <c r="H99" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>155</v>
       </c>
       <c r="I99" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.3539255075023499E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.3941592236905278E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3">
-        <f t="shared" si="14"/>
-        <v>3.9654807823170168</v>
+        <f t="shared" si="15"/>
+        <v>154.14626067052401</v>
       </c>
       <c r="H100" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>154</v>
       </c>
       <c r="I100" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.2972078865402726E-3</v>
-      </c>
-    </row>
-    <row r="101" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.3365906010121771E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3">
-        <f t="shared" si="14"/>
-        <v>3.9448584324480542</v>
+        <f t="shared" si="15"/>
+        <v>153.33877837971963</v>
       </c>
       <c r="H101" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>153</v>
       </c>
       <c r="I101" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.2416792783085264E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.2802377063789199E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3">
-        <f t="shared" si="14"/>
-        <v>3.9245544807351793</v>
+        <f t="shared" si="15"/>
+        <v>152.54385320586184</v>
       </c>
       <c r="H102" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>153</v>
       </c>
       <c r="I102" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.1873026840188394E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.2250624344410603E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3">
-        <f t="shared" si="14"/>
-        <v>3.9045608181784863</v>
+        <f t="shared" si="15"/>
+        <v>151.76116305783864</v>
       </c>
       <c r="H103" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>152</v>
       </c>
       <c r="I103" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.1340426240861908E-3</v>
-      </c>
-    </row>
-    <row r="104" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.171028255753672E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3">
-        <f t="shared" si="14"/>
-        <v>3.8848696219674421</v>
+        <f t="shared" si="15"/>
+        <v>150.99039729242082</v>
       </c>
       <c r="H104" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>151</v>
       </c>
       <c r="I104" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.0818650609515499E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.1181001361484202E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3">
-        <f t="shared" si="14"/>
-        <v>3.8654733426253411</v>
+        <f t="shared" si="15"/>
+        <v>150.2312561964271</v>
       </c>
       <c r="H105" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>150</v>
       </c>
       <c r="I105" s="2">
-        <f t="shared" si="15"/>
-        <v>-5.0307373265618188E-3</v>
-      </c>
-    </row>
-    <row r="106" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.0662444610051283E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3">
-        <f t="shared" si="14"/>
-        <v>3.8463646918525205</v>
+        <f t="shared" si="15"/>
+        <v>149.48345049723122</v>
       </c>
       <c r="H106" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>149</v>
       </c>
       <c r="I106" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.9806280541823764E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-5.0154289640792259E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3">
-        <f t="shared" si="14"/>
-        <v>3.827536631023893</v>
+        <f t="shared" si="15"/>
+        <v>148.74670089979574</v>
       </c>
       <c r="H107" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>149</v>
       </c>
       <c r="I107" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.9315071142432441E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-4.9656226605684839E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3">
-        <f t="shared" si="14"/>
-        <v>3.8089823602995785</v>
+        <f t="shared" si="15"/>
+        <v>148.02073764855041</v>
       </c>
       <c r="H108" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>148</v>
       </c>
       <c r="I108" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.8833455539432444E-3</v>
-      </c>
-    </row>
-    <row r="109" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-4.9167957841273983E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3">
-        <f t="shared" si="14"/>
-        <v>3.7906953083103936</v>
+        <f t="shared" si="15"/>
+        <v>147.30530011255479</v>
       </c>
       <c r="H109" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>147</v>
       </c>
       <c r="I109" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.836115540357783E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-4.8689197275602189E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3">
-        <f t="shared" si="14"/>
-        <v>3.7726691223826743</v>
+        <f t="shared" si="15"/>
+        <v>146.60013639249684</v>
       </c>
       <c r="H110" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>147</v>
       </c>
       <c r="I110" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.7897903068154762E-3</v>
-      </c>
-    </row>
-    <row r="111" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-4.8219669869444069E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3">
-        <f t="shared" si="14"/>
-        <v>3.754897659269421</v>
+        <f t="shared" si="15"/>
+        <v>145.90500294818193</v>
       </c>
       <c r="H111" s="8">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="19"/>
+        <v>146</v>
       </c>
       <c r="I111" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.7443441023265528E-3</v>
-      </c>
-    </row>
-    <row r="112" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-4.7759111089552605E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3">
-        <f t="shared" si="14"/>
-        <v>3.7373749763570623</v>
+        <f t="shared" si="15"/>
+        <v>145.21966424526187</v>
       </c>
       <c r="I112" s="2">
-        <f t="shared" si="15"/>
-        <v>-4.6997521438623254E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>-4.7307266411797727E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3">
-        <f t="shared" ref="G113:G169" si="20">G112*(1+I113+1.5*I113*I113)</f>
-        <v>3.7200953233192626</v>
+        <f t="shared" ref="G113:G169" si="21">G112*(1+I113+1.5*I113*I113)</f>
+        <v>144.54389242004035</v>
       </c>
       <c r="I113" s="2">
-        <f t="shared" ref="I113:I152" si="21">-1*$B$22*G112*G112</f>
-        <v>-4.6559905712999844E-3</v>
-      </c>
-    </row>
-    <row r="114" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" ref="I113:I152" si="22">-1*$B$22*G112*G112</f>
+        <v>-4.6863890852236866E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3">
-        <f t="shared" si="20"/>
-        <v>3.7030531341911637</v>
+        <f t="shared" si="21"/>
+        <v>143.87746696127192</v>
       </c>
       <c r="I114" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.6130364048606164E-3</v>
-      </c>
-    </row>
-    <row r="115" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.6428748524302661E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3">
-        <f t="shared" si="20"/>
-        <v>3.6862430198392575</v>
+        <f t="shared" si="21"/>
+        <v>143.22017440794573</v>
       </c>
       <c r="I115" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.570867504881E-3</v>
-      </c>
-    </row>
-    <row r="116" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.6001612220426431E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3">
-        <f t="shared" si="20"/>
-        <v>3.6696597608037651</v>
+        <f t="shared" si="21"/>
+        <v>142.57180806211369</v>
       </c>
       <c r="I116" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.5294625337712162E-3</v>
-      </c>
-    </row>
-    <row r="117" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.5582263016538645E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3">
-        <f t="shared" si="20"/>
-        <v>3.6532983004919326</v>
+        <f t="shared" si="21"/>
+        <v>141.93216771588581</v>
       </c>
       <c r="I117" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.488800920020782E-3</v>
-      </c>
-    </row>
-    <row r="118" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.5170489898000406E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3">
-        <f t="shared" si="20"/>
-        <v>3.6371537387021022</v>
+        <f t="shared" si="21"/>
+        <v>141.30105939177443</v>
       </c>
       <c r="I118" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.4488628241257473E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.4766089405622973E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3">
-        <f t="shared" si="20"/>
-        <v>3.6212213254597212</v>
+        <f t="shared" si="21"/>
+        <v>140.67829509562256</v>
       </c>
       <c r="I119" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.4096291063182268E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.4368865300528368E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3">
-        <f t="shared" si="20"/>
-        <v>3.6054964551476916</v>
+        <f t="shared" si="21"/>
+        <v>140.06369258140188</v>
       </c>
       <c r="I120" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.3710812959880862E-3</v>
-      </c>
-    </row>
-    <row r="121" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.3978628246691244E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3">
-        <f t="shared" si="20"/>
-        <v>3.5899746609145895</v>
+        <f t="shared" si="21"/>
+        <v>139.45707512721262</v>
       </c>
       <c r="I121" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.3332015626941899E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.3595195510083224E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3">
-        <f t="shared" si="20"/>
-        <v>3.5746516093453464</v>
+        <f t="shared" si="21"/>
+        <v>138.85827132185997</v>
       </c>
       <c r="I122" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.2959726886696069E-3</v>
-      </c>
-    </row>
-    <row r="123" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.3218390673415603E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3">
-        <f t="shared" si="20"/>
-        <v>3.5595230953799524</v>
+        <f t="shared" si="21"/>
+        <v>138.26711486142207</v>
       </c>
       <c r="I123" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.2593780427317585E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.2848043365545062E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3">
-        <f t="shared" si="20"/>
-        <v>3.544585037466661</v>
+        <f t="shared" si="21"/>
+        <v>137.68344435526149</v>
       </c>
       <c r="I124" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.223401555514426E-3</v>
-      </c>
-    </row>
-    <row r="125" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.2483989004670408E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3">
-        <f t="shared" si="20"/>
-        <v>3.5298334729370051</v>
+        <f t="shared" si="21"/>
+        <v>137.10710314096625</v>
       </c>
       <c r="I125" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.1880276959441768E-3</v>
-      </c>
-    </row>
-    <row r="126" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.2126068554507517E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3">
-        <f t="shared" si="20"/>
-        <v>3.5152645535907374</v>
+        <f t="shared" si="21"/>
+        <v>136.53793910773899</v>
       </c>
       <c r="I126" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.1532414488888395E-3</v>
-      </c>
-    </row>
-    <row r="127" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.177412829268346E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3">
-        <f t="shared" si="20"/>
-        <v>3.5008745414795155</v>
+        <f t="shared" si="21"/>
+        <v>135.97580452778206</v>
       </c>
       <c r="I127" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.1190282939104952E-3</v>
-      </c>
-    </row>
-    <row r="128" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.1428019590641421E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3">
-        <f t="shared" si="20"/>
-        <v>3.486659804878856</v>
+        <f t="shared" si="21"/>
+        <v>135.42055589525427</v>
       </c>
       <c r="I128" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.0853741850598027E-3</v>
-      </c>
-    </row>
-    <row r="129" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.1087598704394662E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3">
-        <f t="shared" si="20"/>
-        <v>3.472616814438493</v>
+        <f t="shared" si="21"/>
+        <v>134.87205377240082</v>
       </c>
       <c r="I129" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.0522655316526206E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.075272657551041E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3">
-        <f t="shared" si="20"/>
-        <v>3.4587421395018878</v>
+        <f t="shared" si="21"/>
+        <v>134.33016264248175</v>
       </c>
       <c r="I130" s="2">
-        <f t="shared" si="21"/>
-        <v>-4.0196891799736487E-3</v>
-      </c>
-    </row>
-    <row r="131" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.0423268641745285E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3">
-        <f t="shared" si="20"/>
-        <v>3.4450324445861664</v>
+        <f t="shared" si="21"/>
+        <v>133.79475076914684</v>
       </c>
       <c r="I131" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.9876323958553655E-3</v>
-      </c>
-    </row>
-    <row r="132" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-4.0099094656790221E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3">
-        <f t="shared" si="20"/>
-        <v>3.4314844860142935</v>
+        <f t="shared" si="21"/>
+        <v>133.26569006192568</v>
       </c>
       <c r="I132" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.9560828480837791E-3</v>
-      </c>
-    </row>
-    <row r="133" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.9780078518618046E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3">
-        <f t="shared" si="20"/>
-        <v>3.4180951086917593</v>
+        <f t="shared" si="21"/>
+        <v>132.74285594752098</v>
       </c>
       <c r="I133" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.9250285925855931E-3</v>
-      </c>
-    </row>
-    <row r="134" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.9466098105958303E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3">
-        <f t="shared" si="20"/>
-        <v>3.4048612430205085</v>
+        <f t="shared" si="21"/>
+        <v>132.22612724661192</v>
       </c>
       <c r="I134" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.894458057354176E-3</v>
-      </c>
-    </row>
-    <row r="135" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.915703512245401E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3917799019432593</v>
+        <f t="shared" si="21"/>
+        <v>131.71538605589041</v>
       </c>
       <c r="I135" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.8643600280743868E-3</v>
-      </c>
-    </row>
-    <row r="136" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.8852774948082685E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3788481781117499</v>
+        <f t="shared" si="21"/>
+        <v>131.21051763506998</v>
       </c>
       <c r="I136" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.8347236344087416E-3</v>
-      </c>
-    </row>
-    <row r="137" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.8553206497449442E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3660632411728213</v>
+        <f t="shared" si="21"/>
+        <v>130.71141029862133</v>
       </c>
       <c r="I137" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.8055383369096974E-3</v>
-      </c>
-    </row>
-    <row r="138" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.8258222084584467E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3534223351665831</v>
+        <f t="shared" si="21"/>
+        <v>130.21795531200272</v>
       </c>
       <c r="I138" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.7767939145249593E-3</v>
-      </c>
-    </row>
-    <row r="139" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.7967717293898957E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3409227760312343</v>
+        <f t="shared" si="21"/>
+        <v>129.73004679216609</v>
       </c>
       <c r="I139" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.7484804526646993E-3</v>
-      </c>
-    </row>
-    <row r="140" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.7681590856974969E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3285619492094072</v>
+        <f t="shared" si="21"/>
+        <v>129.24758161213268</v>
       </c>
       <c r="I140" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.7205883318014161E-3</v>
-      </c>
-    </row>
-    <row r="141" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.7399744534883563E-3</v>
+      </c>
+    </row>
+    <row r="141" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3163373073511924</v>
+        <f t="shared" si="21"/>
+        <v>128.77045930944237</v>
       </c>
       <c r="I141" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.6931082165749091E-3</v>
-      </c>
-    </row>
-    <row r="142" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.7122083005744215E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3">
-        <f t="shared" si="20"/>
-        <v>3.3042463681092635</v>
+        <f t="shared" si="21"/>
+        <v>128.29858199829272</v>
       </c>
       <c r="I142" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.6660310453764523E-3</v>
-      </c>
-    </row>
-    <row r="143" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.6848513757255009E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2922867120217667</v>
+        <f t="shared" si="21"/>
+        <v>127.83185428519305</v>
       </c>
       <c r="I143" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.6393480203877528E-3</v>
-      </c>
-    </row>
-    <row r="144" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.65789469839392E-3</v>
+      </c>
+    </row>
+    <row r="144" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2804559804788784</v>
+        <f t="shared" si="21"/>
+        <v>127.37018318796851</v>
       </c>
       <c r="I144" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.613050598051698E-3</v>
-      </c>
-    </row>
-    <row r="145" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.6313295488868504E-3</v>
+      </c>
+    </row>
+    <row r="145" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3">
-        <f t="shared" si="20"/>
-        <v>3.268751873769149</v>
+        <f t="shared" si="21"/>
+        <v>126.91347805795824</v>
       </c>
       <c r="I145" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.587130479953213E-3</v>
-      </c>
-    </row>
-    <row r="146" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.6051474589637012E-3</v>
+      </c>
+    </row>
+    <row r="146" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2571721492019634</v>
+        <f t="shared" si="21"/>
+        <v>126.4616505052596</v>
       </c>
       <c r="I146" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.5615796040897739E-3</v>
-      </c>
-    </row>
-    <row r="147" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.5793402028372993E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2457146193026323</v>
+        <f t="shared" si="21"/>
+        <v>126.01461432687869</v>
       </c>
       <c r="I147" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.5363901365123122E-3</v>
-      </c>
-    </row>
-    <row r="148" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.5538997885587609E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2343771500768246</v>
+        <f t="shared" si="21"/>
+        <v>125.57228543765449</v>
       </c>
       <c r="I148" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.511554463318277E-3</v>
-      </c>
-    </row>
-    <row r="149" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.5288184497671063E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2231576593412079</v>
+        <f t="shared" si="21"/>
+        <v>125.13458180383101</v>
       </c>
       <c r="I149" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.487065182979694E-3</v>
-      </c>
-    </row>
-    <row r="150" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.5040886377857273E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2120541151173359</v>
+        <f t="shared" si="21"/>
+        <v>124.70142337915831</v>
       </c>
       <c r="I150" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.4629150989899647E-3</v>
-      </c>
-    </row>
-    <row r="151" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.4797030140488166E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3">
-        <f t="shared" si="20"/>
-        <v>3.2010645340859702</v>
+        <f t="shared" si="21"/>
+        <v>124.27273204340933</v>
       </c>
       <c r="I151" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.4390972128140701E-3</v>
-      </c>
-    </row>
-    <row r="152" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.4556544428417982E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I152" s="2">
-        <f t="shared" si="21"/>
-        <v>-3.4156047171276767E-3</v>
-      </c>
-    </row>
-    <row r="153" spans="5:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>-3.4319359843406703E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I153" s="2"/>
     </row>
-    <row r="154" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I154" s="2"/>
     </row>
-    <row r="155" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I155" s="2"/>
     </row>
-    <row r="156" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I156" s="2"/>
     </row>
-    <row r="157" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I157" s="2"/>
     </row>
-    <row r="158" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I158" s="2"/>
     </row>
-    <row r="159" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I159" s="2"/>
     </row>
-    <row r="160" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I160" s="2"/>
     </row>
-    <row r="161" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I161" s="2"/>
     </row>
-    <row r="162" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I162" s="2"/>
     </row>
-    <row r="163" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I163" s="2"/>
     </row>
-    <row r="164" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I164" s="2"/>
     </row>
-    <row r="165" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I165" s="2"/>
     </row>
-    <row r="166" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I166" s="2"/>
     </row>
-    <row r="167" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I167" s="2"/>
     </row>
-    <row r="168" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I168" s="2"/>
     </row>
-    <row r="169" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3">
-        <f t="shared" si="20"/>
-        <v>3.1901869800991673</v>
+        <f t="shared" si="21"/>
+        <v>123.84843154320548</v>
       </c>
       <c r="I169" s="2"/>
     </row>
-    <row r="170" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="I170" s="2"/>
     </row>
-    <row r="171" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="I171" s="2"/>
     </row>
-    <row r="172" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="I172" s="2"/>
     </row>
-    <row r="173" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="I173" s="2"/>
     </row>
-    <row r="174" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="I174" s="2"/>
     </row>
-    <row r="175" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="I175" s="2"/>
     </row>
-    <row r="176" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="I176" s="2"/>
     </row>
-    <row r="177" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="I177" s="2"/>
     </row>
-    <row r="178" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="I178" s="2"/>
     </row>
-    <row r="179" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="I179" s="2"/>
     </row>
-    <row r="180" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="I180" s="2"/>
     </row>
-    <row r="181" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="I181" s="2"/>
     </row>
-    <row r="182" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="I182" s="2"/>
     </row>
-    <row r="183" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="I183" s="2"/>
     </row>
-    <row r="184" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="I184" s="2"/>
     </row>
-    <row r="185" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="I185" s="2"/>
     </row>
-    <row r="186" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="I186" s="2"/>
     </row>
-    <row r="187" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="I187" s="2"/>
     </row>
-    <row r="188" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="I188" s="2"/>
     </row>
-    <row r="189" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="I189" s="2"/>
     </row>
-    <row r="190" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="I190" s="2"/>
     </row>
-    <row r="191" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="I191" s="2"/>
     </row>
-    <row r="192" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="I192" s="2"/>
     </row>
-    <row r="193" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="I193" s="2"/>
     </row>
-    <row r="194" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="I194" s="2"/>
     </row>
-    <row r="195" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="I195" s="2"/>
     </row>
-    <row r="196" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="I196" s="2"/>
     </row>
-    <row r="197" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="I197" s="2"/>
     </row>
-    <row r="198" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="I198" s="2"/>
     </row>
-    <row r="199" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="I199" s="2"/>
     </row>
-    <row r="200" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="I200" s="2"/>
     </row>
-    <row r="201" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="I201" s="2"/>
     </row>
-    <row r="202" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="I202" s="2"/>
     </row>
-    <row r="203" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="I203" s="2"/>
     </row>
-    <row r="204" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="I204" s="2"/>
     </row>
-    <row r="205" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="I205" s="2"/>
     </row>
-    <row r="206" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="I206" s="2"/>
     </row>
-    <row r="207" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="I207" s="2"/>
     </row>
-    <row r="208" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="I208" s="2"/>
     </row>
-    <row r="209" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="I209" s="2"/>
     </row>
-    <row r="210" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="I210" s="2"/>
     </row>
-    <row r="211" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="I211" s="2"/>
     </row>
-    <row r="212" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="I212" s="2"/>
     </row>
-    <row r="213" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="I213" s="2"/>
     </row>
-    <row r="214" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="I214" s="2"/>
     </row>
-    <row r="215" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="I215" s="2"/>
     </row>
-    <row r="216" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="I216" s="2"/>
     </row>
-    <row r="217" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="I217" s="2"/>
     </row>
-    <row r="218" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="I218" s="2"/>
     </row>
-    <row r="219" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="I219" s="2"/>
     </row>
-    <row r="220" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="I220" s="2"/>
     </row>
-    <row r="221" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
       <c r="I221" s="2"/>
     </row>
-    <row r="222" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="I222" s="2"/>
     </row>
-    <row r="223" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="I223" s="2"/>
     </row>
-    <row r="224" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="I224" s="2"/>
     </row>
-    <row r="225" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="I225" s="2"/>
     </row>
-    <row r="226" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="I226" s="2"/>
     </row>
-    <row r="227" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="I227" s="2"/>
     </row>
-    <row r="228" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="I228" s="2"/>
     </row>
-    <row r="229" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="I229" s="2"/>
     </row>
-    <row r="230" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
       <c r="I230" s="2"/>
     </row>
-    <row r="231" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="I231" s="2"/>
     </row>
-    <row r="232" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
       <c r="I232" s="2"/>
     </row>
-    <row r="233" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
       <c r="I233" s="2"/>
     </row>
-    <row r="234" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="I234" s="2"/>
     </row>
-    <row r="235" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
       <c r="I235" s="2"/>
     </row>
-    <row r="236" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="I236" s="2"/>
     </row>
-    <row r="237" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
       <c r="I237" s="2"/>
     </row>
-    <row r="238" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
       <c r="I238" s="2"/>
     </row>
-    <row r="239" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="I239" s="2"/>
     </row>
-    <row r="240" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="I240" s="2"/>
     </row>
-    <row r="241" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="I241" s="2"/>
     </row>
-    <row r="242" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="I242" s="2"/>
     </row>
-    <row r="243" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="I243" s="2"/>
     </row>
-    <row r="244" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="I244" s="2"/>
     </row>
-    <row r="245" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="I245" s="2"/>
     </row>
-    <row r="246" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="I246" s="2"/>
     </row>
-    <row r="247" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="I247" s="2"/>
     </row>
-    <row r="248" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
       <c r="I248" s="2"/>
     </row>
-    <row r="249" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
       <c r="I249" s="2"/>
     </row>
-    <row r="250" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="I250" s="2"/>
     </row>
-    <row r="251" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="I251" s="2"/>
     </row>
-    <row r="252" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
       <c r="I252" s="2"/>
     </row>
-    <row r="253" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
       <c r="I253" s="2"/>
     </row>
-    <row r="254" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
       <c r="I254" s="2"/>
     </row>
-    <row r="255" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
       <c r="I255" s="2"/>
     </row>
-    <row r="256" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
       <c r="I256" s="2"/>
     </row>
-    <row r="257" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
       <c r="I257" s="2"/>
     </row>
-    <row r="258" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
       <c r="I258" s="2"/>
     </row>
-    <row r="259" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
       <c r="I259" s="2"/>
     </row>
-    <row r="260" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
       <c r="I260" s="2"/>
     </row>
-    <row r="261" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
       <c r="I261" s="2"/>
     </row>
-    <row r="262" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
       <c r="I262" s="2"/>
     </row>
-    <row r="263" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
       <c r="I263" s="2"/>
     </row>
-    <row r="264" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
       <c r="I264" s="2"/>
     </row>
-    <row r="265" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
       <c r="I265" s="2"/>
     </row>
-    <row r="266" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
       <c r="I266" s="2"/>
     </row>
-    <row r="267" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
       <c r="I267" s="2"/>
     </row>
-    <row r="268" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
       <c r="I268" s="2"/>
     </row>
-    <row r="269" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
       <c r="I269" s="2"/>
     </row>
-    <row r="270" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
       <c r="I270" s="2"/>
     </row>
-    <row r="271" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
       <c r="I271" s="2"/>
     </row>
-    <row r="272" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
       <c r="I272" s="2"/>
     </row>
-    <row r="273" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
       <c r="I273" s="2"/>
     </row>
-    <row r="274" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="I274" s="2"/>
     </row>
-    <row r="275" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
       <c r="I275" s="2"/>
     </row>
-    <row r="276" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
       <c r="I276" s="2"/>
     </row>
-    <row r="277" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
       <c r="I277" s="2"/>
     </row>
-    <row r="278" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
       <c r="I278" s="2"/>
     </row>
-    <row r="279" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
       <c r="I279" s="2"/>
     </row>
-    <row r="280" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
       <c r="I280" s="2"/>
     </row>
-    <row r="281" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
       <c r="I281" s="2"/>
     </row>
-    <row r="282" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
       <c r="I282" s="2"/>
     </row>
-    <row r="283" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
       <c r="I283" s="2"/>
     </row>
-    <row r="284" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
       <c r="I284" s="2"/>
     </row>
-    <row r="285" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
       <c r="I285" s="2"/>
     </row>
-    <row r="286" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
       <c r="I286" s="2"/>
     </row>
-    <row r="287" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
       <c r="I287" s="2"/>
     </row>
-    <row r="288" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
       <c r="I288" s="2"/>
     </row>
-    <row r="289" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
       <c r="I289" s="2"/>
     </row>
-    <row r="290" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
       <c r="I290" s="2"/>
     </row>
-    <row r="291" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
       <c r="I291" s="2"/>
     </row>
-    <row r="292" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
       <c r="I292" s="2"/>
     </row>
-    <row r="293" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
       <c r="I293" s="2"/>
     </row>
-    <row r="294" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
       <c r="I294" s="2"/>
     </row>
-    <row r="295" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
       <c r="I295" s="2"/>
     </row>
-    <row r="296" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
       <c r="I296" s="2"/>
     </row>
-    <row r="297" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
       <c r="I297" s="2"/>
     </row>
-    <row r="298" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
       <c r="I298" s="2"/>
     </row>
-    <row r="299" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
       <c r="I299" s="2"/>
     </row>
-    <row r="300" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="I300" s="2"/>
     </row>
-    <row r="301" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
       <c r="I301" s="2"/>
     </row>
-    <row r="302" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
       <c r="I302" s="2"/>
     </row>
-    <row r="303" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="I303" s="2"/>
     </row>
-    <row r="304" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
       <c r="I304" s="2"/>
     </row>
-    <row r="305" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
       <c r="I305" s="2"/>
     </row>
-    <row r="306" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
       <c r="I306" s="2"/>
     </row>
-    <row r="307" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
       <c r="I307" s="2"/>
     </row>
-    <row r="308" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
       <c r="I308" s="2"/>
     </row>
-    <row r="309" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
       <c r="I309" s="2"/>
     </row>
-    <row r="310" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
       <c r="I310" s="2"/>
     </row>
-    <row r="311" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
       <c r="I311" s="2"/>
     </row>
-    <row r="312" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
       <c r="I312" s="2"/>
     </row>
-    <row r="313" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
       <c r="I313" s="2"/>
     </row>
-    <row r="314" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
       <c r="I314" s="2"/>
     </row>
-    <row r="315" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
       <c r="I315" s="2"/>
     </row>
-    <row r="316" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="I316" s="2"/>
     </row>
-    <row r="317" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
       <c r="I317" s="2"/>
     </row>
-    <row r="318" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
       <c r="I318" s="2"/>
     </row>
-    <row r="319" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
       <c r="I319" s="2"/>
     </row>
-    <row r="320" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
       <c r="I320" s="2"/>
     </row>
-    <row r="321" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
       <c r="I321" s="2"/>
     </row>
-    <row r="322" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
       <c r="I322" s="2"/>
     </row>
-    <row r="323" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
       <c r="I323" s="2"/>
     </row>
-    <row r="324" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
       <c r="I324" s="2"/>
     </row>
-    <row r="325" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
       <c r="I325" s="2"/>
     </row>
-    <row r="326" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
       <c r="I326" s="2"/>
     </row>
-    <row r="327" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
       <c r="I327" s="2"/>
     </row>
-    <row r="328" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
       <c r="I328" s="2"/>
     </row>
-    <row r="329" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
       <c r="I329" s="2"/>
     </row>
-    <row r="330" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
       <c r="I330" s="2"/>
     </row>
-    <row r="331" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
       <c r="I331" s="2"/>
     </row>
-    <row r="332" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="I332" s="2"/>
     </row>
-    <row r="333" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
       <c r="I333" s="2"/>
     </row>
-    <row r="334" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
       <c r="I334" s="2"/>
     </row>
-    <row r="335" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
       <c r="I335" s="2"/>
     </row>
-    <row r="336" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
       <c r="I336" s="2"/>
     </row>
-    <row r="337" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
       <c r="I337" s="2"/>
     </row>
-    <row r="338" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
       <c r="I338" s="2"/>
     </row>
-    <row r="339" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
       <c r="I339" s="2"/>
     </row>
-    <row r="340" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
       <c r="I340" s="2"/>
     </row>
-    <row r="341" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
       <c r="I341" s="2"/>
     </row>
-    <row r="342" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
       <c r="I342" s="2"/>
     </row>
-    <row r="343" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
       <c r="I343" s="2"/>
     </row>
-    <row r="344" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
       <c r="I344" s="2"/>
     </row>
-    <row r="345" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
       <c r="I345" s="2"/>
@@ -11050,144 +11270,144 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>500</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>A1/60</f>
         <v>8.3333333333333339</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1.5</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>A7/A5/A3</f>
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>400/1</f>
         <v>400</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>A2*A3*A5</f>
         <v>5000</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>1800*2</f>
         <v>3600</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>A2*A7</f>
         <v>30000.000000000004</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>A3/A7</f>
         <v>4.1666666666666669E-4</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <f>A14/A5</f>
         <v>0.05</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f>A15/A11</f>
         <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>1366/100000</f>
         <v>1.366E-2</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>A2*A18</f>
         <v>0.11383333333333334</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>A19*A7</f>
         <v>409.8</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>A20*A11</f>
         <v>0.17075000000000001</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -11198,40 +11418,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <f>10/2</f>
@@ -11246,9 +11466,9 @@
         <v>2048000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <v>-2.5</v>
@@ -11264,9 +11484,9 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7">
         <f>12/2</f>
@@ -11287,9 +11507,9 @@
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>-4.5</v>
@@ -11305,9 +11525,9 @@
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B9">
         <v>-1.99</v>
@@ -11332,9 +11552,9 @@
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B10">
         <v>-2.2450000000000001</v>
@@ -11355,9 +11575,9 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <f>B5+B9</f>
@@ -11379,9 +11599,9 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B12">
         <f>B6+B10</f>
@@ -11398,9 +11618,9 @@
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B13">
         <f>-(B5+B9)</f>
@@ -11417,9 +11637,9 @@
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B14">
         <f>-(B6+B10)</f>
@@ -11437,9 +11657,9 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
     </row>
-    <row r="15" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B15">
         <f>SQRT(B9*B9+B10*B10)</f>
@@ -11460,9 +11680,9 @@
       </c>
       <c r="L15" s="10"/>
     </row>
-    <row r="16" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <f>SQRT(B15*B15/2)</f>
@@ -11483,7 +11703,7 @@
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
     </row>
-    <row r="17" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
@@ -11491,9 +11711,9 @@
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
     </row>
-    <row r="18" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B18">
         <f>B5+B13</f>
@@ -11518,9 +11738,9 @@
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
     </row>
-    <row r="19" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B19">
         <f>B6+B14</f>
@@ -11541,9 +11761,9 @@
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
     </row>
-    <row r="20" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <f>B7+B13</f>
@@ -11564,9 +11784,9 @@
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
     </row>
-    <row r="21" spans="1:12" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <f>B8+B14</f>
@@ -11587,7 +11807,7 @@
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
@@ -11595,7 +11815,7 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
@@ -11613,35 +11833,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="6.88671875" customWidth="1"/>
-    <col min="11" max="11" width="48.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" customWidth="1"/>
+    <col min="11" max="11" width="48.28515625" customWidth="1"/>
     <col min="12" max="12" width="5" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="4.44140625" customWidth="1"/>
-    <col min="15" max="15" width="3.33203125" customWidth="1"/>
-    <col min="16" max="16" width="5.21875" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" customWidth="1"/>
-    <col min="18" max="18" width="21.109375" customWidth="1"/>
-    <col min="19" max="19" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.21875" customWidth="1"/>
-    <col min="23" max="23" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="7.28515625" customWidth="1"/>
+    <col min="14" max="14" width="4.42578125" customWidth="1"/>
+    <col min="15" max="15" width="3.28515625" customWidth="1"/>
+    <col min="16" max="16" width="5.28515625" customWidth="1"/>
+    <col min="17" max="17" width="8.85546875" customWidth="1"/>
+    <col min="18" max="18" width="21.140625" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" customWidth="1"/>
     <col min="25" max="25" width="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.21875" customWidth="1"/>
-    <col min="30" max="30" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.28515625" customWidth="1"/>
+    <col min="30" max="30" width="4.7109375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="S1">
         <v>7</v>
@@ -11655,18 +11875,18 @@
         <v>784</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" t="s">
         <v>78</v>
-      </c>
-      <c r="F2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" t="s">
-        <v>81</v>
       </c>
       <c r="K2" s="4">
         <f>600/8</f>
@@ -11679,7 +11899,7 @@
         <v>3750</v>
       </c>
       <c r="R2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S2">
         <v>4</v>
@@ -11689,9 +11909,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <f>-S1</f>
@@ -11702,9 +11922,9 @@
         <v>-159</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <f>S2</f>
@@ -11731,58 +11951,58 @@
         <v>-208</v>
       </c>
       <c r="L4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="V4" s="22"/>
       <c r="W4" s="22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B5">
         <f>(1+2*B3)*B4*B4</f>
         <v>-208</v>
       </c>
       <c r="L5" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="N5" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="Q5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="N5" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" s="24" t="s">
+      <c r="R5" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="P5" s="24" t="s">
+      <c r="S5" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="Q5" s="24" t="s">
+      <c r="T5" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="R5" s="24" t="s">
+      <c r="U5" s="25" t="s">
         <v>90</v>
-      </c>
-      <c r="S5" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="T5" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="U5" s="25" t="s">
-        <v>93</v>
       </c>
       <c r="W5" s="22"/>
       <c r="X5" s="26"/>
       <c r="Y5" s="26"/>
     </row>
-    <row r="6" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6">
         <f>B3*B3</f>
@@ -11831,15 +12051,15 @@
         <v>-159</v>
       </c>
       <c r="AG6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AH6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11886,10 +12106,10 @@
         <v>-12</v>
       </c>
       <c r="AA7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="L8" s="27">
         <v>1</v>
       </c>
@@ -11932,10 +12152,10 @@
         <v>57</v>
       </c>
       <c r="AA8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="L9" s="27">
         <v>1</v>
       </c>
@@ -11978,10 +12198,10 @@
         <v>256</v>
       </c>
       <c r="AA9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="L10" s="27">
         <v>1</v>
       </c>
@@ -12024,7 +12244,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K11">
         <f>57+(-245)</f>
         <v>-188</v>
@@ -12071,7 +12291,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K12">
         <f>-188-57</f>
         <v>-245</v>
@@ -12118,7 +12338,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K13">
         <f>7*7*2</f>
         <v>98</v>
@@ -12165,13 +12385,13 @@
         <v>441</v>
       </c>
       <c r="Z13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AA13" s="30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K14">
         <f>K12+K13</f>
         <v>-147</v>
@@ -12218,10 +12438,10 @@
         <v>457</v>
       </c>
       <c r="AA14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K15">
         <f>K12-K13</f>
         <v>-343</v>
@@ -12239,12 +12459,12 @@
       <c r="V15" s="28"/>
       <c r="W15" s="28"/>
       <c r="AA15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="L16" s="31" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M16" s="28"/>
       <c r="N16" s="28"/>
@@ -12258,58 +12478,58 @@
       <c r="V16" s="28"/>
       <c r="W16" s="28"/>
       <c r="AA16" s="30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="L17" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="P17" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q17" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="R17" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="T17" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="U17" s="32" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="L17" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="M17" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="O17" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="P17" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q17" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="R17" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="S17" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="T17" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="U17" s="32" t="s">
-        <v>104</v>
       </c>
       <c r="V17" s="22"/>
       <c r="W17" s="30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Z17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF17" t="s">
         <v>105</v>
       </c>
-      <c r="AA17" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>107</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L18" s="27">
         <v>1</v>
       </c>
@@ -12371,7 +12591,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L19" s="27">
         <v>1</v>
       </c>
@@ -12433,9 +12653,9 @@
         <v>-64</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="K20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L20" s="27">
         <v>1</v>
@@ -12498,7 +12718,7 @@
         <v>-144</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L21" s="27">
         <v>1</v>
       </c>
@@ -12560,9 +12780,9 @@
         <v>-256</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L22" s="27">
         <v>1</v>
@@ -12614,7 +12834,7 @@
         <v>-332</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L23" s="27">
         <v>1</v>
       </c>
@@ -12665,9 +12885,9 @@
         <v>-188</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L24" s="27">
         <v>1</v>
@@ -12719,7 +12939,7 @@
         <v>-159</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L25" s="27">
         <v>1</v>
       </c>
@@ -12770,7 +12990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L26" s="27">
         <v>1</v>
       </c>
@@ -12821,9 +13041,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L27" s="31"/>
       <c r="M27" s="28"/>
@@ -12838,7 +13058,7 @@
       <c r="V27" s="28"/>
       <c r="W27" s="28"/>
     </row>
-    <row r="28" spans="1:32" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L28" s="31"/>
       <c r="M28" s="28"/>
       <c r="N28" s="28"/>
@@ -12852,15 +13072,15 @@
       <c r="V28" s="28"/>
       <c r="W28" s="28"/>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L29" s="31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M29" s="28"/>
       <c r="N29" s="28"/>
@@ -12874,53 +13094,53 @@
       <c r="V29" s="28"/>
       <c r="W29" s="28"/>
       <c r="AA29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>113</v>
+      </c>
+      <c r="L30" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="M30" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N30" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="P30" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q30" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="R30" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="S30" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="T30" s="22" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="F30" t="s">
+      <c r="U30" s="32" t="s">
         <v>116</v>
-      </c>
-      <c r="L30" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="M30" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="N30" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="O30" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="P30" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q30" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="R30" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="S30" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="T30" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="U30" s="32" t="s">
-        <v>119</v>
       </c>
       <c r="V30" s="22"/>
       <c r="W30" s="22"/>
       <c r="Z30" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AA30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="L31" s="27">
         <v>-1</v>
       </c>
@@ -12963,18 +13183,18 @@
         <v>-159</v>
       </c>
       <c r="AA31" s="30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AD31" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L32" s="27">
         <v>-1</v>
@@ -13018,18 +13238,18 @@
         <v>-12</v>
       </c>
       <c r="AA32" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="6:27" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="6:27" x14ac:dyDescent="0.25">
       <c r="F33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L33" s="27">
         <v>-1</v>
@@ -13073,15 +13293,15 @@
         <v>57</v>
       </c>
       <c r="AA33" s="30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="6:27" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="6:27" x14ac:dyDescent="0.25">
       <c r="I34" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K34" s="34" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L34" s="27">
         <v>-1</v>
@@ -13125,12 +13345,12 @@
         <v>256</v>
       </c>
     </row>
-    <row r="35" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="6:27" x14ac:dyDescent="0.25">
       <c r="I35" s="34" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K35" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L35" s="27">
         <v>-1</v>
@@ -13174,9 +13394,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="6:27" x14ac:dyDescent="0.25">
       <c r="I36" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L36" s="27">
         <v>-1</v>
@@ -13220,9 +13440,9 @@
         <v>505</v>
       </c>
     </row>
-    <row r="37" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="6:27" x14ac:dyDescent="0.25">
       <c r="I37" s="34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L37" s="27">
         <v>-1</v>
@@ -13266,7 +13486,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L38" s="27">
         <v>-1</v>
       </c>
@@ -13309,12 +13529,12 @@
         <v>441</v>
       </c>
     </row>
-    <row r="39" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="6:27" x14ac:dyDescent="0.25">
       <c r="G39" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J39" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L39" s="27">
         <v>-1</v>
@@ -13358,12 +13578,12 @@
         <v>457</v>
       </c>
     </row>
-    <row r="40" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="6:27" x14ac:dyDescent="0.25">
       <c r="G40" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L40" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="M40" s="28"/>
       <c r="N40" s="28"/>
@@ -13377,53 +13597,53 @@
       <c r="V40" s="28"/>
       <c r="W40" s="28"/>
       <c r="Z40" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>135</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="M41" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="N41" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O41" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="P41" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q41" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="R41" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="S41" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="T41" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="U41" s="32" t="s">
         <v>137</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="6:27" x14ac:dyDescent="0.3">
-      <c r="G41" t="s">
-        <v>138</v>
-      </c>
-      <c r="L41" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="M41" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="N41" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="O41" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="P41" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q41" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="R41" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="S41" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="T41" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="U41" s="32" t="s">
-        <v>140</v>
       </c>
       <c r="V41" s="22"/>
       <c r="W41" s="22"/>
       <c r="AA41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" spans="6:27" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L42" s="27">
         <v>-1</v>
       </c>
@@ -13466,10 +13686,10 @@
         <v>-327</v>
       </c>
       <c r="AA42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="6:27" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L43" s="27">
         <v>-1</v>
       </c>
@@ -13512,10 +13732,10 @@
         <v>-279</v>
       </c>
       <c r="AA43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="6:27" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L44" s="27">
         <v>-1</v>
       </c>
@@ -13558,10 +13778,10 @@
         <v>-199</v>
       </c>
       <c r="AA44" s="30" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="6:27" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L45" s="27">
         <v>-1</v>
       </c>
@@ -13604,7 +13824,7 @@
         <v>-87</v>
       </c>
     </row>
-    <row r="46" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L46" s="27">
         <v>-1</v>
       </c>
@@ -13647,7 +13867,7 @@
         <v>-188</v>
       </c>
     </row>
-    <row r="47" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L47" s="27">
         <v>-1</v>
       </c>
@@ -13690,7 +13910,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="48" spans="6:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="6:27" x14ac:dyDescent="0.25">
       <c r="L48" s="27">
         <v>-1</v>
       </c>
@@ -13733,7 +13953,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="12:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L49" s="27">
         <v>-1</v>
       </c>
@@ -13776,7 +13996,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="50" spans="12:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="12:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L50" s="35">
         <v>-1</v>
       </c>
@@ -13828,7 +14048,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/rampup.xlsx
+++ b/rampup.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="151">
   <si>
     <t>pps</t>
   </si>
@@ -906,6 +906,15 @@
   <si>
     <t>p1 - delay period for the initial step:</t>
   </si>
+  <si>
+    <t>mm/min for 2.5mm screw</t>
+  </si>
+  <si>
+    <t>arr delta</t>
+  </si>
+  <si>
+    <t>rev/s</t>
+  </si>
 </sst>
 </file>
 
@@ -920,7 +929,7 @@
     <numFmt numFmtId="168" formatCode="0.00000000"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.0\ _₽_-;\-* #,##0.0\ _₽_-;_-* &quot;-&quot;?\ _₽_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="181" formatCode="0.0000000000000"/>
+    <numFmt numFmtId="171" formatCode="0.0000000000000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1147,7 +1156,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1217,7 +1226,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1388,7 +1399,7 @@
           </c:trendline>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$J$2:$J$35</c:f>
+              <c:f>Лист1!$K$2:$K$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
@@ -1519,7 +1530,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$M$2:$M$35</c:f>
+              <c:f>Лист1!$N$2:$N$35</c:f>
               <c:numCache>
                 <c:formatCode>_-* #\ ##0.0\ _₽_-;\-* #\ ##0.0\ _₽_-;_-* "-"?\ _₽_-;_-@_-</c:formatCode>
                 <c:ptCount val="34"/>
@@ -1629,11 +1640,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1409098560"/>
-        <c:axId val="-1409092576"/>
+        <c:axId val="551630656"/>
+        <c:axId val="551634464"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1409098560"/>
+        <c:axId val="551630656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1689,12 +1700,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409092576"/>
+        <c:crossAx val="551634464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1409092576"/>
+        <c:axId val="551634464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1751,7 +1762,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409098560"/>
+        <c:crossAx val="551630656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2413,11 +2424,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1409087136"/>
-        <c:axId val="-1409085504"/>
+        <c:axId val="551632288"/>
+        <c:axId val="551635008"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1409087136"/>
+        <c:axId val="551632288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2474,12 +2485,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409085504"/>
+        <c:crossAx val="551635008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1409085504"/>
+        <c:axId val="551635008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2536,7 +2547,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409087136"/>
+        <c:crossAx val="551632288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2685,7 +2696,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$R$41:$R$70</c:f>
+              <c:f>Лист1!$U$41:$U$70</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="30"/>
@@ -2792,11 +2803,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1409090400"/>
-        <c:axId val="-1409084960"/>
+        <c:axId val="551636640"/>
+        <c:axId val="551639904"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1409090400"/>
+        <c:axId val="551636640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2852,12 +2863,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409084960"/>
+        <c:crossAx val="551639904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1409084960"/>
+        <c:axId val="551639904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2914,7 +2925,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409090400"/>
+        <c:crossAx val="551636640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2978,7 +2989,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3019,7 +3029,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Лист1!$M$1</c:f>
+              <c:f>Лист1!$N$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -3051,7 +3061,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$M$2:$M$48</c:f>
+              <c:f>Лист1!$N$2:$N$48</c:f>
               <c:numCache>
                 <c:formatCode>_-* #\ ##0.0\ _₽_-;\-* #\ ##0.0\ _₽_-;_-* "-"?\ _₽_-;_-@_-</c:formatCode>
                 <c:ptCount val="47"/>
@@ -3200,11 +3210,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-1409089856"/>
-        <c:axId val="-1409089312"/>
+        <c:axId val="551638816"/>
+        <c:axId val="551631744"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-1409089856"/>
+        <c:axId val="551638816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3260,12 +3270,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409089312"/>
+        <c:crossAx val="551631744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-1409089312"/>
+        <c:axId val="551631744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3322,7 +3332,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1409089856"/>
+        <c:crossAx val="551638816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5599,13 +5609,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>426358</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>145143</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>79994</xdr:rowOff>
@@ -5629,13 +5639,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>253997</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>147864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>426355</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>169635</xdr:rowOff>
@@ -5659,16 +5669,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>848338</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>55069</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>388510</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>87914</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>430759</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>177773</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>176211</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>21759</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5689,13 +5699,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>26529</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>434851</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>342380</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>25043</xdr:rowOff>
@@ -6261,7 +6271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R345"/>
+  <dimension ref="A1:U345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -6269,19 +6279,19 @@
     <col min="3" max="4" width="12.28515625" customWidth="1"/>
     <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="19.5703125" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" customWidth="1"/>
+    <col min="8" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="16" width="19.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -6300,15 +6310,22 @@
       <c r="H1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="11" t="s">
+      <c r="I1" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O1" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="P1" s="19"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6324,20 +6341,27 @@
       <c r="F2" s="15"/>
       <c r="G2" s="21"/>
       <c r="H2" s="12"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="4"/>
-      <c r="L2" t="str">
-        <f t="shared" ref="L2:L48" si="0">CONCATENATE("0x",DEC2HEX(G2*POWER(2,24),8),",")</f>
+      <c r="I2" s="40"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="4"/>
+      <c r="M2" t="str">
+        <f t="shared" ref="M2:M48" si="0">CONCATENATE("0x",DEC2HEX(G2*POWER(2,24),8),",")</f>
         <v>0x00000000,</v>
       </c>
-      <c r="M2" s="19"/>
-      <c r="N2">
+      <c r="N2" s="19"/>
+      <c r="O2" s="19">
+        <v>4</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q2">
         <f>10/0.00625</f>
         <v>1600</v>
       </c>
-      <c r="O2" s="17"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -6357,18 +6381,21 @@
       <c r="F3" s="15"/>
       <c r="G3" s="21"/>
       <c r="H3" s="13"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:K5" si="2">J3-J2</f>
+      <c r="I3" s="40"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="4">
+        <f t="shared" ref="L3:L5" si="2">K3-K2</f>
         <v>0</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <f t="shared" si="0"/>
         <v>0x00000000,</v>
       </c>
-      <c r="M3" s="19"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="D4" s="3">
         <f t="shared" si="1"/>
@@ -6380,18 +6407,23 @@
       <c r="F4" s="15"/>
       <c r="G4" s="21"/>
       <c r="H4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="4">
+      <c r="I4" s="40"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <f t="shared" si="0"/>
         <v>0x00000000,</v>
       </c>
-      <c r="M4" s="19"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f>72000000/(240)</f>
+        <v>300000</v>
+      </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
         <v>-1436.7394278317272</v>
@@ -6411,24 +6443,33 @@
         <f>ROUND(G5,0)</f>
         <v>1437</v>
       </c>
-      <c r="J5" s="4">
-        <f t="shared" ref="J4:J35" si="3">$B$12/H5</f>
+      <c r="I5" s="41"/>
+      <c r="K5" s="4">
+        <f>$B$12/H5</f>
         <v>208.76826722338205</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <f t="shared" si="2"/>
         <v>208.76826722338205</v>
       </c>
-      <c r="L5" t="e">
+      <c r="M5" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M5" s="19">
-        <f t="shared" ref="M2:M48" si="4">$B$12/G5</f>
+      <c r="N5" s="19">
+        <f t="shared" ref="N5:N48" si="3">$B$12/G5</f>
         <v>208.80613017821099</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O5" s="19">
+        <f>K5*60/400*O$2</f>
+        <v>125.26096033402922</v>
+      </c>
+      <c r="P5" s="19">
+        <f>K5/400</f>
+        <v>0.52192066805845516</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -6443,43 +6484,55 @@
         <v>5</v>
       </c>
       <c r="F6" s="15">
-        <f t="shared" ref="F6:F35" si="5">F5*(1+-1*$B$22*F5*F5)</f>
+        <f t="shared" ref="F6:F35" si="4">F5*(1+-1*$B$22*F5*F5)</f>
         <v>777.68464442267782</v>
       </c>
       <c r="G6" s="21">
-        <f t="shared" ref="G6:G48" si="6">G5*(1+I6+1.5*I6*I6)</f>
+        <f t="shared" ref="G6:G48" si="5">G5*(1+J6+1.5*J6*J6)</f>
         <v>1231.1627064013815</v>
       </c>
       <c r="H6" s="8">
-        <f t="shared" ref="H6:H35" si="7">ROUND(G6,0)</f>
+        <f t="shared" ref="H6:H35" si="6">ROUND(G6,0)</f>
         <v>1231</v>
       </c>
-      <c r="I6" s="2">
-        <f t="shared" ref="I6:I48" si="8">-1*$B$22*G5*G5</f>
+      <c r="I6" s="41">
+        <f>H5-H6</f>
+        <v>206</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" ref="J6:J48" si="7">-1*$B$22*G5*G5</f>
         <v>-0.45871559633027531</v>
       </c>
-      <c r="J6" s="4">
-        <f t="shared" si="3"/>
+      <c r="K6" s="4">
+        <f t="shared" ref="K6:K69" si="8">$B$12/H6</f>
         <v>243.70430544272949</v>
       </c>
-      <c r="K6" s="4">
-        <f>J6-J5</f>
+      <c r="L6" s="4">
+        <f>K6-K5</f>
         <v>34.936038219347438</v>
       </c>
-      <c r="L6" t="e">
+      <c r="M6" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M6" s="19">
-        <f t="shared" si="4"/>
+      <c r="N6" s="19">
+        <f t="shared" si="3"/>
         <v>243.67209828576023</v>
       </c>
-      <c r="N6">
-        <f t="shared" ref="N6:N44" si="9">I6*65536</f>
+      <c r="O6" s="19">
+        <f t="shared" ref="O6:O69" si="9">K6*60/400*O$2</f>
+        <v>146.2225832656377</v>
+      </c>
+      <c r="P6" s="19">
+        <f t="shared" ref="P6:P69" si="10">K6/400</f>
+        <v>0.60926076360682369</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ref="Q6:Q44" si="11">J6*65536</f>
         <v>-30062.385321100923</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -6488,98 +6541,122 @@
         <v>239.5</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" ref="D7:D37" si="10">G6-G7</f>
+        <f t="shared" ref="D7:D37" si="12">G6-G7</f>
         <v>205.17112842206325</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" s="15">
+        <f t="shared" si="4"/>
+        <v>673.16496774998018</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v>673.16496774998018</v>
-      </c>
-      <c r="G7" s="21">
+        <v>1025.9915779793182</v>
+      </c>
+      <c r="H7" s="8">
         <f t="shared" si="6"/>
-        <v>1025.9915779793182</v>
-      </c>
-      <c r="H7" s="8">
+        <v>1026</v>
+      </c>
+      <c r="I7" s="41">
+        <f t="shared" ref="I7:I70" si="13">H6-H7</f>
+        <v>205</v>
+      </c>
+      <c r="J7" s="2">
         <f t="shared" si="7"/>
-        <v>1026</v>
-      </c>
-      <c r="I7" s="2">
+        <v>-0.33683591325190537</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="8"/>
-        <v>-0.33683591325190537</v>
-      </c>
-      <c r="J7" s="4">
-        <f t="shared" si="3"/>
         <v>292.39766081871346</v>
       </c>
-      <c r="K7" s="4">
-        <f t="shared" ref="K7:K35" si="11">J7-J6</f>
+      <c r="L7" s="4">
+        <f t="shared" ref="L7:L35" si="14">K7-K6</f>
         <v>48.69335537598397</v>
       </c>
-      <c r="L7" t="e">
+      <c r="M7" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M7" s="19">
-        <f t="shared" si="4"/>
+      <c r="N7" s="19">
+        <f t="shared" si="3"/>
         <v>292.40006101302259</v>
       </c>
-      <c r="N7">
+      <c r="O7" s="19">
         <f t="shared" si="9"/>
+        <v>175.43859649122808</v>
+      </c>
+      <c r="P7" s="19">
+        <f t="shared" si="10"/>
+        <v>0.73099415204678364</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="11"/>
         <v>-22074.87841087687</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>155.79004026137954</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" s="15">
+        <f t="shared" si="4"/>
+        <v>605.37709486456424</v>
+      </c>
+      <c r="G8" s="21">
         <f t="shared" si="5"/>
-        <v>605.37709486456424</v>
-      </c>
-      <c r="G8" s="21">
+        <v>870.20153771793866</v>
+      </c>
+      <c r="H8" s="8">
         <f t="shared" si="6"/>
-        <v>870.20153771793866</v>
-      </c>
-      <c r="H8" s="8">
+        <v>870</v>
+      </c>
+      <c r="I8" s="41">
+        <f t="shared" si="13"/>
+        <v>156</v>
+      </c>
+      <c r="J8" s="2">
         <f t="shared" si="7"/>
-        <v>870</v>
-      </c>
-      <c r="I8" s="2">
+        <v>-0.23392415957433141</v>
+      </c>
+      <c r="K8" s="4">
         <f t="shared" si="8"/>
-        <v>-0.23392415957433141</v>
-      </c>
-      <c r="J8" s="4">
-        <f t="shared" si="3"/>
         <v>344.82758620689657</v>
       </c>
-      <c r="K8" s="4">
-        <f t="shared" si="11"/>
+      <c r="L8" s="4">
+        <f t="shared" si="14"/>
         <v>52.429925388183108</v>
       </c>
-      <c r="L8" t="e">
+      <c r="M8" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M8" s="19">
-        <f t="shared" si="4"/>
+      <c r="N8" s="19">
+        <f t="shared" si="3"/>
         <v>344.74772451762777</v>
       </c>
-      <c r="N8">
+      <c r="O8" s="19">
         <f t="shared" si="9"/>
+        <v>206.89655172413794</v>
+      </c>
+      <c r="P8" s="19">
+        <f t="shared" si="10"/>
+        <v>0.86206896551724144</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="11"/>
         <v>-15330.453721863383</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -6591,50 +6668,62 @@
         <v>0</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>109.47286833583769</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" s="15">
+        <f t="shared" si="4"/>
+        <v>556.07499228878555</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v>556.07499228878555</v>
-      </c>
-      <c r="G9" s="21">
+        <v>760.72866938210097</v>
+      </c>
+      <c r="H9" s="8">
         <f t="shared" si="6"/>
-        <v>760.72866938210097</v>
-      </c>
-      <c r="H9" s="8">
+        <v>761</v>
+      </c>
+      <c r="I9" s="41">
+        <f t="shared" si="13"/>
+        <v>109</v>
+      </c>
+      <c r="J9" s="2">
         <f t="shared" si="7"/>
-        <v>761</v>
-      </c>
-      <c r="I9" s="2">
+        <v>-0.16827793694370333</v>
+      </c>
+      <c r="K9" s="4">
         <f t="shared" si="8"/>
-        <v>-0.16827793694370333</v>
-      </c>
-      <c r="J9" s="4">
-        <f t="shared" si="3"/>
         <v>394.21813403416559</v>
       </c>
-      <c r="K9" s="4">
-        <f t="shared" si="11"/>
+      <c r="L9" s="4">
+        <f t="shared" si="14"/>
         <v>49.390547827269017</v>
       </c>
-      <c r="L9" t="e">
+      <c r="M9" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M9" s="19">
-        <f t="shared" si="4"/>
+      <c r="N9" s="19">
+        <f t="shared" si="3"/>
         <v>394.35874060546962</v>
       </c>
-      <c r="N9">
+      <c r="O9" s="19">
         <f t="shared" si="9"/>
+        <v>236.53088042049933</v>
+      </c>
+      <c r="P9" s="19">
+        <f t="shared" si="10"/>
+        <v>0.98554533508541398</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="11"/>
         <v>-11028.262875542541</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -6646,50 +6735,62 @@
         <v>0</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>78.959198326622186</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" s="15">
+        <f t="shared" si="4"/>
+        <v>517.86406477110768</v>
+      </c>
+      <c r="G10" s="21">
         <f t="shared" si="5"/>
-        <v>517.86406477110768</v>
-      </c>
-      <c r="G10" s="21">
+        <v>681.76947105547879</v>
+      </c>
+      <c r="H10" s="8">
         <f t="shared" si="6"/>
-        <v>681.76947105547879</v>
-      </c>
-      <c r="H10" s="8">
+        <v>682</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" si="13"/>
+        <v>79</v>
+      </c>
+      <c r="J10" s="2">
         <f t="shared" si="7"/>
-        <v>682</v>
-      </c>
-      <c r="I10" s="2">
+        <v>-0.12860180187108042</v>
+      </c>
+      <c r="K10" s="4">
         <f t="shared" si="8"/>
-        <v>-0.12860180187108042</v>
-      </c>
-      <c r="J10" s="4">
-        <f t="shared" si="3"/>
         <v>439.88269794721407</v>
       </c>
-      <c r="K10" s="4">
-        <f t="shared" si="11"/>
+      <c r="L10" s="4">
+        <f t="shared" si="14"/>
         <v>45.664563913048482</v>
       </c>
-      <c r="L10" t="e">
+      <c r="M10" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M10" s="19">
-        <f t="shared" si="4"/>
+      <c r="N10" s="19">
+        <f t="shared" si="3"/>
         <v>440.03143692479534</v>
       </c>
-      <c r="N10">
+      <c r="O10" s="19">
         <f t="shared" si="9"/>
+        <v>263.92961876832845</v>
+      </c>
+      <c r="P10" s="19">
+        <f t="shared" si="10"/>
+        <v>1.0997067448680351</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="11"/>
         <v>-8428.0476874231263</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -6700,50 +6801,62 @@
         <v>29</v>
       </c>
       <c r="D11" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>59.509933003902347</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" s="15">
+        <f t="shared" si="4"/>
+        <v>487.00130106892351</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v>487.00130106892351</v>
-      </c>
-      <c r="G11" s="21">
+        <v>622.25953805157644</v>
+      </c>
+      <c r="H11" s="8">
         <f t="shared" si="6"/>
-        <v>622.25953805157644</v>
-      </c>
-      <c r="H11" s="8">
+        <v>622</v>
+      </c>
+      <c r="I11" s="41">
+        <f t="shared" si="13"/>
+        <v>60</v>
+      </c>
+      <c r="J11" s="2">
         <f t="shared" si="7"/>
-        <v>622</v>
-      </c>
-      <c r="I11" s="2">
+        <v>-0.1032910248140594</v>
+      </c>
+      <c r="K11" s="4">
         <f t="shared" si="8"/>
-        <v>-0.1032910248140594</v>
-      </c>
-      <c r="J11" s="4">
-        <f t="shared" si="3"/>
         <v>482.3151125401929</v>
       </c>
-      <c r="K11" s="4">
-        <f t="shared" si="11"/>
+      <c r="L11" s="4">
+        <f t="shared" si="14"/>
         <v>42.43241459297883</v>
       </c>
-      <c r="L11" t="e">
+      <c r="M11" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M11" s="19">
-        <f t="shared" si="4"/>
+      <c r="N11" s="19">
+        <f t="shared" si="3"/>
         <v>482.11394386876282</v>
       </c>
-      <c r="N11">
+      <c r="O11" s="19">
         <f t="shared" si="9"/>
+        <v>289.38906752411572</v>
+      </c>
+      <c r="P11" s="19">
+        <f t="shared" si="10"/>
+        <v>1.2057877813504823</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="11"/>
         <v>-6769.2806022141967</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -6754,146 +6867,182 @@
         <v>28</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>46.632203040454669</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" s="15">
+        <f t="shared" si="4"/>
+        <v>461.33413913067466</v>
+      </c>
+      <c r="G12" s="21">
         <f t="shared" si="5"/>
-        <v>461.33413913067466</v>
-      </c>
-      <c r="G12" s="21">
+        <v>575.62733501112177</v>
+      </c>
+      <c r="H12" s="8">
         <f t="shared" si="6"/>
-        <v>575.62733501112177</v>
-      </c>
-      <c r="H12" s="8">
+        <v>576</v>
+      </c>
+      <c r="I12" s="41">
+        <f t="shared" si="13"/>
+        <v>46</v>
+      </c>
+      <c r="J12" s="2">
         <f t="shared" si="7"/>
-        <v>576</v>
-      </c>
-      <c r="I12" s="2">
+        <v>-8.60459850435914E-2</v>
+      </c>
+      <c r="K12" s="4">
         <f t="shared" si="8"/>
-        <v>-8.60459850435914E-2</v>
-      </c>
-      <c r="J12" s="4">
-        <f t="shared" si="3"/>
         <v>520.83333333333337</v>
       </c>
-      <c r="K12" s="4">
-        <f t="shared" si="11"/>
+      <c r="L12" s="4">
+        <f t="shared" si="14"/>
         <v>38.518220793140472</v>
       </c>
-      <c r="L12" t="e">
+      <c r="M12" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M12" s="19">
-        <f t="shared" si="4"/>
+      <c r="N12" s="19">
+        <f t="shared" si="3"/>
         <v>521.17052431883496</v>
       </c>
-      <c r="N12">
+      <c r="O12" s="19">
         <f t="shared" si="9"/>
+        <v>312.50000000000006</v>
+      </c>
+      <c r="P12" s="19">
+        <f t="shared" si="10"/>
+        <v>1.3020833333333335</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="11"/>
         <v>-5639.109675816806</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>37.703580443185047</v>
       </c>
       <c r="E13">
         <v>12</v>
       </c>
       <c r="F13" s="15">
+        <f t="shared" si="4"/>
+        <v>439.51516797636657</v>
+      </c>
+      <c r="G13" s="21">
         <f t="shared" si="5"/>
-        <v>439.51516797636657</v>
-      </c>
-      <c r="G13" s="21">
+        <v>537.92375456793673</v>
+      </c>
+      <c r="H13" s="8">
         <f t="shared" si="6"/>
-        <v>537.92375456793673</v>
-      </c>
-      <c r="H13" s="8">
+        <v>538</v>
+      </c>
+      <c r="I13" s="41">
+        <f t="shared" si="13"/>
+        <v>38</v>
+      </c>
+      <c r="J13" s="2">
         <f t="shared" si="7"/>
-        <v>538</v>
-      </c>
-      <c r="I13" s="2">
+        <v>-7.363262862489027E-2</v>
+      </c>
+      <c r="K13" s="4">
         <f t="shared" si="8"/>
-        <v>-7.363262862489027E-2</v>
-      </c>
-      <c r="J13" s="4">
-        <f t="shared" si="3"/>
         <v>557.62081784386612</v>
       </c>
-      <c r="K13" s="4">
-        <f t="shared" si="11"/>
+      <c r="L13" s="4">
+        <f t="shared" si="14"/>
         <v>36.787484510532749</v>
       </c>
-      <c r="L13" t="e">
+      <c r="M13" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M13" s="19">
-        <f t="shared" si="4"/>
+      <c r="N13" s="19">
+        <f t="shared" si="3"/>
         <v>557.69985514203893</v>
       </c>
-      <c r="N13">
+      <c r="O13" s="19">
         <f t="shared" si="9"/>
+        <v>334.57249070631968</v>
+      </c>
+      <c r="P13" s="19">
+        <f t="shared" si="10"/>
+        <v>1.3940520446096654</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="11"/>
         <v>-4825.5879495608087</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>31.253591285839605</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14" s="15">
+        <f t="shared" si="4"/>
+        <v>420.64789692555138</v>
+      </c>
+      <c r="G14" s="21">
         <f t="shared" si="5"/>
-        <v>420.64789692555138</v>
-      </c>
-      <c r="G14" s="21">
+        <v>506.67016328209712</v>
+      </c>
+      <c r="H14" s="8">
         <f t="shared" si="6"/>
-        <v>506.67016328209712</v>
-      </c>
-      <c r="H14" s="8">
+        <v>507</v>
+      </c>
+      <c r="I14" s="41">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="J14" s="2">
         <f t="shared" si="7"/>
-        <v>507</v>
-      </c>
-      <c r="I14" s="2">
+        <v>-6.4302659050770178E-2</v>
+      </c>
+      <c r="K14" s="4">
         <f t="shared" si="8"/>
-        <v>-6.4302659050770178E-2</v>
-      </c>
-      <c r="J14" s="4">
-        <f t="shared" si="3"/>
         <v>591.71597633136093</v>
       </c>
-      <c r="K14" s="4">
-        <f t="shared" si="11"/>
+      <c r="L14" s="4">
+        <f t="shared" si="14"/>
         <v>34.095158487494814</v>
       </c>
-      <c r="L14" t="e">
+      <c r="M14" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M14" s="19">
-        <f t="shared" si="4"/>
+      <c r="N14" s="19">
+        <f t="shared" si="3"/>
         <v>592.10117694056908</v>
       </c>
-      <c r="N14">
+      <c r="O14" s="19">
         <f t="shared" si="9"/>
+        <v>355.02958579881653</v>
+      </c>
+      <c r="P14" s="19">
+        <f t="shared" si="10"/>
+        <v>1.4792899408284024</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="11"/>
         <v>-4214.1390635512744</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -6902,98 +7051,122 @@
         <v>99.91</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>26.430976354279949</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15" s="15">
+        <f t="shared" si="4"/>
+        <v>404.10758665094988</v>
+      </c>
+      <c r="G15" s="21">
         <f t="shared" si="5"/>
-        <v>404.10758665094988</v>
-      </c>
-      <c r="G15" s="21">
+        <v>480.23918692781717</v>
+      </c>
+      <c r="H15" s="8">
         <f t="shared" si="6"/>
-        <v>480.23918692781717</v>
-      </c>
-      <c r="H15" s="8">
+        <v>480</v>
+      </c>
+      <c r="I15" s="41">
+        <f t="shared" si="13"/>
+        <v>27</v>
+      </c>
+      <c r="J15" s="2">
         <f t="shared" si="7"/>
-        <v>480</v>
-      </c>
-      <c r="I15" s="2">
+        <v>-5.7047700968957102E-2</v>
+      </c>
+      <c r="K15" s="4">
         <f t="shared" si="8"/>
-        <v>-5.7047700968957102E-2</v>
-      </c>
-      <c r="J15" s="4">
-        <f t="shared" si="3"/>
         <v>625</v>
       </c>
-      <c r="K15" s="4">
-        <f t="shared" si="11"/>
+      <c r="L15" s="4">
+        <f t="shared" si="14"/>
         <v>33.284023668639065</v>
       </c>
-      <c r="L15" t="e">
+      <c r="M15" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M15" s="19">
-        <f t="shared" si="4"/>
+      <c r="N15" s="19">
+        <f t="shared" si="3"/>
         <v>624.68871380354847</v>
       </c>
-      <c r="N15">
+      <c r="O15" s="19">
         <f t="shared" si="9"/>
+        <v>375</v>
+      </c>
+      <c r="P15" s="19">
+        <f t="shared" si="10"/>
+        <v>1.5625</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="11"/>
         <v>-3738.6781307015726</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>147</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>22.720613327116041</v>
       </c>
       <c r="E16">
         <v>15</v>
       </c>
       <c r="F16" s="15">
+        <f t="shared" si="4"/>
+        <v>389.44270718017805</v>
+      </c>
+      <c r="G16" s="21">
         <f t="shared" si="5"/>
-        <v>389.44270718017805</v>
-      </c>
-      <c r="G16" s="21">
+        <v>457.51857360070113</v>
+      </c>
+      <c r="H16" s="8">
         <f t="shared" si="6"/>
-        <v>457.51857360070113</v>
-      </c>
-      <c r="H16" s="8">
+        <v>458</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="J16" s="2">
         <f t="shared" si="7"/>
-        <v>458</v>
-      </c>
-      <c r="I16" s="2">
+        <v>-5.1251039258020201E-2</v>
+      </c>
+      <c r="K16" s="4">
         <f t="shared" si="8"/>
-        <v>-5.1251039258020201E-2</v>
-      </c>
-      <c r="J16" s="4">
-        <f t="shared" si="3"/>
         <v>655.02183406113534</v>
       </c>
-      <c r="K16" s="4">
-        <f t="shared" si="11"/>
+      <c r="L16" s="4">
+        <f t="shared" si="14"/>
         <v>30.021834061135337</v>
       </c>
-      <c r="L16" t="e">
+      <c r="M16" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M16" s="19">
-        <f t="shared" si="4"/>
+      <c r="N16" s="19">
+        <f t="shared" si="3"/>
         <v>655.71108433692723</v>
       </c>
-      <c r="N16">
+      <c r="O16" s="19">
         <f t="shared" si="9"/>
+        <v>393.01310043668121</v>
+      </c>
+      <c r="P16" s="19">
+        <f t="shared" si="10"/>
+        <v>1.6375545851528384</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="11"/>
         <v>-3358.7881088136119</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -7002,143 +7175,179 @@
         <v>1436.7394278317272</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>19.797117241484102</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17" s="15">
+        <f t="shared" si="4"/>
+        <v>376.31713596099593</v>
+      </c>
+      <c r="G17" s="21">
         <f t="shared" si="5"/>
-        <v>376.31713596099593</v>
-      </c>
-      <c r="G17" s="21">
+        <v>437.72145635921703</v>
+      </c>
+      <c r="H17" s="8">
         <f t="shared" si="6"/>
-        <v>437.72145635921703</v>
-      </c>
-      <c r="H17" s="8">
+        <v>438</v>
+      </c>
+      <c r="I17" s="41">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="J17" s="2">
         <f t="shared" si="7"/>
-        <v>438</v>
-      </c>
-      <c r="I17" s="2">
+        <v>-4.6516276708804483E-2</v>
+      </c>
+      <c r="K17" s="4">
         <f t="shared" si="8"/>
-        <v>-4.6516276708804483E-2</v>
-      </c>
-      <c r="J17" s="4">
-        <f t="shared" si="3"/>
         <v>684.93150684931504</v>
       </c>
-      <c r="K17" s="4">
-        <f t="shared" si="11"/>
+      <c r="L17" s="4">
+        <f t="shared" si="14"/>
         <v>29.909672788179705</v>
       </c>
-      <c r="L17" t="e">
+      <c r="M17" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M17" s="19">
-        <f t="shared" si="4"/>
+      <c r="N17" s="19">
+        <f t="shared" si="3"/>
         <v>685.36736237531932</v>
       </c>
-      <c r="N17">
+      <c r="O17" s="19">
         <f t="shared" si="9"/>
+        <v>410.95890410958907</v>
+      </c>
+      <c r="P17" s="19">
+        <f t="shared" si="10"/>
+        <v>1.7123287671232876</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="11"/>
         <v>-3048.4907103882106</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D18" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>17.446916841026166</v>
       </c>
       <c r="E18">
         <v>17</v>
       </c>
       <c r="F18" s="15">
+        <f t="shared" si="4"/>
+        <v>364.47447024508324</v>
+      </c>
+      <c r="G18" s="21">
         <f t="shared" si="5"/>
-        <v>364.47447024508324</v>
-      </c>
-      <c r="G18" s="21">
+        <v>420.27453951819086</v>
+      </c>
+      <c r="H18" s="8">
         <f t="shared" si="6"/>
-        <v>420.27453951819086</v>
-      </c>
-      <c r="H18" s="8">
+        <v>420</v>
+      </c>
+      <c r="I18" s="41">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="J18" s="2">
         <f t="shared" si="7"/>
-        <v>420</v>
-      </c>
-      <c r="I18" s="2">
+        <v>-4.257779407938532E-2</v>
+      </c>
+      <c r="K18" s="4">
         <f t="shared" si="8"/>
-        <v>-4.257779407938532E-2</v>
-      </c>
-      <c r="J18" s="4">
-        <f t="shared" si="3"/>
         <v>714.28571428571433</v>
       </c>
-      <c r="K18" s="4">
-        <f t="shared" si="11"/>
+      <c r="L18" s="4">
+        <f t="shared" si="14"/>
         <v>29.354207436399292</v>
       </c>
-      <c r="L18" t="e">
+      <c r="M18" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M18" s="19">
-        <f t="shared" si="4"/>
+      <c r="N18" s="19">
+        <f t="shared" si="3"/>
         <v>713.81911534285325</v>
       </c>
-      <c r="N18">
+      <c r="O18" s="19">
         <f t="shared" si="9"/>
+        <v>428.57142857142861</v>
+      </c>
+      <c r="P18" s="19">
+        <f t="shared" si="10"/>
+        <v>1.7857142857142858</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="11"/>
         <v>-2790.3783127865963</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>15.525055603926319</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19" s="15">
+        <f t="shared" si="4"/>
+        <v>353.71505109645437</v>
+      </c>
+      <c r="G19" s="21">
         <f t="shared" si="5"/>
-        <v>353.71505109645437</v>
-      </c>
-      <c r="G19" s="21">
+        <v>404.74948391426454</v>
+      </c>
+      <c r="H19" s="8">
         <f t="shared" si="6"/>
-        <v>404.74948391426454</v>
-      </c>
-      <c r="H19" s="8">
+        <v>405</v>
+      </c>
+      <c r="I19" s="41">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="J19" s="2">
         <f t="shared" si="7"/>
-        <v>405</v>
-      </c>
-      <c r="I19" s="2">
+        <v>-3.9251264126050532E-2</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="8"/>
-        <v>-3.9251264126050532E-2</v>
-      </c>
-      <c r="J19" s="4">
-        <f t="shared" si="3"/>
         <v>740.74074074074076</v>
       </c>
-      <c r="K19" s="4">
-        <f t="shared" si="11"/>
+      <c r="L19" s="4">
+        <f t="shared" si="14"/>
         <v>26.455026455026427</v>
       </c>
-      <c r="L19" t="e">
+      <c r="M19" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M19" s="19">
-        <f t="shared" si="4"/>
+      <c r="N19" s="19">
+        <f t="shared" si="3"/>
         <v>741.19921562036393</v>
       </c>
-      <c r="N19">
+      <c r="O19" s="19">
         <f t="shared" si="9"/>
+        <v>444.44444444444446</v>
+      </c>
+      <c r="P19" s="19">
+        <f t="shared" si="10"/>
+        <v>1.8518518518518519</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="11"/>
         <v>-2572.3708457648477</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -7147,98 +7356,122 @@
         <v>150</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>13.930240174488176</v>
       </c>
       <c r="E20">
         <v>19</v>
       </c>
       <c r="F20" s="15">
+        <f t="shared" si="4"/>
+        <v>343.88064571056657</v>
+      </c>
+      <c r="G20" s="21">
         <f t="shared" si="5"/>
-        <v>343.88064571056657</v>
-      </c>
-      <c r="G20" s="21">
+        <v>390.81924373977637</v>
+      </c>
+      <c r="H20" s="8">
         <f t="shared" si="6"/>
-        <v>390.81924373977637</v>
-      </c>
-      <c r="H20" s="8">
+        <v>391</v>
+      </c>
+      <c r="I20" s="41">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="J20" s="2">
         <f t="shared" si="7"/>
-        <v>391</v>
-      </c>
-      <c r="I20" s="2">
+        <v>-3.6404921050858553E-2</v>
+      </c>
+      <c r="K20" s="4">
         <f t="shared" si="8"/>
-        <v>-3.6404921050858553E-2</v>
-      </c>
-      <c r="J20" s="4">
-        <f t="shared" si="3"/>
         <v>767.26342710997437</v>
       </c>
-      <c r="K20" s="4">
-        <f t="shared" si="11"/>
+      <c r="L20" s="4">
+        <f t="shared" si="14"/>
         <v>26.522686369233611</v>
       </c>
-      <c r="L20" t="e">
+      <c r="M20" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M20" s="19">
-        <f t="shared" si="4"/>
+      <c r="N20" s="19">
+        <f t="shared" si="3"/>
         <v>767.61829107819574</v>
       </c>
-      <c r="N20">
+      <c r="O20" s="19">
         <f t="shared" si="9"/>
+        <v>460.35805626598466</v>
+      </c>
+      <c r="P20" s="19">
+        <f t="shared" si="10"/>
+        <v>1.918158567774936</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="11"/>
         <v>-2385.8329059890661</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>12.589869460146701</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21" s="15">
+        <f t="shared" si="4"/>
+        <v>334.84392860567385</v>
+      </c>
+      <c r="G21" s="21">
         <f t="shared" si="5"/>
-        <v>334.84392860567385</v>
-      </c>
-      <c r="G21" s="21">
+        <v>378.22937427962967</v>
+      </c>
+      <c r="H21" s="8">
         <f t="shared" si="6"/>
-        <v>378.22937427962967</v>
-      </c>
-      <c r="H21" s="8">
+        <v>378</v>
+      </c>
+      <c r="I21" s="41">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="J21" s="2">
         <f t="shared" si="7"/>
-        <v>378</v>
-      </c>
-      <c r="I21" s="2">
+        <v>-3.3942151394962386E-2</v>
+      </c>
+      <c r="K21" s="4">
         <f t="shared" si="8"/>
-        <v>-3.3942151394962386E-2</v>
-      </c>
-      <c r="J21" s="4">
-        <f t="shared" si="3"/>
         <v>793.65079365079362</v>
       </c>
-      <c r="K21" s="4">
-        <f t="shared" si="11"/>
+      <c r="L21" s="4">
+        <f t="shared" si="14"/>
         <v>26.387366540819244</v>
       </c>
-      <c r="L21" t="e">
+      <c r="M21" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M21" s="19">
-        <f t="shared" si="4"/>
+      <c r="N21" s="19">
+        <f t="shared" si="3"/>
         <v>793.16949026335078</v>
       </c>
-      <c r="N21">
+      <c r="O21" s="19">
         <f t="shared" si="9"/>
+        <v>476.1904761904762</v>
+      </c>
+      <c r="P21" s="19">
+        <f t="shared" si="10"/>
+        <v>1.984126984126984</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="11"/>
         <v>-2224.4328338202549</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -7247,4018 +7480,5228 @@
         <v>2.2222222222222222E-7</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>11.450738586924558</v>
       </c>
       <c r="E22">
         <v>21</v>
       </c>
       <c r="F22" s="15">
+        <f t="shared" si="4"/>
+        <v>326.5010721302105</v>
+      </c>
+      <c r="G22" s="21">
         <f t="shared" si="5"/>
-        <v>326.5010721302105</v>
-      </c>
-      <c r="G22" s="21">
+        <v>366.77863569270511</v>
+      </c>
+      <c r="H22" s="8">
         <f t="shared" si="6"/>
-        <v>366.77863569270511</v>
-      </c>
-      <c r="H22" s="8">
+        <v>367</v>
+      </c>
+      <c r="I22" s="41">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="J22" s="2">
         <f t="shared" si="7"/>
-        <v>367</v>
-      </c>
-      <c r="I22" s="2">
+        <v>-3.1790546570657816E-2</v>
+      </c>
+      <c r="K22" s="4">
         <f t="shared" si="8"/>
-        <v>-3.1790546570657816E-2</v>
-      </c>
-      <c r="J22" s="4">
-        <f t="shared" si="3"/>
         <v>817.43869209809259</v>
       </c>
-      <c r="K22" s="4">
-        <f t="shared" si="11"/>
+      <c r="L22" s="4">
+        <f t="shared" si="14"/>
         <v>23.787898447298971</v>
       </c>
-      <c r="L22" t="e">
+      <c r="M22" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M22" s="19">
-        <f t="shared" si="4"/>
+      <c r="N22" s="19">
+        <f t="shared" si="3"/>
         <v>817.93204621478105</v>
       </c>
-      <c r="N22">
+      <c r="O22" s="19">
         <f t="shared" si="9"/>
+        <v>490.46321525885554</v>
+      </c>
+      <c r="P22" s="19">
+        <f t="shared" si="10"/>
+        <v>2.0435967302452314</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="11"/>
         <v>-2083.4252600546306</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10.473086967590746</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="F23" s="15">
+        <f t="shared" si="4"/>
+        <v>318.76641046340961</v>
+      </c>
+      <c r="G23" s="21">
         <f t="shared" si="5"/>
-        <v>318.76641046340961</v>
-      </c>
-      <c r="G23" s="21">
+        <v>356.30554872511436</v>
+      </c>
+      <c r="H23" s="8">
         <f t="shared" si="6"/>
-        <v>356.30554872511436</v>
-      </c>
-      <c r="H23" s="8">
+        <v>356</v>
+      </c>
+      <c r="I23" s="41">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="J23" s="2">
         <f t="shared" si="7"/>
-        <v>356</v>
-      </c>
-      <c r="I23" s="2">
+        <v>-2.9894792800133799E-2</v>
+      </c>
+      <c r="K23" s="4">
         <f t="shared" si="8"/>
-        <v>-2.9894792800133799E-2</v>
-      </c>
-      <c r="J23" s="4">
-        <f t="shared" si="3"/>
         <v>842.69662921348311</v>
       </c>
-      <c r="K23" s="4">
-        <f t="shared" si="11"/>
+      <c r="L23" s="4">
+        <f t="shared" si="14"/>
         <v>25.257937115390519</v>
       </c>
-      <c r="L23" t="e">
+      <c r="M23" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M23" s="19">
-        <f t="shared" si="4"/>
+      <c r="N23" s="19">
+        <f t="shared" si="3"/>
         <v>841.97397731643673</v>
       </c>
-      <c r="N23">
+      <c r="O23" s="19">
         <f t="shared" si="9"/>
+        <v>505.61797752808985</v>
+      </c>
+      <c r="P23" s="19">
+        <f t="shared" si="10"/>
+        <v>2.1067415730337076</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="11"/>
         <v>-1959.1851409495687</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>9.6266819071818759</v>
       </c>
       <c r="E24">
         <v>23</v>
       </c>
       <c r="F24" s="15">
+        <f t="shared" si="4"/>
+        <v>311.56852150994916</v>
+      </c>
+      <c r="G24" s="21">
         <f t="shared" si="5"/>
-        <v>311.56852150994916</v>
-      </c>
-      <c r="G24" s="21">
+        <v>346.67886681793249</v>
+      </c>
+      <c r="H24" s="8">
         <f t="shared" si="6"/>
-        <v>346.67886681793249</v>
-      </c>
-      <c r="H24" s="8">
+        <v>347</v>
+      </c>
+      <c r="I24" s="41">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="J24" s="2">
         <f t="shared" si="7"/>
-        <v>347</v>
-      </c>
-      <c r="I24" s="2">
+        <v>-2.8211920900512191E-2</v>
+      </c>
+      <c r="K24" s="4">
         <f t="shared" si="8"/>
-        <v>-2.8211920900512191E-2</v>
-      </c>
-      <c r="J24" s="4">
-        <f t="shared" si="3"/>
         <v>864.55331412103749</v>
       </c>
-      <c r="K24" s="4">
-        <f t="shared" si="11"/>
+      <c r="L24" s="4">
+        <f t="shared" si="14"/>
         <v>21.856684907554381</v>
       </c>
-      <c r="L24" t="e">
+      <c r="M24" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M24" s="19">
-        <f t="shared" si="4"/>
+      <c r="N24" s="19">
+        <f t="shared" si="3"/>
         <v>865.35416119711988</v>
       </c>
-      <c r="N24">
+      <c r="O24" s="19">
         <f t="shared" si="9"/>
+        <v>518.73198847262245</v>
+      </c>
+      <c r="P24" s="19">
+        <f t="shared" si="10"/>
+        <v>2.1613832853025938</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="11"/>
         <v>-1848.8964481359669</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8.8881779179167211</v>
       </c>
       <c r="E25">
         <v>24</v>
       </c>
       <c r="F25" s="15">
+        <f t="shared" si="4"/>
+        <v>304.84730003176361</v>
+      </c>
+      <c r="G25" s="21">
         <f t="shared" si="5"/>
-        <v>304.84730003176361</v>
-      </c>
-      <c r="G25" s="21">
+        <v>337.79068890001577</v>
+      </c>
+      <c r="H25" s="8">
         <f t="shared" si="6"/>
-        <v>337.79068890001577</v>
-      </c>
-      <c r="H25" s="8">
+        <v>338</v>
+      </c>
+      <c r="I25" s="41">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="J25" s="2">
         <f t="shared" si="7"/>
-        <v>338</v>
-      </c>
-      <c r="I25" s="2">
+        <v>-2.6708052599592396E-2</v>
+      </c>
+      <c r="K25" s="4">
         <f t="shared" si="8"/>
-        <v>-2.6708052599592396E-2</v>
-      </c>
-      <c r="J25" s="4">
-        <f t="shared" si="3"/>
         <v>887.5739644970414</v>
       </c>
-      <c r="K25" s="4">
-        <f t="shared" si="11"/>
+      <c r="L25" s="4">
+        <f t="shared" si="14"/>
         <v>23.020650376003914</v>
       </c>
-      <c r="L25" t="e">
+      <c r="M25" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M25" s="19">
-        <f t="shared" si="4"/>
+      <c r="N25" s="19">
+        <f t="shared" si="3"/>
         <v>888.12394733828319</v>
       </c>
-      <c r="N25">
+      <c r="O25" s="19">
         <f t="shared" si="9"/>
+        <v>532.54437869822482</v>
+      </c>
+      <c r="P25" s="19">
+        <f t="shared" si="10"/>
+        <v>2.2189349112426036</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="11"/>
         <v>-1750.3389351668873</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8.2392968210099298</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26" s="15">
+        <f t="shared" si="4"/>
+        <v>298.55173745662682</v>
+      </c>
+      <c r="G26" s="21">
         <f t="shared" si="5"/>
-        <v>298.55173745662682</v>
-      </c>
-      <c r="G26" s="21">
+        <v>329.55139207900584</v>
+      </c>
+      <c r="H26" s="8">
         <f t="shared" si="6"/>
-        <v>329.55139207900584</v>
-      </c>
-      <c r="H26" s="8">
+        <v>330</v>
+      </c>
+      <c r="I26" s="41">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="J26" s="2">
         <f t="shared" si="7"/>
-        <v>330</v>
-      </c>
-      <c r="I26" s="2">
+        <v>-2.5356122112788277E-2</v>
+      </c>
+      <c r="K26" s="4">
         <f t="shared" si="8"/>
-        <v>-2.5356122112788277E-2</v>
-      </c>
-      <c r="J26" s="4">
-        <f t="shared" si="3"/>
         <v>909.09090909090912</v>
       </c>
-      <c r="K26" s="4">
-        <f t="shared" si="11"/>
+      <c r="L26" s="4">
+        <f t="shared" si="14"/>
         <v>21.51694459386772</v>
       </c>
-      <c r="L26" t="e">
+      <c r="M26" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M26" s="19">
-        <f t="shared" si="4"/>
+      <c r="N26" s="19">
+        <f t="shared" si="3"/>
         <v>910.32842588654194</v>
       </c>
-      <c r="N26">
+      <c r="O26" s="19">
         <f t="shared" si="9"/>
+        <v>545.4545454545455</v>
+      </c>
+      <c r="P26" s="19">
+        <f t="shared" si="10"/>
+        <v>2.2727272727272729</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="11"/>
         <v>-1661.7388187836925</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7.6655485902668943</v>
       </c>
       <c r="E27">
         <v>26</v>
       </c>
       <c r="F27" s="15">
+        <f t="shared" si="4"/>
+        <v>292.63821439139014</v>
+      </c>
+      <c r="G27" s="21">
         <f t="shared" si="5"/>
-        <v>292.63821439139014</v>
-      </c>
-      <c r="G27" s="21">
+        <v>321.88584348873894</v>
+      </c>
+      <c r="H27" s="8">
         <f t="shared" si="6"/>
-        <v>321.88584348873894</v>
-      </c>
-      <c r="H27" s="8">
+        <v>322</v>
+      </c>
+      <c r="I27" s="41">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="J27" s="2">
         <f t="shared" si="7"/>
-        <v>322</v>
-      </c>
-      <c r="I27" s="2">
+        <v>-2.4134248893602363E-2</v>
+      </c>
+      <c r="K27" s="4">
         <f t="shared" si="8"/>
-        <v>-2.4134248893602363E-2</v>
-      </c>
-      <c r="J27" s="4">
-        <f t="shared" si="3"/>
         <v>931.67701863354034</v>
       </c>
-      <c r="K27" s="4">
-        <f t="shared" si="11"/>
+      <c r="L27" s="4">
+        <f t="shared" si="14"/>
         <v>22.58610954263122</v>
       </c>
-      <c r="L27" t="e">
+      <c r="M27" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M27" s="19">
-        <f t="shared" si="4"/>
+      <c r="N27" s="19">
+        <f t="shared" si="3"/>
         <v>932.00743701080285</v>
       </c>
-      <c r="N27">
+      <c r="O27" s="19">
         <f t="shared" si="9"/>
+        <v>559.00621118012418</v>
+      </c>
+      <c r="P27" s="19">
+        <f t="shared" si="10"/>
+        <v>2.329192546583851</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="11"/>
         <v>-1581.6621354911244</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7.1553161456183716</v>
       </c>
       <c r="E28">
         <v>27</v>
       </c>
       <c r="F28" s="15">
+        <f t="shared" si="4"/>
+        <v>287.06917101232699</v>
+      </c>
+      <c r="G28" s="21">
         <f t="shared" si="5"/>
-        <v>287.06917101232699</v>
-      </c>
-      <c r="G28" s="21">
+        <v>314.73052734312057</v>
+      </c>
+      <c r="H28" s="8">
         <f t="shared" si="6"/>
-        <v>314.73052734312057</v>
-      </c>
-      <c r="H28" s="8">
+        <v>315</v>
+      </c>
+      <c r="I28" s="41">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="J28" s="2">
         <f t="shared" si="7"/>
-        <v>315</v>
-      </c>
-      <c r="I28" s="2">
+        <v>-2.3024554719657097E-2</v>
+      </c>
+      <c r="K28" s="4">
         <f t="shared" si="8"/>
-        <v>-2.3024554719657097E-2</v>
-      </c>
-      <c r="J28" s="4">
-        <f t="shared" si="3"/>
         <v>952.38095238095241</v>
       </c>
-      <c r="K28" s="4">
-        <f t="shared" si="11"/>
+      <c r="L28" s="4">
+        <f t="shared" si="14"/>
         <v>20.703933747412066</v>
       </c>
-      <c r="L28" t="e">
+      <c r="M28" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M28" s="19">
-        <f t="shared" si="4"/>
+      <c r="N28" s="19">
+        <f t="shared" si="3"/>
         <v>953.19638210035691</v>
       </c>
-      <c r="N28">
+      <c r="O28" s="19">
         <f t="shared" si="9"/>
+        <v>571.42857142857144</v>
+      </c>
+      <c r="P28" s="19">
+        <f t="shared" si="10"/>
+        <v>2.3809523809523809</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="11"/>
         <v>-1508.9372181074475</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6.6991899047096126</v>
       </c>
       <c r="E29">
         <v>28</v>
       </c>
       <c r="F29" s="15">
+        <f t="shared" si="4"/>
+        <v>281.81205995427376</v>
+      </c>
+      <c r="G29" s="21">
         <f t="shared" si="5"/>
-        <v>281.81205995427376</v>
-      </c>
-      <c r="G29" s="21">
+        <v>308.03133743841096</v>
+      </c>
+      <c r="H29" s="8">
         <f t="shared" si="6"/>
-        <v>308.03133743841096</v>
-      </c>
-      <c r="H29" s="8">
+        <v>308</v>
+      </c>
+      <c r="I29" s="41">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="J29" s="2">
         <f t="shared" si="7"/>
-        <v>308</v>
-      </c>
-      <c r="I29" s="2">
+        <v>-2.2012289964817505E-2</v>
+      </c>
+      <c r="K29" s="4">
         <f t="shared" si="8"/>
-        <v>-2.2012289964817505E-2</v>
-      </c>
-      <c r="J29" s="4">
-        <f t="shared" si="3"/>
         <v>974.02597402597405</v>
       </c>
-      <c r="K29" s="4">
-        <f t="shared" si="11"/>
+      <c r="L29" s="4">
+        <f t="shared" si="14"/>
         <v>21.645021645021643</v>
       </c>
-      <c r="L29" t="e">
+      <c r="M29" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M29" s="19">
-        <f t="shared" si="4"/>
+      <c r="N29" s="19">
+        <f t="shared" si="3"/>
         <v>973.9268819036414</v>
       </c>
-      <c r="N29">
+      <c r="O29" s="19">
         <f t="shared" si="9"/>
+        <v>584.41558441558448</v>
+      </c>
+      <c r="P29" s="19">
+        <f t="shared" si="10"/>
+        <v>2.4350649350649349</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="11"/>
         <v>-1442.59743513428</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6.2894767818793866</v>
       </c>
       <c r="E30">
         <v>29</v>
       </c>
       <c r="F30" s="15">
+        <f t="shared" si="4"/>
+        <v>276.83851314477852</v>
+      </c>
+      <c r="G30" s="21">
         <f t="shared" si="5"/>
-        <v>276.83851314477852</v>
-      </c>
-      <c r="G30" s="21">
+        <v>301.74186065653157</v>
+      </c>
+      <c r="H30" s="8">
         <f t="shared" si="6"/>
-        <v>301.74186065653157</v>
-      </c>
-      <c r="H30" s="8">
+        <v>302</v>
+      </c>
+      <c r="I30" s="41">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="J30" s="2">
         <f t="shared" si="7"/>
-        <v>302</v>
-      </c>
-      <c r="I30" s="2">
+        <v>-2.1085178854243599E-2</v>
+      </c>
+      <c r="K30" s="4">
         <f t="shared" si="8"/>
-        <v>-2.1085178854243599E-2</v>
-      </c>
-      <c r="J30" s="4">
-        <f t="shared" si="3"/>
         <v>993.37748344370857</v>
       </c>
-      <c r="K30" s="4">
-        <f t="shared" si="11"/>
+      <c r="L30" s="4">
+        <f t="shared" si="14"/>
         <v>19.351509417734519</v>
       </c>
-      <c r="L30" t="e">
+      <c r="M30" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M30" s="19">
-        <f t="shared" si="4"/>
+      <c r="N30" s="19">
+        <f t="shared" si="3"/>
         <v>994.22731518675721</v>
       </c>
-      <c r="N30">
+      <c r="O30" s="19">
         <f t="shared" si="9"/>
+        <v>596.02649006622516</v>
+      </c>
+      <c r="P30" s="19">
+        <f t="shared" si="10"/>
+        <v>2.4834437086092715</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="11"/>
         <v>-1381.8382813917085</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5.9198330126387759</v>
       </c>
       <c r="E31">
         <v>30</v>
       </c>
       <c r="F31" s="15">
+        <f t="shared" si="4"/>
+        <v>272.12367259103019</v>
+      </c>
+      <c r="G31" s="21">
         <f t="shared" si="5"/>
-        <v>272.12367259103019</v>
-      </c>
-      <c r="G31" s="21">
+        <v>295.8220276438928</v>
+      </c>
+      <c r="H31" s="8">
         <f t="shared" si="6"/>
-        <v>295.8220276438928</v>
-      </c>
-      <c r="H31" s="8">
+        <v>296</v>
+      </c>
+      <c r="I31" s="41">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="J31" s="2">
         <f t="shared" si="7"/>
-        <v>296</v>
-      </c>
-      <c r="I31" s="2">
+        <v>-2.0232922327214603E-2</v>
+      </c>
+      <c r="K31" s="4">
         <f t="shared" si="8"/>
-        <v>-2.0232922327214603E-2</v>
-      </c>
-      <c r="J31" s="4">
-        <f t="shared" si="3"/>
         <v>1013.5135135135135</v>
       </c>
-      <c r="K31" s="4">
-        <f t="shared" si="11"/>
+      <c r="L31" s="4">
+        <f t="shared" si="14"/>
         <v>20.136030069804974</v>
       </c>
-      <c r="L31" t="e">
+      <c r="M31" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M31" s="19">
-        <f t="shared" si="4"/>
+      <c r="N31" s="19">
+        <f t="shared" si="3"/>
         <v>1014.1232631977515</v>
       </c>
-      <c r="N31">
+      <c r="O31" s="19">
         <f t="shared" si="9"/>
+        <v>608.10810810810813</v>
+      </c>
+      <c r="P31" s="19">
+        <f t="shared" si="10"/>
+        <v>2.5337837837837838</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="11"/>
         <v>-1325.9847976363362</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5.5849861790651403</v>
       </c>
       <c r="E32">
         <v>31</v>
       </c>
       <c r="F32" s="15">
+        <f t="shared" si="4"/>
+        <v>267.64564817737192</v>
+      </c>
+      <c r="G32" s="21">
         <f t="shared" si="5"/>
-        <v>267.64564817737192</v>
-      </c>
-      <c r="G32" s="21">
+        <v>290.23704146482766</v>
+      </c>
+      <c r="H32" s="8">
         <f t="shared" si="6"/>
-        <v>290.23704146482766</v>
-      </c>
-      <c r="H32" s="8">
+        <v>290</v>
+      </c>
+      <c r="I32" s="41">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="J32" s="2">
         <f t="shared" si="7"/>
-        <v>290</v>
-      </c>
-      <c r="I32" s="2">
+        <v>-1.9446816008743126E-2</v>
+      </c>
+      <c r="K32" s="4">
         <f t="shared" si="8"/>
-        <v>-1.9446816008743126E-2</v>
-      </c>
-      <c r="J32" s="4">
-        <f t="shared" si="3"/>
         <v>1034.4827586206898</v>
       </c>
-      <c r="K32" s="4">
-        <f t="shared" si="11"/>
+      <c r="L32" s="4">
+        <f t="shared" si="14"/>
         <v>20.969245107176221</v>
       </c>
-      <c r="L32" t="e">
+      <c r="M32" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M32" s="19">
-        <f t="shared" si="4"/>
+      <c r="N32" s="19">
+        <f t="shared" si="3"/>
         <v>1033.6378791828179</v>
       </c>
-      <c r="N32">
+      <c r="O32" s="19">
         <f t="shared" si="9"/>
+        <v>620.68965517241384</v>
+      </c>
+      <c r="P32" s="19">
+        <f t="shared" si="10"/>
+        <v>2.5862068965517242</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="11"/>
         <v>-1274.4665339489895</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5.2805223715411671</v>
       </c>
       <c r="E33">
         <v>32</v>
       </c>
       <c r="F33" s="15">
+        <f t="shared" si="4"/>
+        <v>263.38507484092469</v>
+      </c>
+      <c r="G33" s="21">
         <f t="shared" si="5"/>
-        <v>263.38507484092469</v>
-      </c>
-      <c r="G33" s="21">
+        <v>284.95651909328649</v>
+      </c>
+      <c r="H33" s="8">
         <f t="shared" si="6"/>
-        <v>284.95651909328649</v>
-      </c>
-      <c r="H33" s="8">
+        <v>285</v>
+      </c>
+      <c r="I33" s="41">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="J33" s="2">
         <f t="shared" si="7"/>
-        <v>285</v>
-      </c>
-      <c r="I33" s="2">
+        <v>-1.8719453386279131E-2</v>
+      </c>
+      <c r="K33" s="4">
         <f t="shared" si="8"/>
-        <v>-1.8719453386279131E-2</v>
-      </c>
-      <c r="J33" s="4">
-        <f t="shared" si="3"/>
         <v>1052.6315789473683</v>
       </c>
-      <c r="K33" s="4">
-        <f t="shared" si="11"/>
+      <c r="L33" s="4">
+        <f t="shared" si="14"/>
         <v>18.14882032667856</v>
       </c>
-      <c r="L33" t="e">
+      <c r="M33" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M33" s="19">
-        <f t="shared" si="4"/>
+      <c r="N33" s="19">
+        <f t="shared" si="3"/>
         <v>1052.7921977520673</v>
       </c>
-      <c r="N33">
+      <c r="O33" s="19">
         <f t="shared" si="9"/>
+        <v>631.57894736842104</v>
+      </c>
+      <c r="P33" s="19">
+        <f t="shared" si="10"/>
+        <v>2.6315789473684208</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="11"/>
         <v>-1226.7980971231891</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D34" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5.0027215133420668</v>
       </c>
       <c r="E34">
         <v>33</v>
       </c>
       <c r="F34" s="15">
+        <f t="shared" si="4"/>
+        <v>259.32474822378839</v>
+      </c>
+      <c r="G34" s="3">
         <f t="shared" si="5"/>
-        <v>259.32474822378839</v>
-      </c>
-      <c r="G34" s="3">
+        <v>279.95379757994442</v>
+      </c>
+      <c r="H34" s="8">
         <f t="shared" si="6"/>
-        <v>279.95379757994442</v>
-      </c>
-      <c r="H34" s="8">
+        <v>280</v>
+      </c>
+      <c r="I34" s="41">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="J34" s="2">
         <f t="shared" si="7"/>
-        <v>280</v>
-      </c>
-      <c r="I34" s="2">
+        <v>-1.8044492838613899E-2</v>
+      </c>
+      <c r="K34" s="4">
         <f t="shared" si="8"/>
-        <v>-1.8044492838613899E-2</v>
-      </c>
-      <c r="J34" s="4">
-        <f t="shared" si="3"/>
         <v>1071.4285714285713</v>
       </c>
-      <c r="K34" s="4">
-        <f t="shared" si="11"/>
+      <c r="L34" s="4">
+        <f t="shared" si="14"/>
         <v>18.796992481203006</v>
       </c>
-      <c r="L34" t="e">
+      <c r="M34" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M34" s="19">
-        <f t="shared" si="4"/>
+      <c r="N34" s="19">
+        <f t="shared" si="3"/>
         <v>1071.6053955807872</v>
       </c>
-      <c r="N34">
+      <c r="O34" s="19">
         <f t="shared" si="9"/>
+        <v>642.85714285714278</v>
+      </c>
+      <c r="P34" s="19">
+        <f t="shared" si="10"/>
+        <v>2.6785714285714284</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="11"/>
         <v>-1182.5638826714005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="D35" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.7484287120500994</v>
       </c>
       <c r="E35">
         <v>34</v>
       </c>
       <c r="F35" s="15">
+        <f t="shared" si="4"/>
+        <v>255.44932282721885</v>
+      </c>
+      <c r="G35" s="3">
         <f t="shared" si="5"/>
-        <v>255.44932282721885</v>
-      </c>
-      <c r="G35" s="3">
+        <v>275.20536886789432</v>
+      </c>
+      <c r="H35" s="9">
         <f t="shared" si="6"/>
-        <v>275.20536886789432</v>
-      </c>
-      <c r="H35" s="9">
+        <v>275</v>
+      </c>
+      <c r="I35" s="41">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="J35" s="2">
         <f t="shared" si="7"/>
-        <v>275</v>
-      </c>
-      <c r="I35" s="2">
+        <v>-1.7416473062096108E-2</v>
+      </c>
+      <c r="K35" s="4">
         <f t="shared" si="8"/>
-        <v>-1.7416473062096108E-2</v>
-      </c>
-      <c r="J35" s="4">
-        <f t="shared" si="3"/>
         <v>1090.909090909091</v>
       </c>
-      <c r="K35" s="4">
-        <f t="shared" si="11"/>
+      <c r="L35" s="4">
+        <f t="shared" si="14"/>
         <v>19.480519480519661</v>
       </c>
-      <c r="L35" t="e">
+      <c r="M35" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M35" s="19">
-        <f t="shared" si="4"/>
+      <c r="N35" s="19">
+        <f t="shared" si="3"/>
         <v>1090.095012441446</v>
       </c>
-      <c r="N35">
+      <c r="O35" s="19">
         <f t="shared" si="9"/>
+        <v>654.5454545454545</v>
+      </c>
+      <c r="P35" s="19">
+        <f t="shared" si="10"/>
+        <v>2.7272727272727275</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="11"/>
         <v>-1141.4059785975305</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.5149528504624641</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>270.69041601743186</v>
       </c>
       <c r="H36" s="12">
         <f>ROUND(G36,0)</f>
         <v>271</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="41">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="J36" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.6830665567491951E-2</v>
+      </c>
+      <c r="K36" s="4">
         <f t="shared" si="8"/>
-        <v>-1.6830665567491951E-2</v>
-      </c>
-      <c r="L36" t="e">
+        <v>1107.0110701107012</v>
+      </c>
+      <c r="M36" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M36" s="19">
-        <f t="shared" si="4"/>
+      <c r="N36" s="19">
+        <f t="shared" si="3"/>
         <v>1108.277139670437</v>
       </c>
-      <c r="N36">
+      <c r="O36" s="19">
         <f t="shared" si="9"/>
+        <v>664.20664206642073</v>
+      </c>
+      <c r="P36" s="19">
+        <f t="shared" si="10"/>
+        <v>2.767527675276753</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="11"/>
         <v>-1103.0144986311525</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.299985979398798</v>
       </c>
       <c r="G37" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>266.39043003803306</v>
       </c>
       <c r="H37" s="13">
         <f>ROUND(G37,0)</f>
         <v>266</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="41">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="J37" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.6282955849708961E-2</v>
+      </c>
+      <c r="K37" s="4">
         <f t="shared" si="8"/>
-        <v>-1.6282955849708961E-2</v>
-      </c>
-      <c r="L37" t="e">
+        <v>1127.8195488721803</v>
+      </c>
+      <c r="M37" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M37" s="19">
-        <f t="shared" si="4"/>
+      <c r="N37" s="19">
+        <f t="shared" si="3"/>
         <v>1126.1665817243077</v>
       </c>
-      <c r="N37">
+      <c r="O37" s="19">
         <f t="shared" si="9"/>
+        <v>676.69172932330821</v>
+      </c>
+      <c r="P37" s="19">
+        <f t="shared" si="10"/>
+        <v>2.8195488721804507</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="11"/>
         <v>-1067.1197945665265</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="G38" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>262.28889129348903</v>
       </c>
       <c r="H38" s="13">
         <f>ROUND(G38,0)</f>
         <v>262</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="41">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="J38" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.5769746936855154E-2</v>
+      </c>
+      <c r="K38" s="4">
         <f t="shared" si="8"/>
-        <v>-1.5769746936855154E-2</v>
-      </c>
-      <c r="L38" t="e">
+        <v>1145.0381679389313</v>
+      </c>
+      <c r="M38" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M38" s="19">
-        <f t="shared" si="4"/>
+      <c r="N38" s="19">
+        <f t="shared" si="3"/>
         <v>1143.7769953601046</v>
       </c>
-      <c r="N38">
+      <c r="O38" s="19">
         <f t="shared" si="9"/>
+        <v>687.02290076335873</v>
+      </c>
+      <c r="P38" s="19">
+        <f t="shared" si="10"/>
+        <v>2.8625954198473282</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="11"/>
         <v>-1033.4861352537393</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="G39" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>258.37100301348136</v>
       </c>
       <c r="H39" s="8">
         <f>ROUND(G39,0)</f>
         <v>258</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I39" s="41">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="J39" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.528788055465949E-2</v>
+      </c>
+      <c r="K39" s="4">
         <f t="shared" si="8"/>
-        <v>-1.528788055465949E-2</v>
-      </c>
-      <c r="L39" t="e">
+        <v>1162.7906976744187</v>
+      </c>
+      <c r="M39" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="M39" s="19">
-        <f t="shared" si="4"/>
+      <c r="N39" s="19">
+        <f t="shared" si="3"/>
         <v>1161.1210101016891</v>
       </c>
-      <c r="N39">
+      <c r="O39" s="19">
         <f t="shared" si="9"/>
+        <v>697.67441860465112</v>
+      </c>
+      <c r="P39" s="19">
+        <f t="shared" si="10"/>
+        <v>2.9069767441860468</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="11"/>
         <v>-1001.9065400301644</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="G40" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>254.62346713946161</v>
       </c>
       <c r="H40" s="8">
-        <f t="shared" ref="H40:H53" si="12">ROUND(G40,0)</f>
+        <f t="shared" ref="H40:H53" si="15">ROUND(G40,0)</f>
         <v>255</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I40" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J40" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.4834572266264976E-2</v>
+      </c>
+      <c r="K40" s="4">
         <f t="shared" si="8"/>
-        <v>-1.4834572266264976E-2</v>
-      </c>
-      <c r="L40" t="str">
+        <v>1176.4705882352941</v>
+      </c>
+      <c r="M40" t="str">
         <f t="shared" si="0"/>
         <v>0xFE9F9B8A,</v>
       </c>
-      <c r="M40" s="19">
-        <f t="shared" si="4"/>
+      <c r="N40" s="19">
+        <f t="shared" si="3"/>
         <v>1178.2103329685826</v>
       </c>
-      <c r="N40">
+      <c r="O40" s="19">
         <f t="shared" si="9"/>
+        <v>705.88235294117646</v>
+      </c>
+      <c r="P40" s="19">
+        <f t="shared" si="10"/>
+        <v>2.9411764705882355</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="11"/>
         <v>-972.19852804194147</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="G41" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>251.03429478627675</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>251</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I41" s="41">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="J41" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.4407357781804552E-2</v>
+      </c>
+      <c r="K41" s="4">
         <f t="shared" si="8"/>
-        <v>-1.4407357781804552E-2</v>
-      </c>
-      <c r="L41" t="str">
+        <v>1195.2191235059761</v>
+      </c>
+      <c r="M41" t="str">
         <f t="shared" si="0"/>
         <v>0xFB08C78B,</v>
       </c>
-      <c r="M41" s="19">
-        <f t="shared" si="4"/>
+      <c r="N41" s="19">
+        <f t="shared" si="3"/>
         <v>1195.0558399019194</v>
       </c>
-      <c r="N41">
+      <c r="O41" s="19">
         <f t="shared" si="9"/>
+        <v>717.13147410358567</v>
+      </c>
+      <c r="P41" s="19">
+        <f t="shared" si="10"/>
+        <v>2.9880478087649402</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="11"/>
         <v>-944.20059958834315</v>
       </c>
-      <c r="Q41">
+      <c r="T41">
         <v>1.1000000000000001</v>
       </c>
-      <c r="R41" s="16">
-        <f xml:space="preserve"> -66.667*POWER(Q41,3) + 500*POWER(Q41,2) - 833.33*Q41</f>
+      <c r="U41" s="16">
+        <f xml:space="preserve"> -66.667*POWER(T41,3) + 500*POWER(T41,2) - 833.33*T41</f>
         <v>-400.39677700000004</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>247.59264517919706</v>
       </c>
       <c r="H42" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>248</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I42" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J42" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.400404825752073E-2</v>
+      </c>
+      <c r="K42" s="4">
         <f t="shared" si="8"/>
-        <v>-1.400404825752073E-2</v>
-      </c>
-      <c r="L42" t="str">
+        <v>1209.6774193548388</v>
+      </c>
+      <c r="M42" t="str">
         <f t="shared" si="0"/>
         <v>0xF797B798,</v>
       </c>
-      <c r="M42" s="19">
-        <f t="shared" si="4"/>
+      <c r="N42" s="19">
+        <f t="shared" si="3"/>
         <v>1211.6676558904758</v>
       </c>
-      <c r="N42">
+      <c r="O42" s="19">
         <f t="shared" si="9"/>
+        <v>725.80645161290329</v>
+      </c>
+      <c r="P42" s="19">
+        <f t="shared" si="10"/>
+        <v>3.024193548387097</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="11"/>
         <v>-917.76930660487858</v>
       </c>
-      <c r="Q42">
+      <c r="T42">
         <v>1.2</v>
       </c>
-      <c r="R42" s="16">
-        <f t="shared" ref="R42:R70" si="13" xml:space="preserve"> -66.667*POWER(Q42,3) + 500*POWER(Q42,2) - 833.33*Q42</f>
+      <c r="U42" s="16">
+        <f t="shared" ref="U42:U70" si="16" xml:space="preserve"> -66.667*POWER(T42,3) + 500*POWER(T42,2) - 833.33*T42</f>
         <v>-395.19657599999994</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>244.28868814848005</v>
       </c>
       <c r="H43" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>244</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I43" s="41">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="J43" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.3622692877073728E-2</v>
+      </c>
+      <c r="K43" s="4">
         <f t="shared" si="8"/>
-        <v>-1.3622692877073728E-2</v>
-      </c>
-      <c r="L43" t="str">
+        <v>1229.5081967213114</v>
+      </c>
+      <c r="M43" t="str">
         <f t="shared" si="0"/>
         <v>0xF449E777,</v>
       </c>
-      <c r="M43" s="19">
-        <f t="shared" si="4"/>
+      <c r="N43" s="19">
+        <f t="shared" si="3"/>
         <v>1228.0552254538218</v>
       </c>
-      <c r="N43">
+      <c r="O43" s="19">
         <f t="shared" si="9"/>
+        <v>737.70491803278685</v>
+      </c>
+      <c r="P43" s="19">
+        <f t="shared" si="10"/>
+        <v>3.0737704918032787</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="11"/>
         <v>-892.77680039190386</v>
       </c>
-      <c r="Q43">
+      <c r="T43">
         <v>1.3</v>
       </c>
-      <c r="R43" s="16">
-        <f t="shared" si="13"/>
+      <c r="U43" s="16">
+        <f t="shared" si="16"/>
         <v>-384.79639900000006</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>241.1134862175771</v>
       </c>
       <c r="H44" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>241</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I44" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J44" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.3261547368290076E-2</v>
+      </c>
+      <c r="K44" s="4">
         <f t="shared" si="8"/>
-        <v>-1.3261547368290076E-2</v>
-      </c>
-      <c r="L44" t="str">
+        <v>1244.8132780082988</v>
+      </c>
+      <c r="M44" t="str">
         <f t="shared" si="0"/>
         <v>0xF11D0D6E,</v>
       </c>
-      <c r="M44" s="19">
-        <f t="shared" si="4"/>
+      <c r="N44" s="19">
+        <f t="shared" si="3"/>
         <v>1244.2273748606688</v>
       </c>
-      <c r="N44">
+      <c r="O44" s="19">
         <f t="shared" si="9"/>
+        <v>746.88796680497921</v>
+      </c>
+      <c r="P44" s="19">
+        <f t="shared" si="10"/>
+        <v>3.1120331950207469</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="11"/>
         <v>-869.10876832825841</v>
       </c>
-      <c r="Q44">
+      <c r="T44">
         <v>1.4</v>
       </c>
-      <c r="R44" s="16">
-        <f t="shared" si="13"/>
+      <c r="U44" s="16">
+        <f t="shared" si="16"/>
         <v>-369.59624800000006</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>238.05889307076711</v>
       </c>
       <c r="H45" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>238</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I45" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J45" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.2919047385776388E-2</v>
+      </c>
+      <c r="K45" s="4">
         <f t="shared" si="8"/>
-        <v>-1.2919047385776388E-2</v>
-      </c>
-      <c r="L45" t="str">
+        <v>1260.5042016806722</v>
+      </c>
+      <c r="M45" t="str">
         <f t="shared" si="0"/>
         <v>0xEE0F139D,</v>
       </c>
-      <c r="M45" s="19">
-        <f t="shared" si="4"/>
+      <c r="N45" s="19">
+        <f t="shared" si="3"/>
         <v>1260.1923672341861</v>
       </c>
-      <c r="N45">
-        <f>I45*65536</f>
+      <c r="O45" s="19">
+        <f t="shared" si="9"/>
+        <v>756.30252100840323</v>
+      </c>
+      <c r="P45" s="19">
+        <f t="shared" si="10"/>
+        <v>3.1512605042016806</v>
+      </c>
+      <c r="Q45">
+        <f>J45*65536</f>
         <v>-846.66268947424135</v>
       </c>
-      <c r="Q45">
+      <c r="T45">
         <v>1.5</v>
       </c>
-      <c r="R45" s="16">
-        <f t="shared" si="13"/>
+      <c r="U45" s="16">
+        <f t="shared" si="16"/>
         <v>-349.99612500000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>235.11746577904282</v>
       </c>
       <c r="H46" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>235</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I46" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J46" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.2593785904461984E-2</v>
+      </c>
+      <c r="K46" s="4">
         <f t="shared" si="8"/>
-        <v>-1.2593785904461984E-2</v>
-      </c>
-      <c r="L46" t="str">
+        <v>1276.5957446808511</v>
+      </c>
+      <c r="M46" t="str">
         <f t="shared" si="0"/>
         <v>0xEB1E123C,</v>
       </c>
-      <c r="M46" s="19">
-        <f t="shared" si="4"/>
+      <c r="N46" s="19">
+        <f t="shared" si="3"/>
         <v>1275.9579515114885</v>
       </c>
-      <c r="N46">
-        <f t="shared" ref="N46:N70" si="14">I46*65536</f>
+      <c r="O46" s="19">
+        <f t="shared" si="9"/>
+        <v>765.95744680851067</v>
+      </c>
+      <c r="P46" s="19">
+        <f t="shared" si="10"/>
+        <v>3.1914893617021276</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" ref="Q46:Q70" si="17">J46*65536</f>
         <v>-825.34635303482059</v>
       </c>
-      <c r="Q46">
+      <c r="T46">
         <v>1.6</v>
       </c>
-      <c r="R46" s="16">
-        <f t="shared" si="13"/>
+      <c r="U46" s="16">
+        <f t="shared" si="16"/>
         <v>-326.3960320000001</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>232.28238863516225</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>232</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J47" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.2284493936524305E-2</v>
+      </c>
+      <c r="K47" s="4">
         <f t="shared" si="8"/>
-        <v>-1.2284493936524305E-2</v>
-      </c>
-      <c r="L47" t="str">
+        <v>1293.1034482758621</v>
+      </c>
+      <c r="M47" t="str">
         <f t="shared" si="0"/>
         <v>0xE8484A9F,</v>
       </c>
-      <c r="M47" s="19">
-        <f t="shared" si="4"/>
+      <c r="N47" s="19">
+        <f t="shared" si="3"/>
         <v>1291.5314060731457</v>
       </c>
-      <c r="N47">
-        <f t="shared" si="14"/>
+      <c r="O47" s="19">
+        <f t="shared" si="9"/>
+        <v>775.86206896551721</v>
+      </c>
+      <c r="P47" s="19">
+        <f t="shared" si="10"/>
+        <v>3.2327586206896552</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="17"/>
         <v>-805.07659462405684</v>
       </c>
-      <c r="Q47">
+      <c r="T47">
         <v>1.7</v>
       </c>
-      <c r="R47" s="16">
-        <f t="shared" si="13"/>
+      <c r="U47" s="16">
+        <f t="shared" si="16"/>
         <v>-299.19597100000033</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>229.54740682681577</v>
       </c>
       <c r="H48" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>230</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J48" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.1990024015568122E-2</v>
+      </c>
+      <c r="K48" s="4">
         <f t="shared" si="8"/>
-        <v>-1.1990024015568122E-2</v>
-      </c>
-      <c r="L48" t="str">
+        <v>1304.3478260869565</v>
+      </c>
+      <c r="M48" t="str">
         <f t="shared" si="0"/>
         <v>0xE58C22DA,</v>
       </c>
-      <c r="M48" s="19">
-        <f t="shared" si="4"/>
+      <c r="N48" s="19">
+        <f t="shared" si="3"/>
         <v>1306.9195777338398</v>
       </c>
-      <c r="N48">
-        <f t="shared" si="14"/>
+      <c r="O48" s="19">
+        <f t="shared" si="9"/>
+        <v>782.60869565217388</v>
+      </c>
+      <c r="P48" s="19">
+        <f t="shared" si="10"/>
+        <v>3.2608695652173911</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="17"/>
         <v>-785.77821388427242</v>
       </c>
-      <c r="Q48">
+      <c r="T48">
         <v>1.8</v>
       </c>
-      <c r="R48" s="16">
-        <f t="shared" si="13"/>
+      <c r="U48" s="16">
+        <f t="shared" si="16"/>
         <v>-268.79594400000019</v>
       </c>
     </row>
-    <row r="49" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3">
-        <f t="shared" ref="G49:G112" si="15">G48*(1+I49+1.5*I49*I49)</f>
+        <f t="shared" ref="G49:G112" si="18">G48*(1+J49+1.5*J49*J49)</f>
         <v>226.90676848129942</v>
       </c>
       <c r="H49" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>227</v>
       </c>
-      <c r="I49" s="2">
-        <f t="shared" ref="I49:I112" si="16">-1*$B$22*G48*G48</f>
+      <c r="I49" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J49" s="2">
+        <f t="shared" ref="J49:J112" si="19">-1*$B$22*G48*G48</f>
         <v>-1.1709335995759037E-2</v>
       </c>
-      <c r="L49" t="str">
-        <f t="shared" ref="L49:L53" si="17">CONCATENATE("0x",DEC2HEX(G49*POWER(2,24),8),",")</f>
+      <c r="K49" s="4">
+        <f t="shared" si="8"/>
+        <v>1321.5859030837005</v>
+      </c>
+      <c r="M49" t="str">
+        <f t="shared" ref="M49:M53" si="20">CONCATENATE("0x",DEC2HEX(G49*POWER(2,24),8),",")</f>
         <v>0xE2E821FA,</v>
       </c>
-      <c r="M49" s="19">
-        <f t="shared" ref="M49:M53" si="18">$B$12/G49</f>
+      <c r="N49" s="19">
+        <f t="shared" ref="N49:N53" si="21">$B$12/G49</f>
         <v>1322.1289166820275</v>
       </c>
-      <c r="N49">
-        <f t="shared" si="14"/>
+      <c r="O49" s="19">
+        <f t="shared" si="9"/>
+        <v>792.95154185022022</v>
+      </c>
+      <c r="P49" s="19">
+        <f t="shared" si="10"/>
+        <v>3.303964757709251</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="17"/>
         <v>-767.38304381806427</v>
       </c>
-      <c r="Q49">
+      <c r="T49">
         <v>1.9</v>
       </c>
-      <c r="R49" s="16">
-        <f t="shared" si="13"/>
+      <c r="U49" s="16">
+        <f t="shared" si="16"/>
         <v>-235.59595300000001</v>
       </c>
     </row>
-    <row r="50" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3">
+        <f t="shared" si="18"/>
+        <v>224.35517386157449</v>
+      </c>
+      <c r="H50" s="8">
         <f t="shared" si="15"/>
-        <v>224.35517386157449</v>
-      </c>
-      <c r="H50" s="8">
-        <f t="shared" si="12"/>
         <v>224</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J50" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.1441484796139115E-2</v>
+      </c>
+      <c r="K50" s="4">
+        <f t="shared" si="8"/>
+        <v>1339.2857142857142</v>
+      </c>
+      <c r="M50" t="str">
+        <f t="shared" si="20"/>
+        <v>0xE05AECAC,</v>
+      </c>
+      <c r="N50" s="19">
+        <f t="shared" si="21"/>
+        <v>1337.1655078705598</v>
+      </c>
+      <c r="O50" s="19">
+        <f t="shared" si="9"/>
+        <v>803.57142857142856</v>
+      </c>
+      <c r="P50" s="19">
+        <f t="shared" si="10"/>
+        <v>3.3482142857142856</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="17"/>
+        <v>-749.82914759977302</v>
+      </c>
+      <c r="T50">
+        <v>2</v>
+      </c>
+      <c r="U50" s="16">
         <f t="shared" si="16"/>
-        <v>-1.1441484796139115E-2</v>
-      </c>
-      <c r="L50" t="str">
-        <f t="shared" si="17"/>
-        <v>0xE05AECAC,</v>
-      </c>
-      <c r="M50" s="19">
-        <f t="shared" si="18"/>
-        <v>1337.1655078705598</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="14"/>
-        <v>-749.82914759977302</v>
-      </c>
-      <c r="Q50">
-        <v>2</v>
-      </c>
-      <c r="R50" s="16">
-        <f t="shared" si="13"/>
         <v>-199.99600000000009</v>
       </c>
     </row>
-    <row r="51" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3">
+        <f t="shared" si="18"/>
+        <v>221.88773069418372</v>
+      </c>
+      <c r="H51" s="8">
         <f t="shared" si="15"/>
-        <v>221.88773069418372</v>
-      </c>
-      <c r="H51" s="8">
-        <f t="shared" si="12"/>
         <v>222</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J51" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.1185609786323847E-2</v>
+      </c>
+      <c r="K51" s="4">
+        <f t="shared" si="8"/>
+        <v>1351.3513513513512</v>
+      </c>
+      <c r="M51" t="str">
+        <f t="shared" si="20"/>
+        <v>0xDDE34251,</v>
+      </c>
+      <c r="N51" s="19">
+        <f t="shared" si="21"/>
+        <v>1352.0350992884521</v>
+      </c>
+      <c r="O51" s="19">
+        <f t="shared" si="9"/>
+        <v>810.81081081081084</v>
+      </c>
+      <c r="P51" s="19">
+        <f t="shared" si="10"/>
+        <v>3.3783783783783781</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="17"/>
+        <v>-733.06012295651965</v>
+      </c>
+      <c r="T51">
+        <v>2.1</v>
+      </c>
+      <c r="U51" s="16">
         <f t="shared" si="16"/>
-        <v>-1.1185609786323847E-2</v>
-      </c>
-      <c r="L51" t="str">
-        <f t="shared" si="17"/>
-        <v>0xDDE34251,</v>
-      </c>
-      <c r="M51" s="19">
-        <f t="shared" si="18"/>
-        <v>1352.0350992884521</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="14"/>
-        <v>-733.06012295651965</v>
-      </c>
-      <c r="Q51">
-        <v>2.1</v>
-      </c>
-      <c r="R51" s="16">
-        <f t="shared" si="13"/>
         <v>-162.39608700000031</v>
       </c>
     </row>
-    <row r="52" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3">
+        <f t="shared" si="18"/>
+        <v>219.49991477352964</v>
+      </c>
+      <c r="H52" s="8">
         <f t="shared" si="15"/>
-        <v>219.49991477352964</v>
-      </c>
-      <c r="H52" s="8">
-        <f t="shared" si="12"/>
         <v>219</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I52" s="41">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="J52" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.0940925562803244E-2</v>
+      </c>
+      <c r="K52" s="4">
+        <f t="shared" si="8"/>
+        <v>1369.8630136986301</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" si="20"/>
+        <v>0xDB7FFA6A,</v>
+      </c>
+      <c r="N52" s="19">
+        <f t="shared" si="21"/>
+        <v>1366.7431274837934</v>
+      </c>
+      <c r="O52" s="19">
+        <f t="shared" si="9"/>
+        <v>821.91780821917814</v>
+      </c>
+      <c r="P52" s="19">
+        <f t="shared" si="10"/>
+        <v>3.4246575342465753</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="17"/>
+        <v>-717.02449768387339</v>
+      </c>
+      <c r="T52">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U52" s="16">
         <f t="shared" si="16"/>
-        <v>-1.0940925562803244E-2</v>
-      </c>
-      <c r="L52" t="str">
-        <f t="shared" si="17"/>
-        <v>0xDB7FFA6A,</v>
-      </c>
-      <c r="M52" s="19">
-        <f t="shared" si="18"/>
-        <v>1366.7431274837934</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="14"/>
-        <v>-717.02449768387339</v>
-      </c>
-      <c r="Q52">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="R52" s="16">
-        <f t="shared" si="13"/>
         <v>-123.19621600000005</v>
       </c>
     </row>
-    <row r="53" spans="5:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="5:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3">
+        <f t="shared" si="18"/>
+        <v>217.18753512178537</v>
+      </c>
+      <c r="H53" s="8">
         <f t="shared" si="15"/>
-        <v>217.18753512178537</v>
-      </c>
-      <c r="H53" s="8">
-        <f t="shared" si="12"/>
         <v>217</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I53" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J53" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.0706713907908172E-2</v>
+      </c>
+      <c r="K53" s="4">
+        <f t="shared" si="8"/>
+        <v>1382.4884792626729</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="20"/>
+        <v>0xD930024D,</v>
+      </c>
+      <c r="N53" s="19">
+        <f t="shared" si="21"/>
+        <v>1381.2947406570938</v>
+      </c>
+      <c r="O53" s="19">
+        <f t="shared" si="9"/>
+        <v>829.49308755760376</v>
+      </c>
+      <c r="P53" s="19">
+        <f t="shared" si="10"/>
+        <v>3.4562211981566819</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="17"/>
+        <v>-701.67520266866995</v>
+      </c>
+      <c r="T53">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="U53" s="16">
         <f t="shared" si="16"/>
-        <v>-1.0706713907908172E-2</v>
-      </c>
-      <c r="L53" t="str">
-        <f t="shared" si="17"/>
-        <v>0xD930024D,</v>
-      </c>
-      <c r="M53" s="19">
-        <f t="shared" si="18"/>
-        <v>1381.2947406570938</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="14"/>
-        <v>-701.67520266866995</v>
-      </c>
-      <c r="Q53">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="R53" s="16">
-        <f t="shared" si="13"/>
         <v>-82.79638900000009</v>
       </c>
     </row>
-    <row r="54" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>214.9467030949196</v>
       </c>
       <c r="H54" s="12">
         <f>ROUND(G54,0)</f>
         <v>215</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I54" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.0482316758283722E-2</v>
+      </c>
+      <c r="K54" s="4">
+        <f t="shared" si="8"/>
+        <v>1395.3488372093022</v>
+      </c>
+      <c r="O54" s="19">
+        <f t="shared" si="9"/>
+        <v>837.20930232558135</v>
+      </c>
+      <c r="P54" s="19">
+        <f t="shared" si="10"/>
+        <v>3.4883720930232558</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="17"/>
+        <v>-686.96911107088204</v>
+      </c>
+      <c r="T54">
+        <v>2.4</v>
+      </c>
+      <c r="U54" s="16">
         <f t="shared" si="16"/>
-        <v>-1.0482316758283722E-2</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="14"/>
-        <v>-686.96911107088204</v>
-      </c>
-      <c r="Q54">
-        <v>2.4</v>
-      </c>
-      <c r="R54" s="16">
-        <f t="shared" si="13"/>
         <v>-41.59660800000006</v>
       </c>
     </row>
-    <row r="55" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>212.77380491747817</v>
       </c>
       <c r="H55" s="13">
         <f>ROUND(G55,0)</f>
         <v>213</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I55" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J55" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.0267130038083449E-2</v>
+      </c>
+      <c r="K55" s="4">
+        <f t="shared" si="8"/>
+        <v>1408.4507042253522</v>
+      </c>
+      <c r="O55" s="19">
+        <f t="shared" si="9"/>
+        <v>845.07042253521126</v>
+      </c>
+      <c r="P55" s="19">
+        <f t="shared" si="10"/>
+        <v>3.5211267605633805</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="17"/>
+        <v>-672.86663417583691</v>
+      </c>
+      <c r="T55">
+        <v>2.5</v>
+      </c>
+      <c r="U55" s="16">
         <f t="shared" si="16"/>
-        <v>-1.0267130038083449E-2</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="14"/>
-        <v>-672.86663417583691</v>
-      </c>
-      <c r="Q55">
-        <v>2.5</v>
-      </c>
-      <c r="R55" s="16">
-        <f t="shared" si="13"/>
         <v>3.1249999997271516E-3</v>
       </c>
     </row>
-    <row r="56" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>210.66547720545293</v>
       </c>
       <c r="H56" s="13">
         <f>ROUND(G56,0)</f>
         <v>211</v>
       </c>
-      <c r="I56" s="2">
+      <c r="I56" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2">
+        <f t="shared" si="19"/>
+        <v>-1.0060598235346902E-2</v>
+      </c>
+      <c r="K56" s="4">
+        <f t="shared" si="8"/>
+        <v>1421.8009478672986</v>
+      </c>
+      <c r="O56" s="19">
+        <f t="shared" si="9"/>
+        <v>853.08056872037923</v>
+      </c>
+      <c r="P56" s="19">
+        <f t="shared" si="10"/>
+        <v>3.5545023696682465</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="17"/>
+        <v>-659.33136595169458</v>
+      </c>
+      <c r="T56">
+        <v>2.6</v>
+      </c>
+      <c r="U56" s="16">
         <f t="shared" si="16"/>
-        <v>-1.0060598235346902E-2</v>
-      </c>
-      <c r="N56">
-        <f t="shared" si="14"/>
-        <v>-659.33136595169458</v>
-      </c>
-      <c r="Q56">
-        <v>2.6</v>
-      </c>
-      <c r="R56" s="16">
-        <f t="shared" si="13"/>
         <v>41.602807999999641</v>
       </c>
     </row>
-    <row r="57" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>208.61858510062589</v>
       </c>
       <c r="H57" s="8">
         <f>ROUND(G57,0)</f>
         <v>209</v>
       </c>
-      <c r="I57" s="2">
+      <c r="I57" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J57" s="2">
+        <f t="shared" si="19"/>
+        <v>-9.8622096191558241E-3</v>
+      </c>
+      <c r="K57" s="4">
+        <f t="shared" si="8"/>
+        <v>1435.4066985645934</v>
+      </c>
+      <c r="O57" s="19">
+        <f t="shared" si="9"/>
+        <v>861.24401913875602</v>
+      </c>
+      <c r="P57" s="19">
+        <f t="shared" si="10"/>
+        <v>3.5885167464114835</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="17"/>
+        <v>-646.32976960099609</v>
+      </c>
+      <c r="T57">
+        <v>2.7</v>
+      </c>
+      <c r="U57" s="16">
         <f t="shared" si="16"/>
-        <v>-9.8622096191558241E-3</v>
-      </c>
-      <c r="N57">
-        <f t="shared" si="14"/>
-        <v>-646.32976960099609</v>
-      </c>
-      <c r="Q57">
-        <v>2.7</v>
-      </c>
-      <c r="R57" s="16">
-        <f t="shared" si="13"/>
         <v>82.802438999999595</v>
       </c>
     </row>
-    <row r="58" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>206.63020269348732</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" ref="H58:H111" si="19">ROUND(G58,0)</f>
+        <f t="shared" ref="H58:H111" si="22">ROUND(G58,0)</f>
         <v>207</v>
       </c>
-      <c r="I58" s="2">
+      <c r="I58" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J58" s="2">
+        <f t="shared" si="19"/>
+        <v>-9.6714920109749088E-3</v>
+      </c>
+      <c r="K58" s="4">
+        <f t="shared" si="8"/>
+        <v>1449.2753623188405</v>
+      </c>
+      <c r="O58" s="19">
+        <f t="shared" si="9"/>
+        <v>869.56521739130437</v>
+      </c>
+      <c r="P58" s="19">
+        <f t="shared" si="10"/>
+        <v>3.6231884057971011</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="17"/>
+        <v>-633.83090043125162</v>
+      </c>
+      <c r="T58">
+        <v>2.8</v>
+      </c>
+      <c r="U58" s="16">
         <f t="shared" si="16"/>
-        <v>-9.6714920109749088E-3</v>
-      </c>
-      <c r="N58">
-        <f t="shared" si="14"/>
-        <v>-633.83090043125162</v>
-      </c>
-      <c r="Q58">
-        <v>2.8</v>
-      </c>
-      <c r="R58" s="16">
-        <f t="shared" si="13"/>
         <v>123.20201599999973</v>
       </c>
     </row>
-    <row r="59" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>204.69759545701831</v>
       </c>
       <c r="H59" s="8">
+        <f t="shared" si="22"/>
+        <v>205</v>
+      </c>
+      <c r="I59" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J59" s="2">
         <f t="shared" si="19"/>
-        <v>205</v>
-      </c>
-      <c r="I59" s="2">
+        <v>-9.4880090367003671E-3</v>
+      </c>
+      <c r="K59" s="4">
+        <f t="shared" si="8"/>
+        <v>1463.4146341463415</v>
+      </c>
+      <c r="O59" s="19">
+        <f t="shared" si="9"/>
+        <v>878.04878048780495</v>
+      </c>
+      <c r="P59" s="19">
+        <f t="shared" si="10"/>
+        <v>3.6585365853658538</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="17"/>
+        <v>-621.80616022919526</v>
+      </c>
+      <c r="T59">
+        <v>2.9</v>
+      </c>
+      <c r="U59" s="16">
         <f t="shared" si="16"/>
-        <v>-9.4880090367003671E-3</v>
-      </c>
-      <c r="N59">
-        <f t="shared" si="14"/>
-        <v>-621.80616022919526</v>
-      </c>
-      <c r="Q59">
-        <v>2.9</v>
-      </c>
-      <c r="R59" s="16">
-        <f t="shared" si="13"/>
         <v>162.40153699999973</v>
       </c>
     </row>
-    <row r="60" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>202.81820445178789</v>
       </c>
       <c r="H60" s="8">
+        <f t="shared" si="22"/>
+        <v>203</v>
+      </c>
+      <c r="I60" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J60" s="2">
         <f t="shared" si="19"/>
-        <v>203</v>
-      </c>
-      <c r="I60" s="2">
+        <v>-9.3113567968633598E-3</v>
+      </c>
+      <c r="K60" s="4">
+        <f t="shared" si="8"/>
+        <v>1477.8325123152708</v>
+      </c>
+      <c r="O60" s="19">
+        <f t="shared" si="9"/>
+        <v>886.69950738916248</v>
+      </c>
+      <c r="P60" s="19">
+        <f t="shared" si="10"/>
+        <v>3.694581280788177</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="17"/>
+        <v>-610.22907903923715</v>
+      </c>
+      <c r="T60">
+        <v>3</v>
+      </c>
+      <c r="U60" s="16">
         <f t="shared" si="16"/>
-        <v>-9.3113567968633598E-3</v>
-      </c>
-      <c r="N60">
-        <f t="shared" si="14"/>
-        <v>-610.22907903923715</v>
-      </c>
-      <c r="Q60">
-        <v>3</v>
-      </c>
-      <c r="R60" s="16">
-        <f t="shared" si="13"/>
         <v>200.00099999999975</v>
       </c>
     </row>
-    <row r="61" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>200.98963209513937</v>
       </c>
       <c r="H61" s="8">
+        <f t="shared" si="22"/>
+        <v>201</v>
+      </c>
+      <c r="I61" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J61" s="2">
         <f t="shared" si="19"/>
-        <v>201</v>
-      </c>
-      <c r="I61" s="2">
+        <v>-9.1411609015660516E-3</v>
+      </c>
+      <c r="K61" s="4">
+        <f t="shared" si="8"/>
+        <v>1492.5373134328358</v>
+      </c>
+      <c r="O61" s="19">
+        <f t="shared" si="9"/>
+        <v>895.52238805970148</v>
+      </c>
+      <c r="P61" s="19">
+        <f t="shared" si="10"/>
+        <v>3.7313432835820897</v>
+      </c>
+      <c r="Q61">
+        <f t="shared" si="17"/>
+        <v>-599.07512084503276</v>
+      </c>
+      <c r="T61">
+        <v>3.1</v>
+      </c>
+      <c r="U61" s="16">
         <f t="shared" si="16"/>
-        <v>-9.1411609015660516E-3</v>
-      </c>
-      <c r="N61">
-        <f t="shared" si="14"/>
-        <v>-599.07512084503276</v>
-      </c>
-      <c r="Q61">
-        <v>3.1</v>
-      </c>
-      <c r="R61" s="16">
-        <f t="shared" si="13"/>
         <v>235.60040300000037</v>
       </c>
     </row>
-    <row r="62" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>199.20962931471041</v>
       </c>
       <c r="H62" s="8">
+        <f t="shared" si="22"/>
+        <v>199</v>
+      </c>
+      <c r="I62" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J62" s="2">
         <f t="shared" si="19"/>
-        <v>199</v>
-      </c>
-      <c r="I62" s="2">
+        <v>-8.9770738243865507E-3</v>
+      </c>
+      <c r="K62" s="4">
+        <f t="shared" si="8"/>
+        <v>1507.537688442211</v>
+      </c>
+      <c r="O62" s="19">
+        <f t="shared" si="9"/>
+        <v>904.5226130653266</v>
+      </c>
+      <c r="P62" s="19">
+        <f t="shared" si="10"/>
+        <v>3.7688442211055273</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" si="17"/>
+        <v>-588.32151015499699</v>
+      </c>
+      <c r="T62">
+        <v>3.2</v>
+      </c>
+      <c r="U62" s="16">
         <f t="shared" si="16"/>
-        <v>-8.9770738243865507E-3</v>
-      </c>
-      <c r="N62">
-        <f t="shared" si="14"/>
-        <v>-588.32151015499699</v>
-      </c>
-      <c r="Q62">
-        <v>3.2</v>
-      </c>
-      <c r="R62" s="16">
-        <f t="shared" si="13"/>
         <v>268.79974399999992</v>
       </c>
     </row>
-    <row r="63" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>197.47608392994803</v>
       </c>
       <c r="H63" s="8">
+        <f t="shared" si="22"/>
+        <v>197</v>
+      </c>
+      <c r="I63" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J63" s="2">
         <f t="shared" si="19"/>
-        <v>197</v>
-      </c>
-      <c r="I63" s="2">
+        <v>-8.818772535934296E-3</v>
+      </c>
+      <c r="K63" s="4">
+        <f t="shared" si="8"/>
+        <v>1522.8426395939086</v>
+      </c>
+      <c r="O63" s="19">
+        <f t="shared" si="9"/>
+        <v>913.70558375634516</v>
+      </c>
+      <c r="P63" s="19">
+        <f t="shared" si="10"/>
+        <v>3.8071065989847717</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" si="17"/>
+        <v>-577.94707691499002</v>
+      </c>
+      <c r="T63">
+        <v>3.3</v>
+      </c>
+      <c r="U63" s="16">
         <f t="shared" si="16"/>
-        <v>-8.818772535934296E-3</v>
-      </c>
-      <c r="N63">
-        <f t="shared" si="14"/>
-        <v>-577.94707691499002</v>
-      </c>
-      <c r="Q63">
-        <v>3.3</v>
-      </c>
-      <c r="R63" s="16">
-        <f t="shared" si="13"/>
         <v>299.19902099999899</v>
       </c>
     </row>
-    <row r="64" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>195.78701012529817</v>
       </c>
       <c r="H64" s="8">
+        <f t="shared" si="22"/>
+        <v>196</v>
+      </c>
+      <c r="I64" s="41">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2">
         <f t="shared" si="19"/>
-        <v>196</v>
-      </c>
-      <c r="I64" s="2">
+        <v>-8.6659563831795287E-3</v>
+      </c>
+      <c r="K64" s="4">
+        <f t="shared" si="8"/>
+        <v>1530.6122448979593</v>
+      </c>
+      <c r="O64" s="19">
+        <f t="shared" si="9"/>
+        <v>918.36734693877554</v>
+      </c>
+      <c r="P64" s="19">
+        <f t="shared" si="10"/>
+        <v>3.8265306122448983</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="17"/>
+        <v>-567.9321175280536</v>
+      </c>
+      <c r="T64">
+        <v>3.4</v>
+      </c>
+      <c r="U64" s="16">
         <f t="shared" si="16"/>
-        <v>-8.6659563831795287E-3</v>
-      </c>
-      <c r="N64">
-        <f t="shared" si="14"/>
-        <v>-567.9321175280536</v>
-      </c>
-      <c r="Q64">
-        <v>3.4</v>
-      </c>
-      <c r="R64" s="16">
-        <f t="shared" si="13"/>
         <v>326.3982319999991</v>
       </c>
     </row>
-    <row r="65" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>194.14053889591329</v>
       </c>
       <c r="H65" s="8">
+        <f t="shared" si="22"/>
+        <v>194</v>
+      </c>
+      <c r="I65" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J65" s="2">
         <f t="shared" si="19"/>
-        <v>194</v>
-      </c>
-      <c r="I65" s="2">
+        <v>-8.5183451852896899E-3</v>
+      </c>
+      <c r="K65" s="4">
+        <f t="shared" si="8"/>
+        <v>1546.3917525773195</v>
+      </c>
+      <c r="O65" s="19">
+        <f t="shared" si="9"/>
+        <v>927.83505154639158</v>
+      </c>
+      <c r="P65" s="19">
+        <f t="shared" si="10"/>
+        <v>3.8659793814432986</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="17"/>
+        <v>-558.25827006314512</v>
+      </c>
+      <c r="T65">
+        <v>3.5</v>
+      </c>
+      <c r="U65" s="16">
         <f t="shared" si="16"/>
-        <v>-8.5183451852896899E-3</v>
-      </c>
-      <c r="N65">
-        <f t="shared" si="14"/>
-        <v>-558.25827006314512</v>
-      </c>
-      <c r="Q65">
-        <v>3.5</v>
-      </c>
-      <c r="R65" s="16">
-        <f t="shared" si="13"/>
         <v>349.99737499999992</v>
       </c>
     </row>
-    <row r="66" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>192.53490936147639</v>
       </c>
       <c r="H66" s="8">
+        <f t="shared" si="22"/>
+        <v>193</v>
+      </c>
+      <c r="I66" s="41">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2">
         <f t="shared" si="19"/>
-        <v>193</v>
-      </c>
-      <c r="I66" s="2">
+        <v>-8.375677520621249E-3</v>
+      </c>
+      <c r="K66" s="4">
+        <f t="shared" si="8"/>
+        <v>1554.4041450777202</v>
+      </c>
+      <c r="O66" s="19">
+        <f t="shared" si="9"/>
+        <v>932.64248704663214</v>
+      </c>
+      <c r="P66" s="19">
+        <f t="shared" si="10"/>
+        <v>3.8860103626943006</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="17"/>
+        <v>-548.90840199143418</v>
+      </c>
+      <c r="T66">
+        <v>3.6</v>
+      </c>
+      <c r="U66" s="16">
         <f t="shared" si="16"/>
-        <v>-8.375677520621249E-3</v>
-      </c>
-      <c r="N66">
-        <f t="shared" si="14"/>
-        <v>-548.90840199143418</v>
-      </c>
-      <c r="Q66">
-        <v>3.6</v>
-      </c>
-      <c r="R66" s="16">
-        <f t="shared" si="13"/>
         <v>369.59644799999933</v>
       </c>
     </row>
-    <row r="67" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>190.9684608564589</v>
       </c>
       <c r="H67" s="8">
+        <f t="shared" si="22"/>
+        <v>191</v>
+      </c>
+      <c r="I67" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J67" s="2">
         <f t="shared" si="19"/>
-        <v>191</v>
-      </c>
-      <c r="I67" s="2">
+        <v>-8.2377091828515405E-3</v>
+      </c>
+      <c r="K67" s="4">
+        <f t="shared" si="8"/>
+        <v>1570.6806282722514</v>
+      </c>
+      <c r="O67" s="19">
+        <f t="shared" si="9"/>
+        <v>942.40837696335086</v>
+      </c>
+      <c r="P67" s="19">
+        <f t="shared" si="10"/>
+        <v>3.9267015706806285</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="17"/>
+        <v>-539.86650900735856</v>
+      </c>
+      <c r="T67">
+        <v>3.7</v>
+      </c>
+      <c r="U67" s="16">
         <f t="shared" si="16"/>
-        <v>-8.2377091828515405E-3</v>
-      </c>
-      <c r="N67">
-        <f t="shared" si="14"/>
-        <v>-539.86650900735856</v>
-      </c>
-      <c r="Q67">
-        <v>3.7</v>
-      </c>
-      <c r="R67" s="16">
-        <f t="shared" si="13"/>
         <v>384.79544900000019</v>
       </c>
     </row>
-    <row r="68" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>189.4396257161205</v>
       </c>
       <c r="H68" s="8">
+        <f t="shared" si="22"/>
+        <v>189</v>
+      </c>
+      <c r="I68" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J68" s="2">
         <f t="shared" si="19"/>
-        <v>189</v>
-      </c>
-      <c r="I68" s="2">
+        <v>-8.104211787085527E-3</v>
+      </c>
+      <c r="K68" s="4">
+        <f t="shared" si="8"/>
+        <v>1587.3015873015872</v>
+      </c>
+      <c r="O68" s="19">
+        <f t="shared" si="9"/>
+        <v>952.38095238095241</v>
+      </c>
+      <c r="P68" s="19">
+        <f t="shared" si="10"/>
+        <v>3.9682539682539679</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="17"/>
+        <v>-531.1176236784371</v>
+      </c>
+      <c r="T68">
+        <v>3.8</v>
+      </c>
+      <c r="U68" s="16">
         <f t="shared" si="16"/>
-        <v>-8.104211787085527E-3</v>
-      </c>
-      <c r="N68">
-        <f t="shared" si="14"/>
-        <v>-531.1176236784371</v>
-      </c>
-      <c r="Q68">
-        <v>3.8</v>
-      </c>
-      <c r="R68" s="16">
-        <f t="shared" si="13"/>
         <v>395.19437600000037</v>
       </c>
     </row>
-    <row r="69" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>187.94692268708141</v>
       </c>
       <c r="H69" s="8">
+        <f t="shared" si="22"/>
+        <v>188</v>
+      </c>
+      <c r="I69" s="41">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
         <f t="shared" si="19"/>
-        <v>188</v>
-      </c>
-      <c r="I69" s="2">
+        <v>-7.9749715092141838E-3</v>
+      </c>
+      <c r="K69" s="4">
+        <f t="shared" si="8"/>
+        <v>1595.7446808510638</v>
+      </c>
+      <c r="O69" s="19">
+        <f t="shared" si="9"/>
+        <v>957.44680851063822</v>
+      </c>
+      <c r="P69" s="19">
+        <f t="shared" si="10"/>
+        <v>3.9893617021276593</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="17"/>
+        <v>-522.64773282786075</v>
+      </c>
+      <c r="T69">
+        <v>3.9</v>
+      </c>
+      <c r="U69" s="16">
         <f t="shared" si="16"/>
-        <v>-7.9749715092141838E-3</v>
-      </c>
-      <c r="N69">
-        <f t="shared" si="14"/>
-        <v>-522.64773282786075</v>
-      </c>
-      <c r="Q69">
-        <v>3.9</v>
-      </c>
-      <c r="R69" s="16">
-        <f t="shared" si="13"/>
         <v>400.39322699999911</v>
       </c>
     </row>
-    <row r="70" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>186.488950899565</v>
       </c>
       <c r="H70" s="8">
+        <f t="shared" si="22"/>
+        <v>186</v>
+      </c>
+      <c r="I70" s="41">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="J70" s="2">
         <f t="shared" si="19"/>
-        <v>186</v>
-      </c>
-      <c r="I70" s="2">
+        <v>-7.8497879438986125E-3</v>
+      </c>
+      <c r="K70" s="4">
+        <f t="shared" ref="K70:K111" si="23">$B$12/H70</f>
+        <v>1612.9032258064517</v>
+      </c>
+      <c r="O70" s="19">
+        <f t="shared" ref="O70:O90" si="24">K70*60/400*O$2</f>
+        <v>967.74193548387109</v>
+      </c>
+      <c r="P70" s="19">
+        <f t="shared" ref="P70:P79" si="25">K70/400</f>
+        <v>4.032258064516129</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="17"/>
+        <v>-514.44370269133947</v>
+      </c>
+      <c r="T70">
+        <v>4</v>
+      </c>
+      <c r="U70" s="16">
         <f t="shared" si="16"/>
-        <v>-7.8497879438986125E-3</v>
-      </c>
-      <c r="N70">
-        <f t="shared" si="14"/>
-        <v>-514.44370269133947</v>
-      </c>
-      <c r="Q70">
-        <v>4</v>
-      </c>
-      <c r="R70" s="16">
-        <f t="shared" si="13"/>
         <v>399.99199999999973</v>
       </c>
     </row>
-    <row r="71" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>185.06438434560565</v>
       </c>
       <c r="H71" s="8">
+        <f t="shared" si="22"/>
+        <v>185</v>
+      </c>
+      <c r="I71" s="41">
+        <f t="shared" ref="I71:I111" si="26">H70-H71</f>
+        <v>1</v>
+      </c>
+      <c r="J71" s="2">
         <f t="shared" si="19"/>
-        <v>185</v>
-      </c>
-      <c r="I71" s="2">
-        <f t="shared" si="16"/>
         <v>-7.7284730683600802E-3</v>
       </c>
-      <c r="Q71">
+      <c r="K71" s="4">
+        <f t="shared" si="23"/>
+        <v>1621.6216216216217</v>
+      </c>
+      <c r="O71" s="19">
+        <f t="shared" si="24"/>
+        <v>972.97297297297303</v>
+      </c>
+      <c r="P71" s="19">
+        <f t="shared" si="25"/>
+        <v>4.0540540540540544</v>
+      </c>
+      <c r="T71">
         <v>4.0999999999999996</v>
       </c>
-      <c r="R71" s="16">
-        <f t="shared" ref="R71:R86" si="20" xml:space="preserve"> -66.667*POWER(Q71,3) + 500*POWER(Q71,2) - 833.33*Q71</f>
+      <c r="U71" s="16">
+        <f t="shared" ref="U71:U86" si="27" xml:space="preserve"> -66.667*POWER(T71,3) + 500*POWER(T71,2) - 833.33*T71</f>
         <v>393.59069300000056</v>
       </c>
     </row>
-    <row r="72" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>183.6719668137944</v>
       </c>
       <c r="H72" s="8">
+        <f t="shared" si="22"/>
+        <v>184</v>
+      </c>
+      <c r="I72" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J72" s="2">
         <f t="shared" si="19"/>
-        <v>184</v>
-      </c>
-      <c r="I72" s="2">
-        <f t="shared" si="16"/>
         <v>-7.6108503007151218E-3</v>
       </c>
-      <c r="Q72">
+      <c r="K72" s="4">
+        <f t="shared" si="23"/>
+        <v>1630.4347826086957</v>
+      </c>
+      <c r="O72" s="19">
+        <f t="shared" si="24"/>
+        <v>978.26086956521749</v>
+      </c>
+      <c r="P72" s="19">
+        <f t="shared" si="25"/>
+        <v>4.0760869565217392</v>
+      </c>
+      <c r="T72">
         <v>4.2</v>
       </c>
-      <c r="R72" s="16">
-        <f t="shared" si="20"/>
+      <c r="U72" s="16">
+        <f t="shared" si="27"/>
         <v>380.78930399999945</v>
       </c>
     </row>
-    <row r="73" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>182.31050723662219</v>
       </c>
       <c r="H73" s="8">
+        <f t="shared" si="22"/>
+        <v>182</v>
+      </c>
+      <c r="I73" s="41">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="J73" s="2">
         <f t="shared" si="19"/>
-        <v>182</v>
-      </c>
-      <c r="I73" s="2">
-        <f t="shared" si="16"/>
         <v>-7.4967536429439091E-3</v>
       </c>
-      <c r="Q73">
+      <c r="K73" s="4">
+        <f t="shared" si="23"/>
+        <v>1648.3516483516485</v>
+      </c>
+      <c r="O73" s="19">
+        <f t="shared" si="24"/>
+        <v>989.01098901098919</v>
+      </c>
+      <c r="P73" s="19">
+        <f t="shared" si="25"/>
+        <v>4.1208791208791213</v>
+      </c>
+      <c r="T73">
         <v>4.3</v>
       </c>
-      <c r="R73" s="16">
-        <f t="shared" si="20"/>
+      <c r="U73" s="16">
+        <f t="shared" si="27"/>
         <v>361.18783100000064</v>
       </c>
     </row>
-    <row r="74" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>180.9788754112889</v>
       </c>
       <c r="H74" s="8">
+        <f t="shared" si="22"/>
+        <v>181</v>
+      </c>
+      <c r="I74" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2">
         <f t="shared" si="19"/>
-        <v>181</v>
-      </c>
-      <c r="I74" s="2">
-        <f t="shared" si="16"/>
         <v>-7.3860268997498818E-3</v>
       </c>
-      <c r="Q74">
+      <c r="K74" s="4">
+        <f t="shared" si="23"/>
+        <v>1657.4585635359117</v>
+      </c>
+      <c r="O74" s="19">
+        <f t="shared" si="24"/>
+        <v>994.47513812154705</v>
+      </c>
+      <c r="P74" s="19">
+        <f t="shared" si="25"/>
+        <v>4.1436464088397793</v>
+      </c>
+      <c r="T74">
         <v>4.4000000000000004</v>
       </c>
-      <c r="R74" s="16">
-        <f t="shared" si="20"/>
+      <c r="U74" s="16">
+        <f t="shared" si="27"/>
         <v>334.38627199999928</v>
       </c>
     </row>
-    <row r="75" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>179.67599805906545</v>
       </c>
       <c r="H75" s="8">
+        <f t="shared" si="22"/>
+        <v>180</v>
+      </c>
+      <c r="I75" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2">
         <f t="shared" si="19"/>
-        <v>180</v>
-      </c>
-      <c r="I75" s="2">
-        <f t="shared" si="16"/>
         <v>-7.2785229655855177E-3</v>
       </c>
-      <c r="Q75">
+      <c r="K75" s="4">
+        <f t="shared" si="23"/>
+        <v>1666.6666666666667</v>
+      </c>
+      <c r="O75" s="19">
+        <f t="shared" si="24"/>
+        <v>1000</v>
+      </c>
+      <c r="P75" s="19">
+        <f t="shared" si="25"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="T75">
         <v>4.5</v>
       </c>
-      <c r="R75" s="16">
-        <f t="shared" si="20"/>
+      <c r="U75" s="16">
+        <f t="shared" si="27"/>
         <v>299.9846249999996</v>
       </c>
     </row>
-    <row r="76" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>178.40085519200866</v>
       </c>
       <c r="H76" s="8">
+        <f t="shared" si="22"/>
+        <v>178</v>
+      </c>
+      <c r="I76" s="41">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="J76" s="2">
         <f t="shared" si="19"/>
-        <v>178</v>
-      </c>
-      <c r="I76" s="2">
-        <f t="shared" si="16"/>
         <v>-7.1741031730047306E-3</v>
       </c>
-      <c r="Q76">
+      <c r="K76" s="4">
+        <f t="shared" si="23"/>
+        <v>1685.3932584269662</v>
+      </c>
+      <c r="O76" s="19">
+        <f t="shared" si="24"/>
+        <v>1011.2359550561797</v>
+      </c>
+      <c r="P76" s="19">
+        <f t="shared" si="25"/>
+        <v>4.2134831460674151</v>
+      </c>
+      <c r="T76">
         <v>4.5999999999999996</v>
       </c>
-      <c r="R76" s="16">
-        <f t="shared" si="20"/>
+      <c r="U76" s="16">
+        <f t="shared" si="27"/>
         <v>257.58288800000037</v>
       </c>
     </row>
-    <row r="77" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>177.1524767590991</v>
       </c>
       <c r="H77" s="8">
+        <f t="shared" si="22"/>
+        <v>177</v>
+      </c>
+      <c r="I77" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J77" s="2">
         <f t="shared" si="19"/>
-        <v>177</v>
-      </c>
-      <c r="I77" s="2">
-        <f t="shared" si="16"/>
         <v>-7.072636696275566E-3</v>
       </c>
-      <c r="Q77">
+      <c r="K77" s="4">
+        <f t="shared" si="23"/>
+        <v>1694.9152542372881</v>
+      </c>
+      <c r="O77" s="19">
+        <f t="shared" si="24"/>
+        <v>1016.9491525423729</v>
+      </c>
+      <c r="P77" s="19">
+        <f t="shared" si="25"/>
+        <v>4.2372881355932206</v>
+      </c>
+      <c r="T77">
         <v>4.7</v>
       </c>
-      <c r="R77" s="16">
-        <f t="shared" si="20"/>
+      <c r="U77" s="16">
+        <f t="shared" si="27"/>
         <v>206.78105899999946</v>
       </c>
     </row>
-    <row r="78" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>175.92993954675978</v>
       </c>
       <c r="H78" s="8">
+        <f t="shared" si="22"/>
+        <v>176</v>
+      </c>
+      <c r="I78" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2">
         <f t="shared" si="19"/>
-        <v>176</v>
-      </c>
-      <c r="I78" s="2">
-        <f t="shared" si="16"/>
         <v>-6.9740000048629219E-3</v>
       </c>
-      <c r="Q78">
+      <c r="K78" s="4">
+        <f t="shared" si="23"/>
+        <v>1704.5454545454545</v>
+      </c>
+      <c r="O78" s="19">
+        <f t="shared" si="24"/>
+        <v>1022.7272727272726</v>
+      </c>
+      <c r="P78" s="19">
+        <f t="shared" si="25"/>
+        <v>4.2613636363636367</v>
+      </c>
+      <c r="T78">
         <v>4.8</v>
       </c>
-      <c r="R78" s="16">
-        <f t="shared" si="20"/>
+      <c r="U78" s="16">
+        <f t="shared" si="27"/>
         <v>147.1791360000002</v>
       </c>
     </row>
-    <row r="79" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>174.7323643112675</v>
       </c>
       <c r="H79" s="8">
+        <f t="shared" si="22"/>
+        <v>175</v>
+      </c>
+      <c r="I79" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2">
         <f t="shared" si="19"/>
-        <v>175</v>
-      </c>
-      <c r="I79" s="2">
-        <f t="shared" si="16"/>
         <v>-6.8780763619836777E-3</v>
       </c>
-      <c r="Q79">
+      <c r="K79" s="4">
+        <f t="shared" si="23"/>
+        <v>1714.2857142857142</v>
+      </c>
+      <c r="O79" s="19">
+        <f t="shared" si="24"/>
+        <v>1028.5714285714284</v>
+      </c>
+      <c r="P79" s="19">
+        <f t="shared" si="25"/>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="T79">
         <v>4.9000000000000004</v>
       </c>
-      <c r="R79" s="16">
-        <f t="shared" si="20"/>
+      <c r="U79" s="16">
+        <f t="shared" si="27"/>
         <v>78.377116999999544</v>
       </c>
     </row>
-    <row r="80" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>173.55891312283134</v>
       </c>
       <c r="H80" s="8">
+        <f t="shared" si="22"/>
+        <v>174</v>
+      </c>
+      <c r="I80" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2">
         <f t="shared" si="19"/>
-        <v>174</v>
-      </c>
-      <c r="I80" s="2">
-        <f t="shared" si="16"/>
         <v>-6.7847553639567805E-3</v>
       </c>
-      <c r="Q80">
+      <c r="K80" s="4">
+        <f t="shared" si="23"/>
+        <v>1724.1379310344828</v>
+      </c>
+      <c r="O80" s="19">
+        <f t="shared" si="24"/>
+        <v>1034.4827586206898</v>
+      </c>
+      <c r="P80" s="19">
+        <f t="shared" ref="P70:P88" si="28">O80/60</f>
+        <v>17.241379310344829</v>
+      </c>
+      <c r="T80">
         <v>5</v>
       </c>
-      <c r="R80" s="16">
-        <f t="shared" si="20"/>
+      <c r="U80" s="16">
+        <f t="shared" si="27"/>
         <v>-2.5000000000545697E-2</v>
       </c>
     </row>
-    <row r="81" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>172.40878690312104</v>
       </c>
       <c r="H81" s="8">
+        <f t="shared" si="22"/>
+        <v>172</v>
+      </c>
+      <c r="I81" s="41">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="J81" s="2">
         <f t="shared" si="19"/>
-        <v>172</v>
-      </c>
-      <c r="I81" s="2">
-        <f t="shared" si="16"/>
         <v>-6.6939325165285592E-3</v>
       </c>
-      <c r="Q81">
+      <c r="K81" s="4">
+        <f t="shared" si="23"/>
+        <v>1744.1860465116279</v>
+      </c>
+      <c r="O81" s="19">
+        <f t="shared" si="24"/>
+        <v>1046.5116279069769</v>
+      </c>
+      <c r="P81" s="19">
+        <f t="shared" si="28"/>
+        <v>17.441860465116282</v>
+      </c>
+      <c r="T81">
         <v>5.0999999999999996</v>
       </c>
-      <c r="R81" s="16">
-        <f t="shared" si="20"/>
+      <c r="U81" s="16">
+        <f t="shared" si="27"/>
         <v>-88.427217000000383</v>
       </c>
     </row>
-    <row r="82" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>171.28122313981333</v>
       </c>
       <c r="H82" s="8">
+        <f t="shared" si="22"/>
+        <v>171</v>
+      </c>
+      <c r="I82" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J82" s="2">
         <f t="shared" si="19"/>
-        <v>171</v>
-      </c>
-      <c r="I82" s="2">
-        <f t="shared" si="16"/>
         <v>-6.6055088447568447E-3</v>
       </c>
-      <c r="Q82">
+      <c r="K82" s="4">
+        <f t="shared" si="23"/>
+        <v>1754.3859649122808</v>
+      </c>
+      <c r="O82" s="19">
+        <f t="shared" si="24"/>
+        <v>1052.6315789473683</v>
+      </c>
+      <c r="P82" s="19">
+        <f t="shared" si="28"/>
+        <v>17.543859649122805</v>
+      </c>
+      <c r="T82">
         <v>5.2</v>
       </c>
-      <c r="R82" s="16">
-        <f t="shared" si="20"/>
+      <c r="U82" s="16">
+        <f t="shared" si="27"/>
         <v>-187.22953600000073</v>
       </c>
     </row>
-    <row r="83" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>170.17549376331323</v>
       </c>
       <c r="H83" s="8">
+        <f t="shared" si="22"/>
+        <v>170</v>
+      </c>
+      <c r="I83" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J83" s="2">
         <f t="shared" si="19"/>
-        <v>170</v>
-      </c>
-      <c r="I83" s="2">
-        <f t="shared" si="16"/>
         <v>-6.5193905333934508E-3</v>
       </c>
-      <c r="Q83">
+      <c r="K83" s="4">
+        <f t="shared" si="23"/>
+        <v>1764.7058823529412</v>
+      </c>
+      <c r="O83" s="19">
+        <f t="shared" si="24"/>
+        <v>1058.8235294117649</v>
+      </c>
+      <c r="P83" s="19">
+        <f t="shared" si="28"/>
+        <v>17.647058823529413</v>
+      </c>
+      <c r="T83">
         <v>5.3</v>
       </c>
-      <c r="R83" s="16">
-        <f t="shared" si="20"/>
+      <c r="U83" s="16">
+        <f t="shared" si="27"/>
         <v>-296.8319590000001</v>
       </c>
     </row>
-    <row r="84" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>169.09090317222555</v>
       </c>
       <c r="H84" s="8">
+        <f t="shared" si="22"/>
+        <v>169</v>
+      </c>
+      <c r="I84" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J84" s="2">
         <f t="shared" si="19"/>
-        <v>169</v>
-      </c>
-      <c r="I84" s="2">
-        <f t="shared" si="16"/>
         <v>-6.4354885950194353E-3</v>
       </c>
-      <c r="Q84">
+      <c r="K84" s="4">
+        <f t="shared" si="23"/>
+        <v>1775.1479289940828</v>
+      </c>
+      <c r="O84" s="19">
+        <f t="shared" si="24"/>
+        <v>1065.0887573964496</v>
+      </c>
+      <c r="P84" s="19">
+        <f t="shared" si="28"/>
+        <v>17.751479289940828</v>
+      </c>
+      <c r="T84">
         <v>5.4</v>
       </c>
-      <c r="R84" s="16">
-        <f t="shared" si="20"/>
+      <c r="U84" s="16">
+        <f t="shared" si="27"/>
         <v>-417.6344880000006</v>
       </c>
     </row>
-    <row r="85" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>168.02678639541745</v>
       </c>
       <c r="H85" s="8">
+        <f t="shared" si="22"/>
+        <v>168</v>
+      </c>
+      <c r="I85" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J85" s="2">
         <f t="shared" si="19"/>
-        <v>168</v>
-      </c>
-      <c r="I85" s="2">
-        <f t="shared" si="16"/>
         <v>-6.3537185634664354E-3</v>
       </c>
-      <c r="Q85">
+      <c r="K85" s="4">
+        <f t="shared" si="23"/>
+        <v>1785.7142857142858</v>
+      </c>
+      <c r="O85" s="19">
+        <f t="shared" si="24"/>
+        <v>1071.4285714285716</v>
+      </c>
+      <c r="P85" s="19">
+        <f t="shared" si="28"/>
+        <v>17.857142857142858</v>
+      </c>
+      <c r="T85">
         <v>5.5</v>
       </c>
-      <c r="R85" s="16">
-        <f t="shared" si="20"/>
+      <c r="U85" s="16">
+        <f t="shared" si="27"/>
         <v>-550.03712500000074</v>
       </c>
     </row>
-    <row r="86" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>166.98250737964526</v>
       </c>
       <c r="H86" s="8">
+        <f t="shared" si="22"/>
+        <v>167</v>
+      </c>
+      <c r="I86" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2">
         <f t="shared" si="19"/>
-        <v>167</v>
-      </c>
-      <c r="I86" s="2">
-        <f t="shared" si="16"/>
         <v>-6.2740002103047207E-3</v>
       </c>
-      <c r="Q86">
+      <c r="K86" s="4">
+        <f t="shared" si="23"/>
+        <v>1796.4071856287426</v>
+      </c>
+      <c r="O86" s="19">
+        <f t="shared" si="24"/>
+        <v>1077.8443113772455</v>
+      </c>
+      <c r="P86" s="19">
+        <f t="shared" si="28"/>
+        <v>17.964071856287426</v>
+      </c>
+      <c r="T86">
         <v>5.6</v>
       </c>
-      <c r="R86" s="16">
-        <f t="shared" si="20"/>
+      <c r="U86" s="16">
+        <f t="shared" si="27"/>
         <v>-694.43987199999992</v>
       </c>
     </row>
-    <row r="87" spans="5:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>165.95745739273343</v>
       </c>
       <c r="H87" s="8">
+        <f t="shared" si="22"/>
+        <v>166</v>
+      </c>
+      <c r="I87" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J87" s="2">
         <f t="shared" si="19"/>
-        <v>166</v>
-      </c>
-      <c r="I87" s="2">
-        <f t="shared" si="16"/>
         <v>-6.1962572823985075E-3</v>
       </c>
-    </row>
-    <row r="88" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K87" s="4">
+        <f t="shared" si="23"/>
+        <v>1807.2289156626507</v>
+      </c>
+      <c r="O87" s="19">
+        <f t="shared" si="24"/>
+        <v>1084.3373493975905</v>
+      </c>
+      <c r="P87" s="19">
+        <f t="shared" si="28"/>
+        <v>18.072289156626507</v>
+      </c>
+    </row>
+    <row r="88" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>164.95105353320301</v>
       </c>
       <c r="H88" s="8">
+        <f t="shared" si="22"/>
+        <v>165</v>
+      </c>
+      <c r="I88" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2">
         <f t="shared" si="19"/>
-        <v>165</v>
-      </c>
-      <c r="I88" s="2">
-        <f t="shared" si="16"/>
         <v>-6.1204172587246515E-3</v>
       </c>
-    </row>
-    <row r="89" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K88" s="4">
+        <f t="shared" si="23"/>
+        <v>1818.1818181818182</v>
+      </c>
+      <c r="O88" s="19">
+        <f t="shared" si="24"/>
+        <v>1090.909090909091</v>
+      </c>
+      <c r="P88" s="19">
+        <f t="shared" si="28"/>
+        <v>18.181818181818183</v>
+      </c>
+    </row>
+    <row r="89" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>163.96273733806481</v>
       </c>
       <c r="H89" s="8">
+        <f t="shared" si="22"/>
+        <v>164</v>
+      </c>
+      <c r="I89" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J89" s="2">
         <f t="shared" si="19"/>
-        <v>164</v>
-      </c>
-      <c r="I89" s="2">
-        <f t="shared" si="16"/>
         <v>-6.0464111248252454E-3</v>
       </c>
-    </row>
-    <row r="90" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K89" s="4">
+        <f t="shared" si="23"/>
+        <v>1829.2682926829268</v>
+      </c>
+      <c r="O89" s="19">
+        <f t="shared" si="24"/>
+        <v>1097.560975609756</v>
+      </c>
+      <c r="P89" s="19"/>
+    </row>
+    <row r="90" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>162.99197348122726</v>
       </c>
       <c r="H90" s="8">
+        <f t="shared" si="22"/>
+        <v>163</v>
+      </c>
+      <c r="I90" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J90" s="2">
         <f t="shared" si="19"/>
-        <v>163</v>
-      </c>
-      <c r="I90" s="2">
-        <f t="shared" si="16"/>
         <v>-5.974173163420274E-3</v>
       </c>
-    </row>
-    <row r="91" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K90" s="4">
+        <f t="shared" si="23"/>
+        <v>1840.4907975460123</v>
+      </c>
+      <c r="O90" s="19">
+        <f t="shared" si="24"/>
+        <v>1104.2944785276075</v>
+      </c>
+      <c r="P90" s="19"/>
+    </row>
+    <row r="91" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>162.03824855563084</v>
       </c>
       <c r="H91" s="8">
+        <f t="shared" si="22"/>
+        <v>162</v>
+      </c>
+      <c r="I91" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J91" s="2">
         <f t="shared" si="19"/>
-        <v>162</v>
-      </c>
-      <c r="I91" s="2">
-        <f t="shared" si="16"/>
         <v>-5.9036407598455761E-3</v>
       </c>
-    </row>
-    <row r="92" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K91" s="4">
+        <f t="shared" si="23"/>
+        <v>1851.851851851852</v>
+      </c>
+    </row>
+    <row r="92" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>161.10106993281892</v>
       </c>
       <c r="H92" s="8">
+        <f t="shared" si="22"/>
+        <v>161</v>
+      </c>
+      <c r="I92" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J92" s="2">
         <f t="shared" si="19"/>
-        <v>161</v>
-      </c>
-      <c r="I92" s="2">
-        <f t="shared" si="16"/>
         <v>-5.8347542211058664E-3</v>
       </c>
-    </row>
-    <row r="93" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K92" s="4">
+        <f t="shared" si="23"/>
+        <v>1863.3540372670807</v>
+      </c>
+    </row>
+    <row r="93" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>160.17996469419262</v>
       </c>
       <c r="H93" s="8">
+        <f t="shared" si="22"/>
+        <v>160</v>
+      </c>
+      <c r="I93" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J93" s="2">
         <f t="shared" si="19"/>
-        <v>160</v>
-      </c>
-      <c r="I93" s="2">
-        <f t="shared" si="16"/>
         <v>-5.7674566074442241E-3</v>
       </c>
-    </row>
-    <row r="94" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K93" s="4">
+        <f t="shared" si="23"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="94" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>159.2744786286859</v>
       </c>
       <c r="H94" s="8">
+        <f t="shared" si="22"/>
+        <v>159</v>
+      </c>
+      <c r="I94" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2">
         <f t="shared" si="19"/>
-        <v>159</v>
-      </c>
-      <c r="I94" s="2">
-        <f t="shared" si="16"/>
         <v>-5.7016935754295095E-3</v>
       </c>
-    </row>
-    <row r="95" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K94" s="4">
+        <f t="shared" si="23"/>
+        <v>1886.7924528301887</v>
+      </c>
+    </row>
+    <row r="95" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>158.38417529203704</v>
       </c>
       <c r="H95" s="8">
+        <f t="shared" si="22"/>
+        <v>158</v>
+      </c>
+      <c r="I95" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J95" s="2">
         <f t="shared" si="19"/>
-        <v>158</v>
-      </c>
-      <c r="I95" s="2">
-        <f t="shared" si="16"/>
         <v>-5.6374132316532712E-3</v>
       </c>
-    </row>
-    <row r="96" spans="5:18" x14ac:dyDescent="0.25">
+      <c r="K95" s="4">
+        <f t="shared" si="23"/>
+        <v>1898.7341772151899</v>
+      </c>
+    </row>
+    <row r="96" spans="5:21" x14ac:dyDescent="0.25">
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>157.5086351232332</v>
       </c>
       <c r="H96" s="8">
+        <f t="shared" si="22"/>
+        <v>158</v>
+      </c>
+      <c r="I96" s="41">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J96" s="2">
         <f t="shared" si="19"/>
-        <v>158</v>
-      </c>
-      <c r="I96" s="2">
-        <f t="shared" si="16"/>
         <v>-5.5745659962086035E-3</v>
       </c>
-    </row>
-    <row r="97" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K96" s="4">
+        <f t="shared" si="23"/>
+        <v>1898.7341772151899</v>
+      </c>
+    </row>
+    <row r="97" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>156.64745461406679</v>
       </c>
       <c r="H97" s="8">
+        <f t="shared" si="22"/>
+        <v>157</v>
+      </c>
+      <c r="I97" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J97" s="2">
         <f t="shared" si="19"/>
-        <v>157</v>
-      </c>
-      <c r="I97" s="2">
-        <f t="shared" si="16"/>
         <v>-5.5131044751964026E-3</v>
       </c>
-    </row>
-    <row r="98" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K97" s="4">
+        <f t="shared" si="23"/>
+        <v>1910.8280254777071</v>
+      </c>
+    </row>
+    <row r="98" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>155.80024552807154</v>
       </c>
       <c r="H98" s="8">
+        <f t="shared" si="22"/>
+        <v>156</v>
+      </c>
+      <c r="I98" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J98" s="2">
         <f t="shared" si="19"/>
-        <v>156</v>
-      </c>
-      <c r="I98" s="2">
-        <f t="shared" si="16"/>
         <v>-5.4529833415702476E-3</v>
       </c>
-    </row>
-    <row r="99" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K98" s="4">
+        <f t="shared" si="23"/>
+        <v>1923.0769230769231</v>
+      </c>
+    </row>
+    <row r="99" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>154.96663416540605</v>
       </c>
       <c r="H99" s="8">
+        <f t="shared" si="22"/>
+        <v>155</v>
+      </c>
+      <c r="I99" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J99" s="2">
         <f t="shared" si="19"/>
-        <v>155</v>
-      </c>
-      <c r="I99" s="2">
-        <f t="shared" si="16"/>
         <v>-5.3941592236905278E-3</v>
       </c>
-    </row>
-    <row r="100" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K99" s="4">
+        <f t="shared" si="23"/>
+        <v>1935.483870967742</v>
+      </c>
+    </row>
+    <row r="100" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>154.14626067052401</v>
       </c>
       <c r="H100" s="8">
+        <f t="shared" si="22"/>
+        <v>154</v>
+      </c>
+      <c r="I100" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J100" s="2">
         <f t="shared" si="19"/>
-        <v>154</v>
-      </c>
-      <c r="I100" s="2">
-        <f t="shared" si="16"/>
         <v>-5.3365906010121771E-3</v>
       </c>
-    </row>
-    <row r="101" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K100" s="4">
+        <f t="shared" si="23"/>
+        <v>1948.0519480519481</v>
+      </c>
+    </row>
+    <row r="101" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>153.33877837971963</v>
       </c>
       <c r="H101" s="8">
+        <f t="shared" si="22"/>
+        <v>153</v>
+      </c>
+      <c r="I101" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J101" s="2">
         <f t="shared" si="19"/>
-        <v>153</v>
-      </c>
-      <c r="I101" s="2">
-        <f t="shared" si="16"/>
         <v>-5.2802377063789199E-3</v>
       </c>
-    </row>
-    <row r="102" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K101" s="4">
+        <f t="shared" si="23"/>
+        <v>1960.7843137254902</v>
+      </c>
+    </row>
+    <row r="102" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>152.54385320586184</v>
       </c>
       <c r="H102" s="8">
+        <f t="shared" si="22"/>
+        <v>153</v>
+      </c>
+      <c r="I102" s="41">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J102" s="2">
         <f t="shared" si="19"/>
-        <v>153</v>
-      </c>
-      <c r="I102" s="2">
-        <f t="shared" si="16"/>
         <v>-5.2250624344410603E-3</v>
       </c>
-    </row>
-    <row r="103" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K102" s="4">
+        <f t="shared" si="23"/>
+        <v>1960.7843137254902</v>
+      </c>
+    </row>
+    <row r="103" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>151.76116305783864</v>
       </c>
       <c r="H103" s="8">
+        <f t="shared" si="22"/>
+        <v>152</v>
+      </c>
+      <c r="I103" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J103" s="2">
         <f t="shared" si="19"/>
-        <v>152</v>
-      </c>
-      <c r="I103" s="2">
-        <f t="shared" si="16"/>
         <v>-5.171028255753672E-3</v>
       </c>
-    </row>
-    <row r="104" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K103" s="4">
+        <f t="shared" si="23"/>
+        <v>1973.6842105263158</v>
+      </c>
+    </row>
+    <row r="104" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>150.99039729242082</v>
       </c>
       <c r="H104" s="8">
+        <f t="shared" si="22"/>
+        <v>151</v>
+      </c>
+      <c r="I104" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J104" s="2">
         <f t="shared" si="19"/>
-        <v>151</v>
-      </c>
-      <c r="I104" s="2">
-        <f t="shared" si="16"/>
         <v>-5.1181001361484202E-3</v>
       </c>
-    </row>
-    <row r="105" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K104" s="4">
+        <f t="shared" si="23"/>
+        <v>1986.7549668874171</v>
+      </c>
+    </row>
+    <row r="105" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>150.2312561964271</v>
       </c>
       <c r="H105" s="8">
+        <f t="shared" si="22"/>
+        <v>150</v>
+      </c>
+      <c r="I105" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J105" s="2">
         <f t="shared" si="19"/>
-        <v>150</v>
-      </c>
-      <c r="I105" s="2">
-        <f t="shared" si="16"/>
         <v>-5.0662444610051283E-3</v>
       </c>
-    </row>
-    <row r="106" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K105" s="4">
+        <f t="shared" si="23"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="106" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>149.48345049723122</v>
       </c>
       <c r="H106" s="8">
+        <f t="shared" si="22"/>
+        <v>149</v>
+      </c>
+      <c r="I106" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2">
         <f t="shared" si="19"/>
-        <v>149</v>
-      </c>
-      <c r="I106" s="2">
-        <f t="shared" si="16"/>
         <v>-5.0154289640792259E-3</v>
       </c>
-    </row>
-    <row r="107" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K106" s="4">
+        <f t="shared" si="23"/>
+        <v>2013.4228187919464</v>
+      </c>
+    </row>
+    <row r="107" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>148.74670089979574</v>
       </c>
       <c r="H107" s="8">
+        <f t="shared" si="22"/>
+        <v>149</v>
+      </c>
+      <c r="I107" s="41">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J107" s="2">
         <f t="shared" si="19"/>
-        <v>149</v>
-      </c>
-      <c r="I107" s="2">
-        <f t="shared" si="16"/>
         <v>-4.9656226605684839E-3</v>
       </c>
-    </row>
-    <row r="108" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K107" s="4">
+        <f t="shared" si="23"/>
+        <v>2013.4228187919464</v>
+      </c>
+    </row>
+    <row r="108" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>148.02073764855041</v>
       </c>
       <c r="H108" s="8">
+        <f t="shared" si="22"/>
+        <v>148</v>
+      </c>
+      <c r="I108" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J108" s="2">
         <f t="shared" si="19"/>
-        <v>148</v>
-      </c>
-      <c r="I108" s="2">
-        <f t="shared" si="16"/>
         <v>-4.9167957841273983E-3</v>
       </c>
-    </row>
-    <row r="109" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K108" s="4">
+        <f t="shared" si="23"/>
+        <v>2027.0270270270271</v>
+      </c>
+    </row>
+    <row r="109" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>147.30530011255479</v>
       </c>
       <c r="H109" s="8">
+        <f t="shared" si="22"/>
+        <v>147</v>
+      </c>
+      <c r="I109" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J109" s="2">
         <f t="shared" si="19"/>
-        <v>147</v>
-      </c>
-      <c r="I109" s="2">
-        <f t="shared" si="16"/>
         <v>-4.8689197275602189E-3</v>
       </c>
-    </row>
-    <row r="110" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K109" s="4">
+        <f t="shared" si="23"/>
+        <v>2040.8163265306123</v>
+      </c>
+    </row>
+    <row r="110" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>146.60013639249684</v>
       </c>
       <c r="H110" s="8">
+        <f t="shared" si="22"/>
+        <v>147</v>
+      </c>
+      <c r="I110" s="41">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J110" s="2">
         <f t="shared" si="19"/>
-        <v>147</v>
-      </c>
-      <c r="I110" s="2">
-        <f t="shared" si="16"/>
         <v>-4.8219669869444069E-3</v>
       </c>
-    </row>
-    <row r="111" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K110" s="4">
+        <f t="shared" si="23"/>
+        <v>2040.8163265306123</v>
+      </c>
+    </row>
+    <row r="111" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>145.90500294818193</v>
       </c>
       <c r="H111" s="8">
+        <f t="shared" si="22"/>
+        <v>146</v>
+      </c>
+      <c r="I111" s="41">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="J111" s="2">
         <f t="shared" si="19"/>
-        <v>146</v>
-      </c>
-      <c r="I111" s="2">
-        <f t="shared" si="16"/>
         <v>-4.7759111089552605E-3</v>
       </c>
-    </row>
-    <row r="112" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="K111" s="4">
+        <f t="shared" si="23"/>
+        <v>2054.794520547945</v>
+      </c>
+    </row>
+    <row r="112" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>145.21966424526187</v>
       </c>
-      <c r="I112" s="2">
-        <f t="shared" si="16"/>
+      <c r="J112" s="2">
+        <f t="shared" si="19"/>
         <v>-4.7307266411797727E-3</v>
       </c>
     </row>
-    <row r="113" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3">
-        <f t="shared" ref="G113:G169" si="21">G112*(1+I113+1.5*I113*I113)</f>
+        <f t="shared" ref="G113:G169" si="29">G112*(1+J113+1.5*J113*J113)</f>
         <v>144.54389242004035</v>
       </c>
-      <c r="I113" s="2">
-        <f t="shared" ref="I113:I152" si="22">-1*$B$22*G112*G112</f>
+      <c r="J113" s="2">
+        <f t="shared" ref="J113:J152" si="30">-1*$B$22*G112*G112</f>
         <v>-4.6863890852236866E-3</v>
       </c>
     </row>
-    <row r="114" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>143.87746696127192</v>
       </c>
-      <c r="I114" s="2">
-        <f t="shared" si="22"/>
+      <c r="J114" s="2">
+        <f t="shared" si="30"/>
         <v>-4.6428748524302661E-3</v>
       </c>
     </row>
-    <row r="115" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>143.22017440794573</v>
       </c>
-      <c r="I115" s="2">
-        <f t="shared" si="22"/>
+      <c r="J115" s="2">
+        <f t="shared" si="30"/>
         <v>-4.6001612220426431E-3</v>
       </c>
     </row>
-    <row r="116" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>142.57180806211369</v>
       </c>
-      <c r="I116" s="2">
-        <f t="shared" si="22"/>
+      <c r="J116" s="2">
+        <f t="shared" si="30"/>
         <v>-4.5582263016538645E-3</v>
       </c>
     </row>
-    <row r="117" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>141.93216771588581</v>
       </c>
-      <c r="I117" s="2">
-        <f t="shared" si="22"/>
+      <c r="J117" s="2">
+        <f t="shared" si="30"/>
         <v>-4.5170489898000406E-3</v>
       </c>
     </row>
-    <row r="118" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>141.30105939177443</v>
       </c>
-      <c r="I118" s="2">
-        <f t="shared" si="22"/>
+      <c r="J118" s="2">
+        <f t="shared" si="30"/>
         <v>-4.4766089405622973E-3</v>
       </c>
     </row>
-    <row r="119" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>140.67829509562256</v>
       </c>
-      <c r="I119" s="2">
-        <f t="shared" si="22"/>
+      <c r="J119" s="2">
+        <f t="shared" si="30"/>
         <v>-4.4368865300528368E-3</v>
       </c>
     </row>
-    <row r="120" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>140.06369258140188</v>
       </c>
-      <c r="I120" s="2">
-        <f t="shared" si="22"/>
+      <c r="J120" s="2">
+        <f t="shared" si="30"/>
         <v>-4.3978628246691244E-3</v>
       </c>
     </row>
-    <row r="121" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>139.45707512721262</v>
       </c>
-      <c r="I121" s="2">
-        <f t="shared" si="22"/>
+      <c r="J121" s="2">
+        <f t="shared" si="30"/>
         <v>-4.3595195510083224E-3</v>
       </c>
     </row>
-    <row r="122" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>138.85827132185997</v>
       </c>
-      <c r="I122" s="2">
-        <f t="shared" si="22"/>
+      <c r="J122" s="2">
+        <f t="shared" si="30"/>
         <v>-4.3218390673415603E-3</v>
       </c>
     </row>
-    <row r="123" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>138.26711486142207</v>
       </c>
-      <c r="I123" s="2">
-        <f t="shared" si="22"/>
+      <c r="J123" s="2">
+        <f t="shared" si="30"/>
         <v>-4.2848043365545062E-3</v>
       </c>
     </row>
-    <row r="124" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>137.68344435526149</v>
       </c>
-      <c r="I124" s="2">
-        <f t="shared" si="22"/>
+      <c r="J124" s="2">
+        <f t="shared" si="30"/>
         <v>-4.2483989004670408E-3</v>
       </c>
     </row>
-    <row r="125" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>137.10710314096625</v>
       </c>
-      <c r="I125" s="2">
-        <f t="shared" si="22"/>
+      <c r="J125" s="2">
+        <f t="shared" si="30"/>
         <v>-4.2126068554507517E-3</v>
       </c>
     </row>
-    <row r="126" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>136.53793910773899</v>
       </c>
-      <c r="I126" s="2">
-        <f t="shared" si="22"/>
+      <c r="J126" s="2">
+        <f t="shared" si="30"/>
         <v>-4.177412829268346E-3</v>
       </c>
     </row>
-    <row r="127" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>135.97580452778206</v>
       </c>
-      <c r="I127" s="2">
-        <f t="shared" si="22"/>
+      <c r="J127" s="2">
+        <f t="shared" si="30"/>
         <v>-4.1428019590641421E-3</v>
       </c>
     </row>
-    <row r="128" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>135.42055589525427</v>
       </c>
-      <c r="I128" s="2">
-        <f t="shared" si="22"/>
+      <c r="J128" s="2">
+        <f t="shared" si="30"/>
         <v>-4.1087598704394662E-3</v>
       </c>
     </row>
-    <row r="129" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>134.87205377240082</v>
       </c>
-      <c r="I129" s="2">
-        <f t="shared" si="22"/>
+      <c r="J129" s="2">
+        <f t="shared" si="30"/>
         <v>-4.075272657551041E-3</v>
       </c>
     </row>
-    <row r="130" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>134.33016264248175</v>
       </c>
-      <c r="I130" s="2">
-        <f t="shared" si="22"/>
+      <c r="J130" s="2">
+        <f t="shared" si="30"/>
         <v>-4.0423268641745285E-3</v>
       </c>
     </row>
-    <row r="131" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>133.79475076914684</v>
       </c>
-      <c r="I131" s="2">
-        <f t="shared" si="22"/>
+      <c r="J131" s="2">
+        <f t="shared" si="30"/>
         <v>-4.0099094656790221E-3</v>
       </c>
     </row>
-    <row r="132" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>133.26569006192568</v>
       </c>
-      <c r="I132" s="2">
-        <f t="shared" si="22"/>
+      <c r="J132" s="2">
+        <f t="shared" si="30"/>
         <v>-3.9780078518618046E-3</v>
       </c>
     </row>
-    <row r="133" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>132.74285594752098</v>
       </c>
-      <c r="I133" s="2">
-        <f t="shared" si="22"/>
+      <c r="J133" s="2">
+        <f t="shared" si="30"/>
         <v>-3.9466098105958303E-3</v>
       </c>
     </row>
-    <row r="134" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>132.22612724661192</v>
       </c>
-      <c r="I134" s="2">
-        <f t="shared" si="22"/>
+      <c r="J134" s="2">
+        <f t="shared" si="30"/>
         <v>-3.915703512245401E-3</v>
       </c>
     </row>
-    <row r="135" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>131.71538605589041</v>
       </c>
-      <c r="I135" s="2">
-        <f t="shared" si="22"/>
+      <c r="J135" s="2">
+        <f t="shared" si="30"/>
         <v>-3.8852774948082685E-3</v>
       </c>
     </row>
-    <row r="136" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>131.21051763506998</v>
       </c>
-      <c r="I136" s="2">
-        <f t="shared" si="22"/>
+      <c r="J136" s="2">
+        <f t="shared" si="30"/>
         <v>-3.8553206497449442E-3</v>
       </c>
     </row>
-    <row r="137" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>130.71141029862133</v>
       </c>
-      <c r="I137" s="2">
-        <f t="shared" si="22"/>
+      <c r="J137" s="2">
+        <f t="shared" si="30"/>
         <v>-3.8258222084584467E-3</v>
       </c>
     </row>
-    <row r="138" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>130.21795531200272</v>
       </c>
-      <c r="I138" s="2">
-        <f t="shared" si="22"/>
+      <c r="J138" s="2">
+        <f t="shared" si="30"/>
         <v>-3.7967717293898957E-3</v>
       </c>
     </row>
-    <row r="139" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>129.73004679216609</v>
       </c>
-      <c r="I139" s="2">
-        <f t="shared" si="22"/>
+      <c r="J139" s="2">
+        <f t="shared" si="30"/>
         <v>-3.7681590856974969E-3</v>
       </c>
     </row>
-    <row r="140" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>129.24758161213268</v>
       </c>
-      <c r="I140" s="2">
-        <f t="shared" si="22"/>
+      <c r="J140" s="2">
+        <f t="shared" si="30"/>
         <v>-3.7399744534883563E-3</v>
       </c>
     </row>
-    <row r="141" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>128.77045930944237</v>
       </c>
-      <c r="I141" s="2">
-        <f t="shared" si="22"/>
+      <c r="J141" s="2">
+        <f t="shared" si="30"/>
         <v>-3.7122083005744215E-3</v>
       </c>
     </row>
-    <row r="142" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>128.29858199829272</v>
       </c>
-      <c r="I142" s="2">
-        <f t="shared" si="22"/>
+      <c r="J142" s="2">
+        <f t="shared" si="30"/>
         <v>-3.6848513757255009E-3</v>
       </c>
     </row>
-    <row r="143" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>127.83185428519305</v>
       </c>
-      <c r="I143" s="2">
-        <f t="shared" si="22"/>
+      <c r="J143" s="2">
+        <f t="shared" si="30"/>
         <v>-3.65789469839392E-3</v>
       </c>
     </row>
-    <row r="144" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>127.37018318796851</v>
       </c>
-      <c r="I144" s="2">
-        <f t="shared" si="22"/>
+      <c r="J144" s="2">
+        <f t="shared" si="30"/>
         <v>-3.6313295488868504E-3</v>
       </c>
     </row>
-    <row r="145" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>126.91347805795824</v>
       </c>
-      <c r="I145" s="2">
-        <f t="shared" si="22"/>
+      <c r="J145" s="2">
+        <f t="shared" si="30"/>
         <v>-3.6051474589637012E-3</v>
       </c>
     </row>
-    <row r="146" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>126.4616505052596</v>
       </c>
-      <c r="I146" s="2">
-        <f t="shared" si="22"/>
+      <c r="J146" s="2">
+        <f t="shared" si="30"/>
         <v>-3.5793402028372993E-3</v>
       </c>
     </row>
-    <row r="147" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>126.01461432687869</v>
       </c>
-      <c r="I147" s="2">
-        <f t="shared" si="22"/>
+      <c r="J147" s="2">
+        <f t="shared" si="30"/>
         <v>-3.5538997885587609E-3</v>
       </c>
     </row>
-    <row r="148" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>125.57228543765449</v>
       </c>
-      <c r="I148" s="2">
-        <f t="shared" si="22"/>
+      <c r="J148" s="2">
+        <f t="shared" si="30"/>
         <v>-3.5288184497671063E-3</v>
       </c>
     </row>
-    <row r="149" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>125.13458180383101</v>
       </c>
-      <c r="I149" s="2">
-        <f t="shared" si="22"/>
+      <c r="J149" s="2">
+        <f t="shared" si="30"/>
         <v>-3.5040886377857273E-3</v>
       </c>
     </row>
-    <row r="150" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>124.70142337915831</v>
       </c>
-      <c r="I150" s="2">
-        <f t="shared" si="22"/>
+      <c r="J150" s="2">
+        <f t="shared" si="30"/>
         <v>-3.4797030140488166E-3</v>
       </c>
     </row>
-    <row r="151" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>124.27273204340933</v>
       </c>
-      <c r="I151" s="2">
-        <f t="shared" si="22"/>
+      <c r="J151" s="2">
+        <f t="shared" si="30"/>
         <v>-3.4556544428417982E-3</v>
       </c>
     </row>
-    <row r="152" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I152" s="2">
-        <f t="shared" si="22"/>
+      <c r="J152" s="2">
+        <f t="shared" si="30"/>
         <v>-3.4319359843406703E-3</v>
       </c>
     </row>
-    <row r="153" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I153" s="2"/>
-    </row>
-    <row r="154" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I154" s="2"/>
-    </row>
-    <row r="155" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J154" s="2"/>
+    </row>
+    <row r="155" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I155" s="2"/>
-    </row>
-    <row r="156" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I156" s="2"/>
-    </row>
-    <row r="157" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I157" s="2"/>
-    </row>
-    <row r="158" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I158" s="2"/>
-    </row>
-    <row r="159" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I159" s="2"/>
-    </row>
-    <row r="160" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J159" s="2"/>
+    </row>
+    <row r="160" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I160" s="2"/>
-    </row>
-    <row r="161" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J160" s="2"/>
+    </row>
+    <row r="161" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I161" s="2"/>
-    </row>
-    <row r="162" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J161" s="2"/>
+    </row>
+    <row r="162" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I162" s="2"/>
-    </row>
-    <row r="163" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J162" s="2"/>
+    </row>
+    <row r="163" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I163" s="2"/>
-    </row>
-    <row r="164" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J163" s="2"/>
+    </row>
+    <row r="164" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I164" s="2"/>
-    </row>
-    <row r="165" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J164" s="2"/>
+    </row>
+    <row r="165" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I165" s="2"/>
-    </row>
-    <row r="166" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J165" s="2"/>
+    </row>
+    <row r="166" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I166" s="2"/>
-    </row>
-    <row r="167" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J166" s="2"/>
+    </row>
+    <row r="167" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I167" s="2"/>
-    </row>
-    <row r="168" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J167" s="2"/>
+    </row>
+    <row r="168" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I168" s="2"/>
-    </row>
-    <row r="169" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J168" s="2"/>
+    </row>
+    <row r="169" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>123.84843154320548</v>
       </c>
-      <c r="I169" s="2"/>
-    </row>
-    <row r="170" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J169" s="2"/>
+    </row>
+    <row r="170" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
-      <c r="I170" s="2"/>
-    </row>
-    <row r="171" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J170" s="2"/>
+    </row>
+    <row r="171" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
-      <c r="I171" s="2"/>
-    </row>
-    <row r="172" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J171" s="2"/>
+    </row>
+    <row r="172" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
-      <c r="I172" s="2"/>
-    </row>
-    <row r="173" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J172" s="2"/>
+    </row>
+    <row r="173" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
-      <c r="I173" s="2"/>
-    </row>
-    <row r="174" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J173" s="2"/>
+    </row>
+    <row r="174" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
-      <c r="I174" s="2"/>
-    </row>
-    <row r="175" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J174" s="2"/>
+    </row>
+    <row r="175" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
-      <c r="I175" s="2"/>
-    </row>
-    <row r="176" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J175" s="2"/>
+    </row>
+    <row r="176" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
-      <c r="I176" s="2"/>
-    </row>
-    <row r="177" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J176" s="2"/>
+    </row>
+    <row r="177" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
-      <c r="I177" s="2"/>
-    </row>
-    <row r="178" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J177" s="2"/>
+    </row>
+    <row r="178" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
-      <c r="I178" s="2"/>
-    </row>
-    <row r="179" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J178" s="2"/>
+    </row>
+    <row r="179" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
-      <c r="I179" s="2"/>
-    </row>
-    <row r="180" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J179" s="2"/>
+    </row>
+    <row r="180" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
-      <c r="I180" s="2"/>
-    </row>
-    <row r="181" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J180" s="2"/>
+    </row>
+    <row r="181" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
-      <c r="I181" s="2"/>
-    </row>
-    <row r="182" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J181" s="2"/>
+    </row>
+    <row r="182" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
-      <c r="I182" s="2"/>
-    </row>
-    <row r="183" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J182" s="2"/>
+    </row>
+    <row r="183" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
-      <c r="I183" s="2"/>
-    </row>
-    <row r="184" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J183" s="2"/>
+    </row>
+    <row r="184" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
-      <c r="I184" s="2"/>
-    </row>
-    <row r="185" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J184" s="2"/>
+    </row>
+    <row r="185" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
-      <c r="I185" s="2"/>
-    </row>
-    <row r="186" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J185" s="2"/>
+    </row>
+    <row r="186" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
-      <c r="I186" s="2"/>
-    </row>
-    <row r="187" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J186" s="2"/>
+    </row>
+    <row r="187" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
-      <c r="I187" s="2"/>
-    </row>
-    <row r="188" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J187" s="2"/>
+    </row>
+    <row r="188" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
-      <c r="I188" s="2"/>
-    </row>
-    <row r="189" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J188" s="2"/>
+    </row>
+    <row r="189" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
-      <c r="I189" s="2"/>
-    </row>
-    <row r="190" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J189" s="2"/>
+    </row>
+    <row r="190" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
-      <c r="I190" s="2"/>
-    </row>
-    <row r="191" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J190" s="2"/>
+    </row>
+    <row r="191" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
-      <c r="I191" s="2"/>
-    </row>
-    <row r="192" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J191" s="2"/>
+    </row>
+    <row r="192" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
-      <c r="I192" s="2"/>
-    </row>
-    <row r="193" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J192" s="2"/>
+    </row>
+    <row r="193" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
-      <c r="I193" s="2"/>
-    </row>
-    <row r="194" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J193" s="2"/>
+    </row>
+    <row r="194" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
-      <c r="I194" s="2"/>
-    </row>
-    <row r="195" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J194" s="2"/>
+    </row>
+    <row r="195" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
-      <c r="I195" s="2"/>
-    </row>
-    <row r="196" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J195" s="2"/>
+    </row>
+    <row r="196" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
-      <c r="I196" s="2"/>
-    </row>
-    <row r="197" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J196" s="2"/>
+    </row>
+    <row r="197" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
-      <c r="I197" s="2"/>
-    </row>
-    <row r="198" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J197" s="2"/>
+    </row>
+    <row r="198" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
-      <c r="I198" s="2"/>
-    </row>
-    <row r="199" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J198" s="2"/>
+    </row>
+    <row r="199" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
-      <c r="I199" s="2"/>
-    </row>
-    <row r="200" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J199" s="2"/>
+    </row>
+    <row r="200" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
-      <c r="I200" s="2"/>
-    </row>
-    <row r="201" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J200" s="2"/>
+    </row>
+    <row r="201" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
-      <c r="I201" s="2"/>
-    </row>
-    <row r="202" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J201" s="2"/>
+    </row>
+    <row r="202" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
-      <c r="I202" s="2"/>
-    </row>
-    <row r="203" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J202" s="2"/>
+    </row>
+    <row r="203" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
-      <c r="I203" s="2"/>
-    </row>
-    <row r="204" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J203" s="2"/>
+    </row>
+    <row r="204" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
-      <c r="I204" s="2"/>
-    </row>
-    <row r="205" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J204" s="2"/>
+    </row>
+    <row r="205" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
-      <c r="I205" s="2"/>
-    </row>
-    <row r="206" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J205" s="2"/>
+    </row>
+    <row r="206" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
-      <c r="I206" s="2"/>
-    </row>
-    <row r="207" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J206" s="2"/>
+    </row>
+    <row r="207" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
-      <c r="I207" s="2"/>
-    </row>
-    <row r="208" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J207" s="2"/>
+    </row>
+    <row r="208" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
-      <c r="I208" s="2"/>
-    </row>
-    <row r="209" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J208" s="2"/>
+    </row>
+    <row r="209" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
-      <c r="I209" s="2"/>
-    </row>
-    <row r="210" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J209" s="2"/>
+    </row>
+    <row r="210" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
-      <c r="I210" s="2"/>
-    </row>
-    <row r="211" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J210" s="2"/>
+    </row>
+    <row r="211" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
-      <c r="I211" s="2"/>
-    </row>
-    <row r="212" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J211" s="2"/>
+    </row>
+    <row r="212" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
-      <c r="I212" s="2"/>
-    </row>
-    <row r="213" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J212" s="2"/>
+    </row>
+    <row r="213" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
-      <c r="I213" s="2"/>
-    </row>
-    <row r="214" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J213" s="2"/>
+    </row>
+    <row r="214" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
-      <c r="I214" s="2"/>
-    </row>
-    <row r="215" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J214" s="2"/>
+    </row>
+    <row r="215" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
-      <c r="I215" s="2"/>
-    </row>
-    <row r="216" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J215" s="2"/>
+    </row>
+    <row r="216" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
-      <c r="I216" s="2"/>
-    </row>
-    <row r="217" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J216" s="2"/>
+    </row>
+    <row r="217" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
-      <c r="I217" s="2"/>
-    </row>
-    <row r="218" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J217" s="2"/>
+    </row>
+    <row r="218" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
-      <c r="I218" s="2"/>
-    </row>
-    <row r="219" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J218" s="2"/>
+    </row>
+    <row r="219" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
-      <c r="I219" s="2"/>
-    </row>
-    <row r="220" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J219" s="2"/>
+    </row>
+    <row r="220" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
-      <c r="I220" s="2"/>
-    </row>
-    <row r="221" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J220" s="2"/>
+    </row>
+    <row r="221" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
-      <c r="I221" s="2"/>
-    </row>
-    <row r="222" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J221" s="2"/>
+    </row>
+    <row r="222" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
-      <c r="I222" s="2"/>
-    </row>
-    <row r="223" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J222" s="2"/>
+    </row>
+    <row r="223" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
-      <c r="I223" s="2"/>
-    </row>
-    <row r="224" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J223" s="2"/>
+    </row>
+    <row r="224" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
-      <c r="I224" s="2"/>
-    </row>
-    <row r="225" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J224" s="2"/>
+    </row>
+    <row r="225" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
-      <c r="I225" s="2"/>
-    </row>
-    <row r="226" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J225" s="2"/>
+    </row>
+    <row r="226" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
-      <c r="I226" s="2"/>
-    </row>
-    <row r="227" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J226" s="2"/>
+    </row>
+    <row r="227" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
-      <c r="I227" s="2"/>
-    </row>
-    <row r="228" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J227" s="2"/>
+    </row>
+    <row r="228" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
-      <c r="I228" s="2"/>
-    </row>
-    <row r="229" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J228" s="2"/>
+    </row>
+    <row r="229" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
-      <c r="I229" s="2"/>
-    </row>
-    <row r="230" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J229" s="2"/>
+    </row>
+    <row r="230" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
-      <c r="I230" s="2"/>
-    </row>
-    <row r="231" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J230" s="2"/>
+    </row>
+    <row r="231" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
-      <c r="I231" s="2"/>
-    </row>
-    <row r="232" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J231" s="2"/>
+    </row>
+    <row r="232" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
-      <c r="I232" s="2"/>
-    </row>
-    <row r="233" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J232" s="2"/>
+    </row>
+    <row r="233" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
-      <c r="I233" s="2"/>
-    </row>
-    <row r="234" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J233" s="2"/>
+    </row>
+    <row r="234" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
-      <c r="I234" s="2"/>
-    </row>
-    <row r="235" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J234" s="2"/>
+    </row>
+    <row r="235" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
-      <c r="I235" s="2"/>
-    </row>
-    <row r="236" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J235" s="2"/>
+    </row>
+    <row r="236" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
-      <c r="I236" s="2"/>
-    </row>
-    <row r="237" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J236" s="2"/>
+    </row>
+    <row r="237" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
-      <c r="I237" s="2"/>
-    </row>
-    <row r="238" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J237" s="2"/>
+    </row>
+    <row r="238" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
-      <c r="I238" s="2"/>
-    </row>
-    <row r="239" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J238" s="2"/>
+    </row>
+    <row r="239" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
-      <c r="I239" s="2"/>
-    </row>
-    <row r="240" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J239" s="2"/>
+    </row>
+    <row r="240" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
-      <c r="I240" s="2"/>
-    </row>
-    <row r="241" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J240" s="2"/>
+    </row>
+    <row r="241" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
-      <c r="I241" s="2"/>
-    </row>
-    <row r="242" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J241" s="2"/>
+    </row>
+    <row r="242" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
-      <c r="I242" s="2"/>
-    </row>
-    <row r="243" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J242" s="2"/>
+    </row>
+    <row r="243" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
-      <c r="I243" s="2"/>
-    </row>
-    <row r="244" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J243" s="2"/>
+    </row>
+    <row r="244" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
-      <c r="I244" s="2"/>
-    </row>
-    <row r="245" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J244" s="2"/>
+    </row>
+    <row r="245" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
-      <c r="I245" s="2"/>
-    </row>
-    <row r="246" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J245" s="2"/>
+    </row>
+    <row r="246" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
-      <c r="I246" s="2"/>
-    </row>
-    <row r="247" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J246" s="2"/>
+    </row>
+    <row r="247" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
-      <c r="I247" s="2"/>
-    </row>
-    <row r="248" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J247" s="2"/>
+    </row>
+    <row r="248" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
-      <c r="I248" s="2"/>
-    </row>
-    <row r="249" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J248" s="2"/>
+    </row>
+    <row r="249" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
-      <c r="I249" s="2"/>
-    </row>
-    <row r="250" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J249" s="2"/>
+    </row>
+    <row r="250" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
-      <c r="I250" s="2"/>
-    </row>
-    <row r="251" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J250" s="2"/>
+    </row>
+    <row r="251" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
-      <c r="I251" s="2"/>
-    </row>
-    <row r="252" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J251" s="2"/>
+    </row>
+    <row r="252" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
-      <c r="I252" s="2"/>
-    </row>
-    <row r="253" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J252" s="2"/>
+    </row>
+    <row r="253" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
-      <c r="I253" s="2"/>
-    </row>
-    <row r="254" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J253" s="2"/>
+    </row>
+    <row r="254" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
-      <c r="I254" s="2"/>
-    </row>
-    <row r="255" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J254" s="2"/>
+    </row>
+    <row r="255" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
-      <c r="I255" s="2"/>
-    </row>
-    <row r="256" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J255" s="2"/>
+    </row>
+    <row r="256" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
-      <c r="I256" s="2"/>
-    </row>
-    <row r="257" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J256" s="2"/>
+    </row>
+    <row r="257" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
-      <c r="I257" s="2"/>
-    </row>
-    <row r="258" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J257" s="2"/>
+    </row>
+    <row r="258" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
-      <c r="I258" s="2"/>
-    </row>
-    <row r="259" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J258" s="2"/>
+    </row>
+    <row r="259" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
-      <c r="I259" s="2"/>
-    </row>
-    <row r="260" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J259" s="2"/>
+    </row>
+    <row r="260" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
-      <c r="I260" s="2"/>
-    </row>
-    <row r="261" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J260" s="2"/>
+    </row>
+    <row r="261" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
-      <c r="I261" s="2"/>
-    </row>
-    <row r="262" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J261" s="2"/>
+    </row>
+    <row r="262" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
-      <c r="I262" s="2"/>
-    </row>
-    <row r="263" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J262" s="2"/>
+    </row>
+    <row r="263" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
-      <c r="I263" s="2"/>
-    </row>
-    <row r="264" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J263" s="2"/>
+    </row>
+    <row r="264" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
-      <c r="I264" s="2"/>
-    </row>
-    <row r="265" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J264" s="2"/>
+    </row>
+    <row r="265" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
-      <c r="I265" s="2"/>
-    </row>
-    <row r="266" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J265" s="2"/>
+    </row>
+    <row r="266" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
-      <c r="I266" s="2"/>
-    </row>
-    <row r="267" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J266" s="2"/>
+    </row>
+    <row r="267" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
-      <c r="I267" s="2"/>
-    </row>
-    <row r="268" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J267" s="2"/>
+    </row>
+    <row r="268" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
-      <c r="I268" s="2"/>
-    </row>
-    <row r="269" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J268" s="2"/>
+    </row>
+    <row r="269" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
-      <c r="I269" s="2"/>
-    </row>
-    <row r="270" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J269" s="2"/>
+    </row>
+    <row r="270" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
-      <c r="I270" s="2"/>
-    </row>
-    <row r="271" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J270" s="2"/>
+    </row>
+    <row r="271" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
-      <c r="I271" s="2"/>
-    </row>
-    <row r="272" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J271" s="2"/>
+    </row>
+    <row r="272" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
-      <c r="I272" s="2"/>
-    </row>
-    <row r="273" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J272" s="2"/>
+    </row>
+    <row r="273" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
-      <c r="I273" s="2"/>
-    </row>
-    <row r="274" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J273" s="2"/>
+    </row>
+    <row r="274" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
-      <c r="I274" s="2"/>
-    </row>
-    <row r="275" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J274" s="2"/>
+    </row>
+    <row r="275" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
-      <c r="I275" s="2"/>
-    </row>
-    <row r="276" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J275" s="2"/>
+    </row>
+    <row r="276" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
-      <c r="I276" s="2"/>
-    </row>
-    <row r="277" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J276" s="2"/>
+    </row>
+    <row r="277" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
-      <c r="I277" s="2"/>
-    </row>
-    <row r="278" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J277" s="2"/>
+    </row>
+    <row r="278" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
-      <c r="I278" s="2"/>
-    </row>
-    <row r="279" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J278" s="2"/>
+    </row>
+    <row r="279" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
-      <c r="I279" s="2"/>
-    </row>
-    <row r="280" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J279" s="2"/>
+    </row>
+    <row r="280" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
-      <c r="I280" s="2"/>
-    </row>
-    <row r="281" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J280" s="2"/>
+    </row>
+    <row r="281" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
-      <c r="I281" s="2"/>
-    </row>
-    <row r="282" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J281" s="2"/>
+    </row>
+    <row r="282" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
-      <c r="I282" s="2"/>
-    </row>
-    <row r="283" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J282" s="2"/>
+    </row>
+    <row r="283" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
-      <c r="I283" s="2"/>
-    </row>
-    <row r="284" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J283" s="2"/>
+    </row>
+    <row r="284" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
-      <c r="I284" s="2"/>
-    </row>
-    <row r="285" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J284" s="2"/>
+    </row>
+    <row r="285" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
-      <c r="I285" s="2"/>
-    </row>
-    <row r="286" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J285" s="2"/>
+    </row>
+    <row r="286" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
-      <c r="I286" s="2"/>
-    </row>
-    <row r="287" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J286" s="2"/>
+    </row>
+    <row r="287" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
-      <c r="I287" s="2"/>
-    </row>
-    <row r="288" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J287" s="2"/>
+    </row>
+    <row r="288" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
-      <c r="I288" s="2"/>
-    </row>
-    <row r="289" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J288" s="2"/>
+    </row>
+    <row r="289" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
-      <c r="I289" s="2"/>
-    </row>
-    <row r="290" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J289" s="2"/>
+    </row>
+    <row r="290" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
-      <c r="I290" s="2"/>
-    </row>
-    <row r="291" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J290" s="2"/>
+    </row>
+    <row r="291" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
-      <c r="I291" s="2"/>
-    </row>
-    <row r="292" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J291" s="2"/>
+    </row>
+    <row r="292" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
-      <c r="I292" s="2"/>
-    </row>
-    <row r="293" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J292" s="2"/>
+    </row>
+    <row r="293" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
-      <c r="I293" s="2"/>
-    </row>
-    <row r="294" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J293" s="2"/>
+    </row>
+    <row r="294" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
-      <c r="I294" s="2"/>
-    </row>
-    <row r="295" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J294" s="2"/>
+    </row>
+    <row r="295" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
-      <c r="I295" s="2"/>
-    </row>
-    <row r="296" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J295" s="2"/>
+    </row>
+    <row r="296" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
-      <c r="I296" s="2"/>
-    </row>
-    <row r="297" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J296" s="2"/>
+    </row>
+    <row r="297" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
-      <c r="I297" s="2"/>
-    </row>
-    <row r="298" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J297" s="2"/>
+    </row>
+    <row r="298" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
-      <c r="I298" s="2"/>
-    </row>
-    <row r="299" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J298" s="2"/>
+    </row>
+    <row r="299" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
-      <c r="I299" s="2"/>
-    </row>
-    <row r="300" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J299" s="2"/>
+    </row>
+    <row r="300" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
-      <c r="I300" s="2"/>
-    </row>
-    <row r="301" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J300" s="2"/>
+    </row>
+    <row r="301" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
-      <c r="I301" s="2"/>
-    </row>
-    <row r="302" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J301" s="2"/>
+    </row>
+    <row r="302" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
-      <c r="I302" s="2"/>
-    </row>
-    <row r="303" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J302" s="2"/>
+    </row>
+    <row r="303" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
-      <c r="I303" s="2"/>
-    </row>
-    <row r="304" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J303" s="2"/>
+    </row>
+    <row r="304" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
-      <c r="I304" s="2"/>
-    </row>
-    <row r="305" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J304" s="2"/>
+    </row>
+    <row r="305" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
-      <c r="I305" s="2"/>
-    </row>
-    <row r="306" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J305" s="2"/>
+    </row>
+    <row r="306" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
-      <c r="I306" s="2"/>
-    </row>
-    <row r="307" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J306" s="2"/>
+    </row>
+    <row r="307" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
-      <c r="I307" s="2"/>
-    </row>
-    <row r="308" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J307" s="2"/>
+    </row>
+    <row r="308" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
-      <c r="I308" s="2"/>
-    </row>
-    <row r="309" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J308" s="2"/>
+    </row>
+    <row r="309" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
-      <c r="I309" s="2"/>
-    </row>
-    <row r="310" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J309" s="2"/>
+    </row>
+    <row r="310" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
-      <c r="I310" s="2"/>
-    </row>
-    <row r="311" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J310" s="2"/>
+    </row>
+    <row r="311" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
-      <c r="I311" s="2"/>
-    </row>
-    <row r="312" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J311" s="2"/>
+    </row>
+    <row r="312" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
-      <c r="I312" s="2"/>
-    </row>
-    <row r="313" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J312" s="2"/>
+    </row>
+    <row r="313" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
-      <c r="I313" s="2"/>
-    </row>
-    <row r="314" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J313" s="2"/>
+    </row>
+    <row r="314" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
-      <c r="I314" s="2"/>
-    </row>
-    <row r="315" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J314" s="2"/>
+    </row>
+    <row r="315" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
-      <c r="I315" s="2"/>
-    </row>
-    <row r="316" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J315" s="2"/>
+    </row>
+    <row r="316" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
-      <c r="I316" s="2"/>
-    </row>
-    <row r="317" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J316" s="2"/>
+    </row>
+    <row r="317" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
-      <c r="I317" s="2"/>
-    </row>
-    <row r="318" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J317" s="2"/>
+    </row>
+    <row r="318" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
-      <c r="I318" s="2"/>
-    </row>
-    <row r="319" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J318" s="2"/>
+    </row>
+    <row r="319" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
-      <c r="I319" s="2"/>
-    </row>
-    <row r="320" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J319" s="2"/>
+    </row>
+    <row r="320" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
-      <c r="I320" s="2"/>
-    </row>
-    <row r="321" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J320" s="2"/>
+    </row>
+    <row r="321" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
-      <c r="I321" s="2"/>
-    </row>
-    <row r="322" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J321" s="2"/>
+    </row>
+    <row r="322" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
-      <c r="I322" s="2"/>
-    </row>
-    <row r="323" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J322" s="2"/>
+    </row>
+    <row r="323" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
-      <c r="I323" s="2"/>
-    </row>
-    <row r="324" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J323" s="2"/>
+    </row>
+    <row r="324" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
-      <c r="I324" s="2"/>
-    </row>
-    <row r="325" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J324" s="2"/>
+    </row>
+    <row r="325" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
-      <c r="I325" s="2"/>
-    </row>
-    <row r="326" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J325" s="2"/>
+    </row>
+    <row r="326" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
-      <c r="I326" s="2"/>
-    </row>
-    <row r="327" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J326" s="2"/>
+    </row>
+    <row r="327" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
-      <c r="I327" s="2"/>
-    </row>
-    <row r="328" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J327" s="2"/>
+    </row>
+    <row r="328" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
-      <c r="I328" s="2"/>
-    </row>
-    <row r="329" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J328" s="2"/>
+    </row>
+    <row r="329" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
-      <c r="I329" s="2"/>
-    </row>
-    <row r="330" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J329" s="2"/>
+    </row>
+    <row r="330" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
-      <c r="I330" s="2"/>
-    </row>
-    <row r="331" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J330" s="2"/>
+    </row>
+    <row r="331" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
-      <c r="I331" s="2"/>
-    </row>
-    <row r="332" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J331" s="2"/>
+    </row>
+    <row r="332" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
-      <c r="I332" s="2"/>
-    </row>
-    <row r="333" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J332" s="2"/>
+    </row>
+    <row r="333" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
-      <c r="I333" s="2"/>
-    </row>
-    <row r="334" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J333" s="2"/>
+    </row>
+    <row r="334" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
-      <c r="I334" s="2"/>
-    </row>
-    <row r="335" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J334" s="2"/>
+    </row>
+    <row r="335" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
-      <c r="I335" s="2"/>
-    </row>
-    <row r="336" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J335" s="2"/>
+    </row>
+    <row r="336" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
-      <c r="I336" s="2"/>
-    </row>
-    <row r="337" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J336" s="2"/>
+    </row>
+    <row r="337" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
-      <c r="I337" s="2"/>
-    </row>
-    <row r="338" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J337" s="2"/>
+    </row>
+    <row r="338" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
-      <c r="I338" s="2"/>
-    </row>
-    <row r="339" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J338" s="2"/>
+    </row>
+    <row r="339" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
-      <c r="I339" s="2"/>
-    </row>
-    <row r="340" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J339" s="2"/>
+    </row>
+    <row r="340" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
-      <c r="I340" s="2"/>
-    </row>
-    <row r="341" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J340" s="2"/>
+    </row>
+    <row r="341" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
-      <c r="I341" s="2"/>
-    </row>
-    <row r="342" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J341" s="2"/>
+    </row>
+    <row r="342" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
-      <c r="I342" s="2"/>
-    </row>
-    <row r="343" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J342" s="2"/>
+    </row>
+    <row r="343" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
-      <c r="I343" s="2"/>
-    </row>
-    <row r="344" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J343" s="2"/>
+    </row>
+    <row r="344" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
-      <c r="I344" s="2"/>
-    </row>
-    <row r="345" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="J344" s="2"/>
+    </row>
+    <row r="345" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
-      <c r="I345" s="2"/>
+      <c r="J345" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
